--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -5000,8 +5000,10 @@
       <c r="A252" t="s">
         <v>1</v>
       </c>
-      <c r="B252" t="s">
-        <v>290</v>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Modeled from the NMC622 inventory provided by Crenna et al., 2021., itself based on Dai et al., 2019. Market normalization correction: 1 kg of battery sold requires 1 kg of complete battery production. The 0.72591 kg cell fraction is already included in battery production and must not be applied again at market level.</t>
+        </is>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.2">
@@ -5088,7 +5090,7 @@
         <v>289</v>
       </c>
       <c r="B260">
-        <v>0.72591000000000006</v>
+        <v>1</v>
       </c>
       <c r="C260" t="s">
         <v>8</v>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X690"/>
+  <dimension ref="A1:X712"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -5652,8 +5652,10 @@
       <c r="A295" t="s">
         <v>1</v>
       </c>
-      <c r="B295" t="s">
-        <v>2</v>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Anode boundary correction: 0.2 kg dry silicon-graphite paste plus 0.12 kg separate copper collector foil per nominal kg cell. Dry paste contains 85.54% synthetic graphite, 8.46% silicon and 6% additives/binders. The prior complete-anode supplier embedded collector foil in the paste input. Remaining cell exchanges are preserved. Retained material inputs sum to 0.9919 kg/kg nominal cell; the 0.0081 kg source rounding/coverage gap is not filled with an assumed material. This boundary/composition correction does not validate practical energy density, first-cycle losses or lifetime.</t>
+        </is>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.2">
@@ -5692,8 +5694,10 @@
       <c r="A300" t="s">
         <v>9</v>
       </c>
-      <c r="B300" t="s">
-        <v>284</v>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Originally from Eleonora Crenna, EMPA, Switzerland, see https://doi.org/10.1016/j.resconrec.2021.105619. Adapted to NMC955 chemistry. The original instruction to substitute 9% by weight of graphite with silicon is implemented in the anode, interpreted as 9% of the 94% graphite-plus-silicon pool. See the dedicated dry-anode paste source and process-proxy metadata.</t>
+        </is>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.2">
@@ -5802,8 +5806,10 @@
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A307" t="s">
-        <v>285</v>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>anode paste production, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
       </c>
       <c r="B307" s="4">
         <v>0.2</v>
@@ -5817,8 +5823,10 @@
       <c r="E307" t="s">
         <v>16</v>
       </c>
-      <c r="F307" t="s">
-        <v>286</v>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.2">
@@ -11351,6 +11359,518 @@
         <v>136</v>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>anode paste production, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Produces 1 kg dry anode mixture with 0.8554 kg synthetic graphite, 0.0846 kg elemental silicon, 0.01 kg carbon black, 0.03 kg CMC and 0.02 kg SBR. The original 94% graphite pool is split 91:9 by mass; silicon is 8.46% of dry paste, not 9% of all dry paste. Synthetic graphite follows the original Crenna dry-paste route. Process proxy: Crenna 2021 supplementary workbook, NMC811 J149:J153: 0.96 kg deionised water, 0.00096 m3 wastewater, 8.48487394434316 MJ heat, 0.46810728671732227 kWh electricity and 4e-10 units chemical factory per kg dry paste. These quantities cover mixing, drying, cutting and calendaring; copper foil is purchased separately by the cell. The process quantities are retained from a 2% silicon design as an explicit proxy for this revised composition, not new measured manufacturing data. Electricity is supplied in CN; legacy graphite and other background identities follow the workbook source version 3.8 and normal premise migration. No foil manufacture, complete anode or additional cell-assembly energy is included here. Practical reversible capacity, formation losses, expansion and lifetime remain unvalidated. SBR follows Crenna NMC811 J148 through the source latex market as a nominal dry-binder proxy; native supplier documentation identifies styrene-butadiene emulsion polymerisation. Wet-latex solids concentration and a new binder process are not modelled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B695">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Crenna et al. (2021), https://doi.org/10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx, NMC811 rows 145-154. Source dry solids: graphite 92%, Si 2%, carbon black 1%, CMC 3%, SBR 2% (binder rounding normalised to the stated 6% total). This premise variant implements the original NMC955 workbook instruction to replace 9% of graphite: 0.94*0.91 graphite and 0.94*0.09 Si. User-approved model interpretation, not the paper's measured NMC955-Si composition. Source processing/solvent quantities are a proxy, kept separately from cell assembly and collector-foil production.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>anode paste production, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
+      </c>
+      <c r="B701">
+        <v>1</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, for Li-ion battery, NMC955</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>One kg of retained dry solids; solvent excluded from product mass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>market for graphite, battery grade</t>
+        </is>
+      </c>
+      <c r="B702">
+        <v>0.8554</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>graphite, battery grade</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>0.94 * (1 - 0.09); synthetic graphite as in the original paste source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B703">
+        <v>0.0846</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>0.94 * 0.09; elemental Si proxy retained from the source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B704">
+        <v>0.01</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>1% of dry paste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>market for carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+      <c r="B705">
+        <v>0.03</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>3% of dry paste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>market for latex</t>
+        </is>
+      </c>
+      <c r="B706">
+        <v>0.02</v>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>latex</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J148: 2% nominal dry SBR binder, supplied through the source latex proxy (styrene-butadiene emulsion polymerisation); no wet-latex concentration model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B707">
+        <v>0.96</v>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J149; process solvent, not retained dry solids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B708">
+        <v>-0.00096</v>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J152; negative waste-market input; 0.96 kg / 1000 kg per m3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B709">
+        <v>0.46810728671732227</v>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J151; mixing, cutting and calendaring process proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B710">
+        <v>8.48487394434316</v>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J150; electrode drying process proxy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B711">
+        <v>4e-10</v>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>Crenna NMC811 J153; paste manufacturing infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712"/>
   </sheetData>
   <autoFilter ref="A1:X737" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1317,15 +1317,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X712"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
     <col min="2" max="2" width="42.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>197</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1381,12 +1381,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>265</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>266</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>256</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1602,12 +1602,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ns3:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>256</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -1967,7 +1967,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -2043,12 +2043,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ns3:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>43</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>0</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2444,12 +2444,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ns3:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -2489,7 +2489,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>65</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>67</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>69</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>74</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>75</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ns3:dyDescent="0.2">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ns3:dyDescent="0.2">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2677,7 +2677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2685,12 +2685,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ns3:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>69</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>77</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>79</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>81</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>67</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>85</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>87</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>72</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>89</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>93</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ns3:dyDescent="0.2">
       <c r="A115" t="s">
         <v>95</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>95</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>0</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>1</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -3106,12 +3106,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ns3:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>74</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>35</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>98</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>98</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>0</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>1</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>3</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3291,7 +3291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -3299,7 +3299,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -3307,12 +3307,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ns3:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>65</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>101</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>72</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ns3:dyDescent="0.2">
       <c r="A146" t="s">
         <v>85</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>103</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>105</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>35</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>70</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>107</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>67</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>75</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>109</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>109</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>98</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>98</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>0</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" ns3:dyDescent="0.2">
       <c r="A165" t="s">
         <v>9</v>
       </c>
@@ -3688,12 +3688,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" ns3:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" ns3:dyDescent="0.2">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>116</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>122</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>159</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>161</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>162</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" ns3:dyDescent="0.2">
       <c r="A173" t="s">
         <v>45</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" ns3:dyDescent="0.2">
       <c r="A174" t="s">
         <v>164</v>
       </c>
@@ -3856,7 +3856,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>0</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>1</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>3</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>7</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" ns3:dyDescent="0.2">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -3912,12 +3912,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" ns3:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>59</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>61</v>
       </c>
@@ -4000,7 +4000,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>52</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" ns3:dyDescent="0.2">
       <c r="A189" t="s">
         <v>57</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" ns3:dyDescent="0.2">
       <c r="A190" t="s">
         <v>55</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>43</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>50</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>89</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>141</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>166</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>166</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>166</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>169</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>169</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A201" s="2" t="s">
         <v>0</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" ns3:dyDescent="0.2">
       <c r="A202" t="s">
         <v>1</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>3</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>5</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>7</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" ns3:dyDescent="0.2">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -4296,12 +4296,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" ns3:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" ns3:dyDescent="0.2">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>118</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>55</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>61</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>52</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>57</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>59</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>141</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>15</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>39</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>171</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>166</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>166</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" ns3:dyDescent="0.2">
       <c r="A222" t="s">
         <v>166</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" ns3:dyDescent="0.2">
       <c r="A223" t="s">
         <v>169</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>169</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>0</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" ns3:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>3</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ns3:dyDescent="0.2">
       <c r="A230" t="s">
         <v>6</v>
       </c>
@@ -4664,7 +4664,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" ns3:dyDescent="0.2">
       <c r="A231" t="s">
         <v>7</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" ns3:dyDescent="0.2">
       <c r="A232" t="s">
         <v>9</v>
       </c>
@@ -4680,12 +4680,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" ns3:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>11</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" ns3:dyDescent="0.2">
       <c r="A235" t="s">
         <v>119</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ns3:dyDescent="0.2">
       <c r="A236" t="s">
         <v>59</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>55</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>63</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>37</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>173</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>175</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>112</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" ns3:dyDescent="0.2">
       <c r="A243" t="s">
         <v>127</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ns3:dyDescent="0.2">
       <c r="A244" t="s">
         <v>177</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>179</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>45</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>122</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>181</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>0</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>1</v>
       </c>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" ns3:dyDescent="0.2">
       <c r="A253" t="s">
         <v>3</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>5</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>6</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>7</v>
       </c>
@@ -5038,12 +5038,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A257" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:6" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>11</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="259" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A259" s="3" t="str">
         <f>B251</f>
         <v>market for battery, Li-ion, NMC955</v>
@@ -5085,7 +5085,7 @@
         <v>battery, Li-ion, NMC955</v>
       </c>
     </row>
-    <row r="260" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A260" s="11" t="s">
         <v>289</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:6" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>59</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:6" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>57</v>
       </c>
@@ -5145,7 +5145,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:6" ns3:dyDescent="0.2">
       <c r="A263" t="s">
         <v>266</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:6" ns3:dyDescent="0.2">
       <c r="A264" t="s">
         <v>61</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="266" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A266" s="2" t="s">
         <v>0</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:6" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>1</v>
       </c>
@@ -5201,7 +5201,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:6" ns3:dyDescent="0.2">
       <c r="A268" t="s">
         <v>3</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:6" ns3:dyDescent="0.2">
       <c r="A269" t="s">
         <v>5</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>6</v>
       </c>
@@ -5225,7 +5225,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:6" ns3:dyDescent="0.2">
       <c r="A271" t="s">
         <v>7</v>
       </c>
@@ -5233,12 +5233,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="272" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A272" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:6" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>11</v>
       </c>
@@ -5258,7 +5258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="274" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A274" s="3" t="str">
         <f>B266</f>
         <v>battery production, Li-ion, NMC955</v>
@@ -5280,7 +5280,7 @@
         <v>battery, Li-ion, NMC955</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:6" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>15</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:6" ns3:dyDescent="0.2">
       <c r="A276" t="s">
         <v>277</v>
       </c>
@@ -5320,7 +5320,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:6" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>256</v>
       </c>
@@ -5340,7 +5340,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:6" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>288</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:6" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>41</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:6" ns3:dyDescent="0.2">
       <c r="A280" t="s">
         <v>45</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:6" ns3:dyDescent="0.2">
       <c r="A281" t="s">
         <v>33</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:6" ns3:dyDescent="0.2">
       <c r="A282" t="s">
         <v>24</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:6" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>48</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:6" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:6" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>35</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:6" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>50</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:6" ns3:dyDescent="0.2">
       <c r="A287" t="s">
         <v>37</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:6" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>29</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:6" ns3:dyDescent="0.2">
       <c r="A289" t="s">
         <v>39</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:6" ns3:dyDescent="0.2">
       <c r="A290" t="s">
         <v>43</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:6" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>31</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:6" ns3:dyDescent="0.2">
       <c r="A292" t="s">
         <v>26</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="294" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A294" s="2" t="s">
         <v>0</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:6" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>1</v>
       </c>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:6" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>3</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:6" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>5</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:6" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>7</v>
       </c>
@@ -5690,7 +5690,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:6" ns3:dyDescent="0.2">
       <c r="A300" t="s">
         <v>9</v>
       </c>
@@ -5700,12 +5700,12 @@
         </is>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:6" ns3:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:6" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>11</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>277</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:6" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>112</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:6" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>45</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:6" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>279</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:6" ns3:dyDescent="0.2">
       <c r="A307" t="inlineStr">
         <is>
           <t>anode paste production, silicon-graphite, for Li-ion battery, NMC955</t>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:6" ns3:dyDescent="0.2">
       <c r="A308" t="s">
         <v>116</v>
       </c>
@@ -5849,7 +5849,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:6" ns3:dyDescent="0.2">
       <c r="A309" t="s">
         <v>117</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:6" ns3:dyDescent="0.2">
       <c r="A310" t="s">
         <v>43</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:6" ns3:dyDescent="0.2">
       <c r="A311" t="s">
         <v>41</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:6" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>118</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:6" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>15</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:6" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>39</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:6" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>119</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:6" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>63</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:6" ns3:dyDescent="0.2">
       <c r="A317" t="s">
         <v>85</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:6" ns3:dyDescent="0.2">
       <c r="A318" t="s">
         <v>120</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:6" ns3:dyDescent="0.2">
       <c r="A319" t="s">
         <v>122</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="321" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A321" s="2" t="s">
         <v>0</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:6" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>1</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:6" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>3</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:6" ns3:dyDescent="0.2">
       <c r="A324" t="s">
         <v>5</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:6" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>6</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:6" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>7</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:6" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>9</v>
       </c>
@@ -6125,12 +6125,12 @@
         <v>273</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:6" ns3:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:6" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>11</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:6" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>279</v>
       </c>
@@ -6170,7 +6170,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:6" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>124</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:6" ns3:dyDescent="0.2">
       <c r="A332" t="s">
         <v>55</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:6" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>61</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:6" ns3:dyDescent="0.2">
       <c r="A334" t="s">
         <v>45</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:6" ns3:dyDescent="0.2">
       <c r="A335" t="s">
         <v>125</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:6" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>127</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>112</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>129</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>122</v>
       </c>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="G339" s="5"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>280</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A342" s="2" t="s">
         <v>0</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>1</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>3</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>6</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>7</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>9</v>
       </c>
@@ -6427,12 +6427,12 @@
         <v>281</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" ns3:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>11</v>
       </c>
@@ -6455,7 +6455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" ns3:dyDescent="0.2">
       <c r="A351" t="s">
         <v>280</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" ns3:dyDescent="0.2">
       <c r="A352" t="s">
         <v>124</v>
       </c>
@@ -6495,7 +6495,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>132</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>61</v>
       </c>
@@ -6535,7 +6535,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>55</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>45</v>
       </c>
@@ -6575,7 +6575,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>253</v>
       </c>
@@ -6595,7 +6595,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>282</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:7" ns3:dyDescent="0.2">
       <c r="A359" t="s">
         <v>122</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" ns3:dyDescent="0.2">
       <c r="A360" t="s">
         <v>134</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>137</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A363" s="2" t="s">
         <v>0</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>3</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>5</v>
       </c>
@@ -6701,7 +6701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" ns3:dyDescent="0.2">
       <c r="A367" t="s">
         <v>6</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>7</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="369" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:24" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>9</v>
       </c>
@@ -6725,12 +6725,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="370" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:24" ns3:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="371" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:24" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>11</v>
       </c>
@@ -6753,7 +6753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="372" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:24" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>282</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="373" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:24" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>132</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="374" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:24" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>55</v>
       </c>
@@ -6813,7 +6813,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="375" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:24" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>124</v>
       </c>
@@ -6836,7 +6836,7 @@
       <c r="S375" s="5"/>
       <c r="X375" s="5"/>
     </row>
-    <row r="376" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:24" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>61</v>
       </c>
@@ -6856,7 +6856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="377" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:24" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>112</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="378" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:24" ns3:dyDescent="0.2">
       <c r="A378" t="s">
         <v>141</v>
       </c>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="M378" s="7"/>
     </row>
-    <row r="379" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:24" ns3:dyDescent="0.2">
       <c r="A379" t="s">
         <v>252</v>
       </c>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="M379" s="7"/>
     </row>
-    <row r="380" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:24" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>144</v>
       </c>
@@ -6939,7 +6939,7 @@
       </c>
       <c r="M380" s="7"/>
     </row>
-    <row r="381" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:24" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>146</v>
       </c>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="M381" s="7"/>
     </row>
-    <row r="382" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:24" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>148</v>
       </c>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="N382" s="7"/>
     </row>
-    <row r="383" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:24" ns3:dyDescent="0.2">
       <c r="A383" t="s">
         <v>122</v>
       </c>
@@ -7001,7 +7001,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="384" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:24" ns3:dyDescent="0.2">
       <c r="A384" t="s">
         <v>150</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:7" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>152</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:7" ns3:dyDescent="0.2">
       <c r="A386" t="s">
         <v>153</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A388" s="2" t="s">
         <v>0</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:7" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>1</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:7" ns3:dyDescent="0.2">
       <c r="A390" t="s">
         <v>3</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:7" ns3:dyDescent="0.2">
       <c r="A391" t="s">
         <v>5</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:7" ns3:dyDescent="0.2">
       <c r="A392" t="s">
         <v>6</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:7" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:7" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>9</v>
       </c>
@@ -7111,12 +7111,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:7" ns3:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:7" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>11</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:7" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>161</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:7" ns3:dyDescent="0.2">
       <c r="A398" t="s">
         <v>61</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:7" ns3:dyDescent="0.2">
       <c r="A399" t="s">
         <v>55</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:7" ns3:dyDescent="0.2">
       <c r="A400" t="s">
         <v>59</v>
       </c>
@@ -7219,7 +7219,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>185</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>186</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>45</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>122</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11" ns3:dyDescent="0.2">
       <c r="A405" t="s">
         <v>187</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11" ns3:dyDescent="0.2">
       <c r="A406" t="s">
         <v>190</v>
       </c>
@@ -7339,7 +7339,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11" ns3:dyDescent="0.2">
       <c r="A407" t="s">
         <v>162</v>
       </c>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="K407" s="5"/>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>188</v>
       </c>
@@ -7380,7 +7380,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>188</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>150</v>
       </c>
@@ -7420,7 +7420,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>150</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>150</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>192</v>
       </c>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="K413" s="5"/>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11" ns3:dyDescent="0.2">
       <c r="A414" t="s">
         <v>192</v>
       </c>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="K414" s="5"/>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11" ns3:dyDescent="0.2">
       <c r="A415" t="s">
         <v>194</v>
       </c>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="K415" s="5"/>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11" ns3:dyDescent="0.2">
       <c r="A416" t="s">
         <v>194</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="418" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A418" s="2" t="s">
         <v>0</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>1</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>3</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>5</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>6</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>7</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>205</v>
       </c>
@@ -7599,12 +7599,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="425" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A425" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:6" ns3:dyDescent="0.2">
       <c r="A426" t="s">
         <v>11</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" ns3:dyDescent="0.2">
       <c r="A427" t="s">
         <v>201</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>216</v>
       </c>
@@ -7664,7 +7664,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>217</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>218</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="432" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A432" s="2" t="s">
         <v>0</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>1</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" ns3:dyDescent="0.2">
       <c r="A434" t="s">
         <v>3</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>5</v>
       </c>
@@ -7736,7 +7736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>6</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" ns3:dyDescent="0.2">
       <c r="A437" t="s">
         <v>7</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" ns3:dyDescent="0.2">
       <c r="A438" t="s">
         <v>205</v>
       </c>
@@ -7760,12 +7760,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="439" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A439" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>11</v>
       </c>
@@ -7791,7 +7791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>216</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>220</v>
       </c>
@@ -7834,7 +7834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>171</v>
       </c>
@@ -7857,7 +7857,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>35</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>98</v>
       </c>
@@ -7903,7 +7903,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" ns3:dyDescent="0.2">
       <c r="A446" t="s">
         <v>222</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" ns3:dyDescent="0.2">
       <c r="A447" t="s">
         <v>224</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" ns3:dyDescent="0.2">
       <c r="A448" t="s">
         <v>85</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>120</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>39</v>
       </c>
@@ -8021,7 +8021,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A452" s="2" t="s">
         <v>0</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>1</v>
       </c>
@@ -8037,7 +8037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>3</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" ns3:dyDescent="0.2">
       <c r="A455" t="s">
         <v>5</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>6</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>7</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>205</v>
       </c>
@@ -8077,12 +8077,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A459" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>11</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>217</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>220</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>171</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>39</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A466" s="2" t="s">
         <v>0</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:7" ns3:dyDescent="0.2">
       <c r="A467" t="s">
         <v>1</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" ns3:dyDescent="0.2">
       <c r="A468" t="s">
         <v>3</v>
       </c>
@@ -8218,7 +8218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" ns3:dyDescent="0.2">
       <c r="A469" t="s">
         <v>5</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>6</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>7</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>205</v>
       </c>
@@ -8250,12 +8250,12 @@
         <v>199</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A473" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>11</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" ns3:dyDescent="0.2">
       <c r="A475" t="s">
         <v>218</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" ns3:dyDescent="0.2">
       <c r="A476" t="s">
         <v>41</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>50</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>43</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A480" s="2" t="s">
         <v>0</v>
       </c>
@@ -8375,7 +8375,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>3</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:8" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>5</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:8" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>6</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:8" ns3:dyDescent="0.2">
       <c r="A484" t="s">
         <v>13</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:8" ns3:dyDescent="0.2">
       <c r="A485" t="s">
         <v>7</v>
       </c>
@@ -8415,12 +8415,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A486" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:8" ns3:dyDescent="0.2">
       <c r="A487" t="s">
         <v>11</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:8" ns3:dyDescent="0.2">
       <c r="A488" t="s">
         <v>214</v>
       </c>
@@ -8466,7 +8466,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:8" ns3:dyDescent="0.2">
       <c r="A489" t="s">
         <v>228</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:8" ns3:dyDescent="0.2">
       <c r="A490" t="s">
         <v>153</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:8" ns3:dyDescent="0.2">
       <c r="A491" t="s">
         <v>208</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:8" ns3:dyDescent="0.2">
       <c r="A492" t="s">
         <v>229</v>
       </c>
@@ -8552,7 +8552,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:8" ns3:dyDescent="0.2">
       <c r="A493" t="s">
         <v>231</v>
       </c>
@@ -8575,7 +8575,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:8" ns3:dyDescent="0.2">
       <c r="A494" t="s">
         <v>233</v>
       </c>
@@ -8598,7 +8598,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:8" ns3:dyDescent="0.2">
       <c r="A495" t="s">
         <v>235</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:8" ns3:dyDescent="0.2">
       <c r="A496" t="s">
         <v>237</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:8" ns3:dyDescent="0.2">
       <c r="A497" t="s">
         <v>157</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:8" ns3:dyDescent="0.2">
       <c r="A498" t="s">
         <v>45</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:8" ns3:dyDescent="0.2">
       <c r="A499" t="s">
         <v>239</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:8" ns3:dyDescent="0.2">
       <c r="A500" t="s">
         <v>241</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A502" s="2" t="s">
         <v>0</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:8" ns3:dyDescent="0.2">
       <c r="A503" t="s">
         <v>1</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:8" ns3:dyDescent="0.2">
       <c r="A504" t="s">
         <v>3</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:8" ns3:dyDescent="0.2">
       <c r="A505" t="s">
         <v>5</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A506" t="s">
         <v>6</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:8" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>7</v>
       </c>
@@ -8784,12 +8784,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="508" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A508" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:8" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>11</v>
       </c>
@@ -8809,7 +8809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A510" s="3" t="s">
         <v>267</v>
       </c>
@@ -8829,7 +8829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:8" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>57</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:8" ns3:dyDescent="0.2">
       <c r="A512" t="s">
         <v>52</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" ns3:dyDescent="0.2">
       <c r="A513" t="s">
         <v>59</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" ns3:dyDescent="0.2">
       <c r="A514" t="s">
         <v>266</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" ns3:dyDescent="0.2">
       <c r="A515" t="s">
         <v>61</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="516" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A516" s="3" t="s">
         <v>255</v>
       </c>
@@ -8949,7 +8949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="518" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A518" s="2" t="s">
         <v>0</v>
       </c>
@@ -8957,7 +8957,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:9" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>1</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" ns3:dyDescent="0.2">
       <c r="A520" t="s">
         <v>3</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:9" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>5</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A522" t="s">
         <v>6</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" ns3:dyDescent="0.2">
       <c r="A523" t="s">
         <v>7</v>
       </c>
@@ -8997,7 +8997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" ns3:dyDescent="0.2">
       <c r="A524" t="s">
         <v>9</v>
       </c>
@@ -9005,12 +9005,12 @@
         <v>243</v>
       </c>
     </row>
-    <row r="525" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A525" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" ns3:dyDescent="0.2">
       <c r="A526" t="s">
         <v>11</v>
       </c>
@@ -9039,7 +9039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="527" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A527" s="8" t="s">
         <v>255</v>
       </c>
@@ -9062,7 +9062,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:9" ns3:dyDescent="0.2">
       <c r="A528" t="s">
         <v>196</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" ns3:dyDescent="0.2">
       <c r="A529" t="s">
         <v>244</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:9" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>245</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" ns3:dyDescent="0.2">
       <c r="A531" t="s">
         <v>246</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>247</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>119</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>201</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" ns3:dyDescent="0.2">
       <c r="A535" t="s">
         <v>202</v>
       </c>
@@ -9231,7 +9231,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" ns3:dyDescent="0.2">
       <c r="A536" t="s">
         <v>45</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:9" ns3:dyDescent="0.2">
       <c r="A537" t="s">
         <v>112</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="539" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A539" s="2" t="s">
         <v>0</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" ns3:dyDescent="0.2">
       <c r="A540" t="s">
         <v>1</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" ns3:dyDescent="0.2">
       <c r="A541" t="s">
         <v>3</v>
       </c>
@@ -9301,7 +9301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" ns3:dyDescent="0.2">
       <c r="A542" t="s">
         <v>5</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:9" ns3:dyDescent="0.2">
       <c r="A544" t="s">
         <v>7</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:9" ns3:dyDescent="0.2">
       <c r="A545" t="s">
         <v>9</v>
       </c>
@@ -9333,12 +9333,12 @@
         <v>243</v>
       </c>
     </row>
-    <row r="546" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A546" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:9" ns3:dyDescent="0.2">
       <c r="A547" t="s">
         <v>11</v>
       </c>
@@ -9367,7 +9367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A548" s="8" t="str">
         <f>B539</f>
         <v>market for battery, Li-ion, LTO</v>
@@ -9392,7 +9392,7 @@
         <v>battery, Li-ion, LTO</v>
       </c>
     </row>
-    <row r="549" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A549" s="8" t="s">
         <v>255</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:9" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>265</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:9" ns3:dyDescent="0.2">
       <c r="A551" t="s">
         <v>59</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:9" ns3:dyDescent="0.2">
       <c r="A552" t="s">
         <v>57</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:9" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>266</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:9" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>61</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="556" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:9" ht="16" ns3:dyDescent="0.2">
       <c r="A556" s="2" t="s">
         <v>0</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:9" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>1</v>
       </c>
@@ -9528,7 +9528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:9" ns3:dyDescent="0.2">
       <c r="A558" t="s">
         <v>3</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:9" ns3:dyDescent="0.2">
       <c r="A559" t="s">
         <v>5</v>
       </c>
@@ -9544,7 +9544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:9" ns3:dyDescent="0.2">
       <c r="A560" t="s">
         <v>6</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:7" ns3:dyDescent="0.2">
       <c r="A561" t="s">
         <v>7</v>
       </c>
@@ -9560,7 +9560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:7" ns3:dyDescent="0.2">
       <c r="A562" t="s">
         <v>205</v>
       </c>
@@ -9568,12 +9568,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="563" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A563" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:7" ns3:dyDescent="0.2">
       <c r="A564" t="s">
         <v>11</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:7" ns3:dyDescent="0.2">
       <c r="A565" t="s">
         <v>246</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:7" ns3:dyDescent="0.2">
       <c r="A566" t="s">
         <v>41</v>
       </c>
@@ -9639,7 +9639,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:7" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>43</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="569" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A569" s="2" t="s">
         <v>0</v>
       </c>
@@ -9670,7 +9670,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:7" ns3:dyDescent="0.2">
       <c r="A570" t="s">
         <v>1</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:7" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>3</v>
       </c>
@@ -9686,7 +9686,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:7" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>5</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:7" ns3:dyDescent="0.2">
       <c r="A573" t="s">
         <v>6</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:7" ns3:dyDescent="0.2">
       <c r="A574" t="s">
         <v>7</v>
       </c>
@@ -9710,7 +9710,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:7" ns3:dyDescent="0.2">
       <c r="A575" t="s">
         <v>205</v>
       </c>
@@ -9718,12 +9718,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="576" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A576" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" ns3:dyDescent="0.2">
       <c r="A577" t="s">
         <v>11</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>244</v>
       </c>
@@ -9766,7 +9766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>248</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>125</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" ns3:dyDescent="0.2">
       <c r="A581" t="s">
         <v>155</v>
       </c>
@@ -9835,7 +9835,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" ns3:dyDescent="0.2">
       <c r="A582" t="s">
         <v>287</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" ns3:dyDescent="0.2">
       <c r="A583" t="s">
         <v>127</v>
       </c>
@@ -9881,7 +9881,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" ns3:dyDescent="0.2">
       <c r="A584" t="s">
         <v>208</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="586" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A586" s="2" t="s">
         <v>0</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" ns3:dyDescent="0.2">
       <c r="A587" t="s">
         <v>1</v>
       </c>
@@ -9920,7 +9920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" ns3:dyDescent="0.2">
       <c r="A588" t="s">
         <v>3</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:7" ns3:dyDescent="0.2">
       <c r="A589" t="s">
         <v>5</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>6</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" ns3:dyDescent="0.2">
       <c r="A591" t="s">
         <v>7</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" ns3:dyDescent="0.2">
       <c r="A592" t="s">
         <v>205</v>
       </c>
@@ -9960,12 +9960,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A593" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" ns3:dyDescent="0.2">
       <c r="A594" t="s">
         <v>11</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>245</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:7" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>211</v>
       </c>
@@ -10031,7 +10031,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>39</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A599" s="2" t="s">
         <v>0</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" ns3:dyDescent="0.2">
       <c r="A600" t="s">
         <v>1</v>
       </c>
@@ -10070,7 +10070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" ns3:dyDescent="0.2">
       <c r="A601" t="s">
         <v>3</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>5</v>
       </c>
@@ -10086,7 +10086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:7" ns3:dyDescent="0.2">
       <c r="A603" t="s">
         <v>6</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" ns3:dyDescent="0.2">
       <c r="A604" t="s">
         <v>7</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>205</v>
       </c>
@@ -10110,12 +10110,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A606" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" ns3:dyDescent="0.2">
       <c r="A607" t="s">
         <v>11</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" ns3:dyDescent="0.2">
       <c r="A608" t="s">
         <v>247</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:8" ns3:dyDescent="0.2">
       <c r="A609" t="s">
         <v>162</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:8" ns3:dyDescent="0.2">
       <c r="A610" t="s">
         <v>164</v>
       </c>
@@ -10204,7 +10204,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="612" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A612" s="2" t="s">
         <v>0</v>
       </c>
@@ -10212,7 +10212,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:8" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>5</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:8" ns3:dyDescent="0.2">
       <c r="A614" t="s">
         <v>6</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:8" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>13</v>
       </c>
@@ -10236,7 +10236,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:8" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>7</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:8" ns3:dyDescent="0.2">
       <c r="A617" t="s">
         <v>3</v>
       </c>
@@ -10252,12 +10252,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A618" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="619" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A619" s="2" t="s">
         <v>11</v>
       </c>
@@ -10283,7 +10283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:8" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>248</v>
       </c>
@@ -10306,7 +10306,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:8" ns3:dyDescent="0.2">
       <c r="A621" t="s">
         <v>134</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:8" ns3:dyDescent="0.2">
       <c r="A622" t="s">
         <v>45</v>
       </c>
@@ -10349,7 +10349,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:8" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>253</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:8" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>249</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="626" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A626" s="2" t="s">
         <v>0</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:6" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>1</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:6" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>3</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:6" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>5</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:6" ns3:dyDescent="0.2">
       <c r="A630" t="s">
         <v>6</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:6" ns3:dyDescent="0.2">
       <c r="A631" t="s">
         <v>7</v>
       </c>
@@ -10443,7 +10443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:6" ns3:dyDescent="0.2">
       <c r="A632" t="s">
         <v>9</v>
       </c>
@@ -10451,12 +10451,12 @@
         <v>274</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:6" ns3:dyDescent="0.2">
       <c r="A633" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:6" ns3:dyDescent="0.2">
       <c r="A634" t="s">
         <v>11</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:6" ns3:dyDescent="0.2">
       <c r="A635" t="s">
         <v>196</v>
       </c>
@@ -10496,7 +10496,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:6" ns3:dyDescent="0.2">
       <c r="A636" t="s">
         <v>124</v>
       </c>
@@ -10516,7 +10516,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:6" ns3:dyDescent="0.2">
       <c r="A637" t="s">
         <v>55</v>
       </c>
@@ -10536,7 +10536,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:6" ns3:dyDescent="0.2">
       <c r="A638" t="s">
         <v>61</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:6" ns3:dyDescent="0.2">
       <c r="A639" t="s">
         <v>45</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:6" ns3:dyDescent="0.2">
       <c r="A640" t="s">
         <v>125</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:7" ns3:dyDescent="0.2">
       <c r="A641" t="s">
         <v>127</v>
       </c>
@@ -10616,7 +10616,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:7" ns3:dyDescent="0.2">
       <c r="A642" t="s">
         <v>112</v>
       </c>
@@ -10636,7 +10636,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:7" ns3:dyDescent="0.2">
       <c r="A643" t="s">
         <v>129</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:7" ns3:dyDescent="0.2">
       <c r="A644" t="s">
         <v>122</v>
       </c>
@@ -10677,7 +10677,7 @@
       </c>
       <c r="G644" s="5"/>
     </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:7" ns3:dyDescent="0.2">
       <c r="A645" t="s">
         <v>258</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="647" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A647" s="2" t="s">
         <v>0</v>
       </c>
@@ -10705,15 +10705,17 @@
         <v>258</v>
       </c>
     </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:7" ns3:dyDescent="0.2">
       <c r="A648" t="s">
         <v>1</v>
       </c>
-      <c r="B648" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity). Preserve the original rounded anhydrous LiOH dose, precursor, output and energy boundary. Correct battery-grade monohydrate mass and add its water of crystallisation to the existing air emission. Existing reaction-water baseline is not validated by this change. NCA source includes 0.04 kg oxygen and 0.00024 m3 water; this workbook omits that oxygen and repeats the NMC811 water value. Those inherited reaction discrepancies need a separate correction. No complete reaction or whole-cell validation is claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649" spans="1:7" ns3:dyDescent="0.2">
       <c r="A649" t="s">
         <v>3</v>
       </c>
@@ -10721,7 +10723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:7" ns3:dyDescent="0.2">
       <c r="A650" t="s">
         <v>5</v>
       </c>
@@ -10729,7 +10731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:7" ns3:dyDescent="0.2">
       <c r="A651" t="s">
         <v>6</v>
       </c>
@@ -10737,7 +10739,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:7" ns3:dyDescent="0.2">
       <c r="A652" t="s">
         <v>7</v>
       </c>
@@ -10745,7 +10747,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:7" ns3:dyDescent="0.2">
       <c r="A653" t="s">
         <v>9</v>
       </c>
@@ -10753,12 +10755,12 @@
         <v>274</v>
       </c>
     </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:7" ns3:dyDescent="0.2">
       <c r="A654" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:7" ns3:dyDescent="0.2">
       <c r="A655" t="s">
         <v>11</v>
       </c>
@@ -10780,8 +10782,13 @@
       <c r="G655" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" spans="1:7" ns3:dyDescent="0.2">
       <c r="A656" t="s">
         <v>258</v>
       </c>
@@ -10801,7 +10808,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:7" ns3:dyDescent="0.2">
       <c r="A657" t="s">
         <v>124</v>
       </c>
@@ -10821,7 +10828,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:7" ns3:dyDescent="0.2">
       <c r="A658" t="s">
         <v>132</v>
       </c>
@@ -10841,7 +10848,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:7" ns3:dyDescent="0.2">
       <c r="A659" t="s">
         <v>61</v>
       </c>
@@ -10861,7 +10868,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:7" ns3:dyDescent="0.2">
       <c r="A660" t="s">
         <v>55</v>
       </c>
@@ -10881,7 +10888,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:7" ns3:dyDescent="0.2">
       <c r="A661" t="s">
         <v>45</v>
       </c>
@@ -10901,12 +10908,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:7" ns3:dyDescent="0.2">
       <c r="A662" t="s">
         <v>259</v>
       </c>
       <c r="B662" s="4">
-        <v>0.25</v>
+        <v>0.4380715747275233</v>
       </c>
       <c r="C662" t="s">
         <v>8</v>
@@ -10920,8 +10927,13 @@
       <c r="G662" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: preserve 0.25 kg anhydrous LiOH equivalent per kg oxide; purchase 0.43807157472752328 kg LiOH.H2O = 0.25 * 41.962 / 23.947. Atomic masses Li=6.94, H=1.008, O=15.999 g/mol. No additional yield or excess-lithium factor. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="663" spans="1:7" ns3:dyDescent="0.2">
       <c r="A663" t="s">
         <v>261</v>
       </c>
@@ -10941,7 +10953,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:7" ns3:dyDescent="0.2">
       <c r="A664" t="s">
         <v>122</v>
       </c>
@@ -10961,12 +10973,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:7" ns3:dyDescent="0.2">
       <c r="A665" t="s">
         <v>137</v>
       </c>
       <c r="B665" s="4">
-        <v>1.9562E-4</v>
+        <v>0.0003836915747275233</v>
       </c>
       <c r="C665" t="s">
         <v>138</v>
@@ -10977,11 +10989,16 @@
       <c r="F665" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: retained inherited 0.00019562 m3 reaction-water baseline plus 0.18807157472752328 kg water of crystallisation / 1000 kg/m3. Assume bound water exits to air during calcination through the existing Water flow. This closes the hydration increment only; original reaction-water/oxygen balance remains unresolved. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="666" spans="1:7" ns3:dyDescent="0.2">
       <c r="G666" s="5"/>
     </row>
-    <row r="667" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A667" s="2" t="s">
         <v>0</v>
       </c>
@@ -10989,7 +11006,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:7" ns3:dyDescent="0.2">
       <c r="A668" t="s">
         <v>1</v>
       </c>
@@ -10997,7 +11014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:7" ns3:dyDescent="0.2">
       <c r="A669" t="s">
         <v>3</v>
       </c>
@@ -11005,7 +11022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:7" ns3:dyDescent="0.2">
       <c r="A670" t="s">
         <v>5</v>
       </c>
@@ -11013,7 +11030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:7" ns3:dyDescent="0.2">
       <c r="A671" t="s">
         <v>6</v>
       </c>
@@ -11021,7 +11038,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:7" ns3:dyDescent="0.2">
       <c r="A672" t="s">
         <v>7</v>
       </c>
@@ -11029,7 +11046,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:7" ns3:dyDescent="0.2">
       <c r="A673" t="s">
         <v>9</v>
       </c>
@@ -11037,12 +11054,12 @@
         <v>274</v>
       </c>
     </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:7" ns3:dyDescent="0.2">
       <c r="A674" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:7" ns3:dyDescent="0.2">
       <c r="A675" t="s">
         <v>11</v>
       </c>
@@ -11065,7 +11082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:7" ns3:dyDescent="0.2">
       <c r="A676" t="s">
         <v>261</v>
       </c>
@@ -11085,7 +11102,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:7" ns3:dyDescent="0.2">
       <c r="A677" t="s">
         <v>132</v>
       </c>
@@ -11105,7 +11122,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:7" ns3:dyDescent="0.2">
       <c r="A678" t="s">
         <v>55</v>
       </c>
@@ -11125,7 +11142,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:7" ns3:dyDescent="0.2">
       <c r="A679" t="s">
         <v>124</v>
       </c>
@@ -11145,7 +11162,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:7" ns3:dyDescent="0.2">
       <c r="A680" t="s">
         <v>61</v>
       </c>
@@ -11165,7 +11182,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:7" ns3:dyDescent="0.2">
       <c r="A681" t="s">
         <v>112</v>
       </c>
@@ -11185,7 +11202,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:7" ns3:dyDescent="0.2">
       <c r="A682" t="s">
         <v>141</v>
       </c>
@@ -11205,7 +11222,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:7" ns3:dyDescent="0.2">
       <c r="A683" t="s">
         <v>252</v>
       </c>
@@ -11225,7 +11242,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:7" ns3:dyDescent="0.2">
       <c r="A684" t="s">
         <v>144</v>
       </c>
@@ -11245,7 +11262,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:7" ns3:dyDescent="0.2">
       <c r="A685" t="s">
         <v>262</v>
       </c>
@@ -11265,7 +11282,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:7" ns3:dyDescent="0.2">
       <c r="A686" t="s">
         <v>148</v>
       </c>
@@ -11285,7 +11302,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:7" ns3:dyDescent="0.2">
       <c r="A687" t="s">
         <v>122</v>
       </c>
@@ -11305,7 +11322,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="688" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:7" ns3:dyDescent="0.2">
       <c r="A688" t="s">
         <v>150</v>
       </c>
@@ -11325,7 +11342,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:6" ns3:dyDescent="0.2">
       <c r="A689" t="s">
         <v>152</v>
       </c>
@@ -11342,7 +11359,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:6" ns3:dyDescent="0.2">
       <c r="A690" t="s">
         <v>153</v>
       </c>
@@ -11872,8 +11889,8 @@
     </row>
     <row r="712"/>
   </sheetData>
-  <autoFilter ref="A1:X737" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -9674,8 +9674,10 @@
       <c r="A570" t="s">
         <v>1</v>
       </c>
-      <c r="B570" t="s">
-        <v>2</v>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>APPROVED LTO-PASTE GRAPHITE PRODUCT-BOUNDARY CORRECTION, 2026-10-17. Schmidt et al. (2019), Additional Emissions and Cost from Storing Electricity in Stationary Battery Systems, DOI 10.1021/acs.est.8b05313, original supporting archive es8b05313_si_002.zip, member LCA data results script for ESI/LCI import files/NCA LTO battery import.xlsx. Both original and refined sheets, rows 42:47, list the same six paste-ingredient masses; row 45 explicitly buys market for graphite, battery grade, graphite, battery grade, GLO, not a complete graphite anode. Source graphite is 0.0070205791446 kg per reference paste unit; the six ingredient masses sum to 0.40835198594565897 kg. The existing normalized input 0.0070205791446/0.40835198594565897 = 0.017192469698272154 kg graphite per kg declared LTO paste is retained exactly (within the existing stored rounding). Restore the source GLO battery-grade graphite market in place of the RoW complete graphite-anode market. The latter supplies an electrode including collector foil, binder and electrode manufacturing, not the intended graphite ingredient; the LTO cell already purchases its own separate anode current collector. Existing migrations map the source graphite market to the synthetic battery-grade graphite market for later ecoinvent versions; no runtime mapping, new supplier or custom natural/synthetic supply assumption is added. Preserve all six ingredient quantities, 1 kg paste output, separate collector, cell purchases and lifetime/per-MJ allocations. Source mass agreement is not independent validation of the paste composition, binder loading, manufacturing yields, actual LTO design, cell energy density, cell/BMS split, recycling balance or future assumptions. No wholesale cell/pack renormalization, additional fabrication service or recycling credit is introduced. Upstream trace-metal burdens in graphite supply remain possible; removing the unintended complete-electrode path does not establish a zero-metal graphite supply chain or a quantified system metal correction. No complete scenario rebuild is claimed. Source: https://acs.figshare.com/doi/suppl/10.1021/acs.est.8b05313 . Source archive SHA256: 58097039590e4a92ad744f2615c60848b7f5fc934a61573f3268953ae86075d1. Source XLSX member SHA256: 5ec420d68789fddd6fe6429a78b76b5a776d45e1abc2fb7300c036ebcdeeca78.</t>
+        </is>
       </c>
     </row>
     <row r="571" spans="1:7" ns3:dyDescent="0.2">
@@ -9836,8 +9838,10 @@
       </c>
     </row>
     <row r="582" spans="1:7" ns3:dyDescent="0.2">
-      <c r="A582" t="s">
-        <v>287</v>
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>market for graphite, battery grade</t>
+        </is>
       </c>
       <c r="B582">
         <v>1.7192469698272154E-2</v>
@@ -9845,8 +9849,10 @@
       <c r="C582" t="s">
         <v>207</v>
       </c>
-      <c r="D582" t="s">
-        <v>27</v>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="E582" t="s">
         <v>8</v>
@@ -9854,8 +9860,10 @@
       <c r="F582" t="s">
         <v>16</v>
       </c>
-      <c r="G582" t="s">
-        <v>115</v>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>graphite, battery grade</t>
+        </is>
       </c>
     </row>
     <row r="583" spans="1:7" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1337,16 +1337,20 @@
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>265</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>market for non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:6" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>2</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>APPROVED LTO NON-CELL ASSEMBLY IDENTITY CORRECTION, 2026-10-18. This existing broad inventory contains housing, module packaging, coolant, management electronics, steel, plastic and copper. Its physical product inputs sum to 1.0000000000000002 kg per kg assembly when manufacturing services are excluded. It was named battery management system production, for Li-ion battery, with a market of the corresponding name. Those identities collide with native electronics-only BMS inventories, causing the broad recipes to be skipped at import. LTO then bought 0.25 kg of electronics-only BMS per kg battery instead of its intended 0.25 kg non-cell hardware proxy alongside 0.75 kg cells. Give the existing broad producer and market distinct LTO-proxy names and a consistent reference product; redirect only the LTO non-cell purchase and the renamed market provider. The NMC955 battery keeps its separate 0.02424 kg purchase from the native electronics-only BMS producer under the original identity. No material, energy, service, transport or output quantity changes. The retained non-cell recipe is inherited from the NMC111 reference inventory attributed here to Dai et al. (2019), Batteries 5(2), 48, and Crenna et al. (2021), DOI 10.1016/j.resconrec.2021.105619. It is an explicit proxy, not a measured LTO pack design or a reconstruction of the Schmidt et al. (2019) LTO hardware. The retained 75/25 cell/non-cell split, cell energy density, manufacturing yields, replacement lives and future design assumptions remain unvalidated. The direct nested management-system input is 0.08843810427231934 kg/kg assembly, or 0.022109526068079834 kg/kg LTO battery at the retained 0.25 assembly dose. This is only that direct management path, not the total electronics content: module regulators and other electronic components remain in the recipe. Their potential functional overlap remains unresolved. The correction restores the intended assembly boundary and avoids substituting a complete non-cell fraction with BMS electronics. It does not validate complete component coverage, pack composition, primary/secondary shares, recycling balance or a system metal correction. Preserve the existing supplier mixes and lifetime/per-MJ allocations; no extra scrap, disposal, recovery credit or runtime mapping is introduced. No complete scenario/indicator/dashboard rebuild is claimed. Source context: https://doi.org/10.3390/batteries5020048 ; https://doi.org/10.1016/j.resconrec.2021.105619 ; https://doi.org/10.1021/acs.est.8b05313 .</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:6" ns3:dyDescent="0.2">
@@ -1369,8 +1373,10 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>264</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:6" ns3:dyDescent="0.2">
@@ -1407,11 +1413,15 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" t="s">
-        <v>264</v>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>market for non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1527,11 +1537,15 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="16" ns3:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" t="s">
-        <v>264</v>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly production, for Li-ion battery, LTO proxy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1550,16 +1564,20 @@
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>256</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly production, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:6" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
-      <c r="B20" t="s">
-        <v>2</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>APPROVED LTO NON-CELL ASSEMBLY IDENTITY CORRECTION, 2026-10-18. This existing broad inventory contains housing, module packaging, coolant, management electronics, steel, plastic and copper. Its physical product inputs sum to 1.0000000000000002 kg per kg assembly when manufacturing services are excluded. It was named battery management system production, for Li-ion battery, with a market of the corresponding name. Those identities collide with native electronics-only BMS inventories, causing the broad recipes to be skipped at import. LTO then bought 0.25 kg of electronics-only BMS per kg battery instead of its intended 0.25 kg non-cell hardware proxy alongside 0.75 kg cells. Give the existing broad producer and market distinct LTO-proxy names and a consistent reference product; redirect only the LTO non-cell purchase and the renamed market provider. The NMC955 battery keeps its separate 0.02424 kg purchase from the native electronics-only BMS producer under the original identity. No material, energy, service, transport or output quantity changes. The retained non-cell recipe is inherited from the NMC111 reference inventory attributed here to Dai et al. (2019), Batteries 5(2), 48, and Crenna et al. (2021), DOI 10.1016/j.resconrec.2021.105619. It is an explicit proxy, not a measured LTO pack design or a reconstruction of the Schmidt et al. (2019) LTO hardware. The retained 75/25 cell/non-cell split, cell energy density, manufacturing yields, replacement lives and future design assumptions remain unvalidated. The direct nested management-system input is 0.08843810427231934 kg/kg assembly, or 0.022109526068079834 kg/kg LTO battery at the retained 0.25 assembly dose. This is only that direct management path, not the total electronics content: module regulators and other electronic components remain in the recipe. Their potential functional overlap remains unresolved. The correction restores the intended assembly boundary and avoids substituting a complete non-cell fraction with BMS electronics. It does not validate complete component coverage, pack composition, primary/secondary shares, recycling balance or a system metal correction. Preserve the existing supplier mixes and lifetime/per-MJ allocations; no extra scrap, disposal, recovery credit or runtime mapping is introduced. No complete scenario/indicator/dashboard rebuild is claimed. Source context: https://doi.org/10.3390/batteries5020048 ; https://doi.org/10.1016/j.resconrec.2021.105619 ; https://doi.org/10.1021/acs.est.8b05313 .</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:6" ns3:dyDescent="0.2">
@@ -1582,8 +1600,10 @@
       <c r="A23" t="s">
         <v>6</v>
       </c>
-      <c r="B23" t="s">
-        <v>264</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:6" ns3:dyDescent="0.2">
@@ -1628,8 +1648,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" ns3:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>256</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly production, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
       <c r="B28">
         <v>1</v>
@@ -1643,8 +1665,10 @@
       <c r="E28" t="s">
         <v>14</v>
       </c>
-      <c r="F28" t="s">
-        <v>256</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:6" ns3:dyDescent="0.2">
@@ -9289,8 +9313,12 @@
       <c r="A540" t="s">
         <v>1</v>
       </c>
-      <c r="B540" t="s">
-        <v>271</v>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>APPROVED LTO NON-CELL ASSEMBLY IDENTITY CORRECTION, 2026-10-18. This existing broad inventory contains housing, module packaging, coolant, management electronics, steel, plastic and copper. Its physical product inputs sum to 1.0000000000000002 kg per kg assembly when manufacturing services are excluded. It was named battery management system production, for Li-ion battery, with a market of the corresponding name. Those identities collide with native electronics-only BMS inventories, causing the broad recipes to be skipped at import. LTO then bought 0.25 kg of electronics-only BMS per kg battery instead of its intended 0.25 kg non-cell hardware proxy alongside 0.75 kg cells. Give the existing broad producer and market distinct LTO-proxy names and a consistent reference product; redirect only the LTO non-cell purchase and the renamed market provider. The NMC955 battery keeps its separate 0.02424 kg purchase from the native electronics-only BMS producer under the original identity. No material, energy, service, transport or output quantity changes. The retained non-cell recipe is inherited from the NMC111 reference inventory attributed here to Dai et al. (2019), Batteries 5(2), 48, and Crenna et al. (2021), DOI 10.1016/j.resconrec.2021.105619. It is an explicit proxy, not a measured LTO pack design or a reconstruction of the Schmidt et al. (2019) LTO hardware. The retained 75/25 cell/non-cell split, cell energy density, manufacturing yields, replacement lives and future design assumptions remain unvalidated. The direct nested management-system input is 0.08843810427231934 kg/kg assembly, or 0.022109526068079834 kg/kg LTO battery at the retained 0.25 assembly dose. This is only that direct management path, not the total electronics content: module regulators and other electronic components remain in the recipe. Their potential functional overlap remains unresolved. The correction restores the intended assembly boundary and avoids substituting a complete non-cell fraction with BMS electronics. It does not validate complete component coverage, pack composition, primary/secondary shares, recycling balance or a system metal correction. Preserve the existing supplier mixes and lifetime/per-MJ allocations; no extra scrap, disposal, recovery credit or runtime mapping is introduced. No complete scenario/indicator/dashboard rebuild is claimed. Source context: https://doi.org/10.3390/batteries5020048 ; https://doi.org/10.1016/j.resconrec.2021.105619 ; https://doi.org/10.1021/acs.est.8b05313 .
+PREVIOUS SOURCE NOTES:
+Market structure adapted from ecoinvent's "market for battery, Li-ion, NMC811". Battery inventory source: Additional Emissions and Cost from Storing Electricity in Stationary Battery Systems. Schmidt et al. 2019. https://doi.org/10.1021/acs.est.8b05313. Specific energy at cell, updated LCI, excluding BMS and cooling: 60 Wh/kg cell</t>
+        </is>
       </c>
     </row>
     <row r="541" spans="1:9" ns3:dyDescent="0.2">
@@ -9413,8 +9441,10 @@
       </c>
     </row>
     <row r="550" spans="1:9" ns3:dyDescent="0.2">
-      <c r="A550" t="s">
-        <v>265</v>
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>market for non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
       <c r="B550">
         <v>0.25</v>
@@ -9428,8 +9458,10 @@
       <c r="G550" t="s">
         <v>16</v>
       </c>
-      <c r="I550" t="s">
-        <v>264</v>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>non-cell battery assembly, for Li-ion battery, LTO proxy</t>
+        </is>
       </c>
     </row>
     <row r="551" spans="1:9" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -7091,8 +7091,10 @@
       <c r="A389" t="s">
         <v>1</v>
       </c>
-      <c r="B389" t="s">
-        <v>2</v>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>APPROVED ADDITIVE PRODUCT-METADATA CONSISTENCY CORRECTION, 2026-10-18. The existing activity is named vinyl carbonate; its production exchange and the electrolyte buyer both already specify vinyl carbonate. The activity-level reference product instead said disodium disulphite. Align only that declared reference product with the existing provider/output/consumer label, vinyl carbonate. Retain 1 kg output and the 0.024 kg/kg electrolyte purchase, all process inputs, emissions, waste, supplier geographies, allocations and existing source text. This is metadata consistency, not independent validation of the intended chemical identity, synthesis stoichiometry, reaction/process yields or emissions. The existing source field includes a sulfites reference and a generic chemical LCI methodology citation; it remains unverified provenance for this additive recipe and is retained for traceability, not endorsed as evidence of the intended synthesis. Recover the original chemical-specific source before treating the recipe as validated. The existing inventory label vinyl carbonate is preserved; no substitution or rename to vinylene carbonate or another chemical is implied. No quantities, other product labels, runtime/migrations, native inventories or metal factors change. No full scenario rebuild or quantified system-metal effect is claimed.</t>
+        </is>
       </c>
     </row>
     <row r="390" spans="1:7" ns3:dyDescent="0.2">
@@ -7115,8 +7117,10 @@
       <c r="A392" t="s">
         <v>6</v>
       </c>
-      <c r="B392" t="s">
-        <v>183</v>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>vinyl carbonate</t>
+        </is>
       </c>
     </row>
     <row r="393" spans="1:7" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -6705,8 +6705,10 @@
       <c r="A364" t="s">
         <v>1</v>
       </c>
-      <c r="B364" t="s">
-        <v>2</v>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>APPROVED NMC955 PRECURSOR MOLAR-COMPOSITION CORRECTION, 2026-10-18. The existing source metadata targets NMC 90%-5%-5% chemistry. Former anhydrous sulfate inputs were NiSO4 1.458, CoSO4 0.081 and MnSO4 0.081 kg/kg precursor: a 90/5/5 compound-mass split, which gives Ni/Co/Mn cation mole percentages 89.8951655059211/4.986449042714119/5.118385451364775. Set the nominal cation fractions to Ni=0.90, Co=0.05, Mn=0.05 while retaining the existing combined 1.62 kg sulfate/kg precursor dose. For each salt i, q_i = 1.62*x_i*M_i/sum_j(x_j*M_j). Explicit conventional atomic weights, g/mol: Ni 58.6934, Co 58.933194, Mn 54.938044, S 32.06, O 15.999. Anhydrous molar masses are NiSO4 154.7494, CoSO4 154.989194, MnSO4 150.994044 g/mol. New inputs are NiSO4 1.4596580090875133, CoSO4 0.08121776898080177, MnSO4 0.07912422193168524 kg/kg precursor. Their sum is 1.62 within floating-point precision and their cation mole fractions are 0.90/0.05/0.05. Formula references confirm the anhydrous species and approximate molar masses; their last-digit conventions may differ from the explicit atomic weights used here: https://pubchem.ncbi.nlm.nih.gov/compound/7786-81-4 ; https://webbook.nist.gov/cgi/cbook.cgi?ID=10124-43-3 ; https://pubchem.ncbi.nlm.nih.gov/compound/Manganese-sulphate . Use of pure anhydrous salts is the explicit nominal modelling basis, not evidence of measured industrial purity or hydration. Keep all supplier identities/mixes, the cobalt supplier and its 0.38 kg Co/kg CoSO4 basis, all metal-indicator factors, other inputs/emissions, 1 kg reference output, downstream precursor purchases, cell/pack and lifetime/per-MJ allocations unchanged. The total precursor dose, economic allocation, purity/hydration, conversion yields, sodium/hydrogen/oxygen/sulfur balance, co-products and auxiliary process coefficients remain unvalidated. No new allocation multiplier, generic renormalization, calcination correction, recovery credit or primary/secondary split is introduced. This small nominal-composition repair does not explain the large transport-metal increase or validate a complete physical precursor/cell inventory. No complete scenario rebuild or quantified system-metal effect is claimed. Original source adaptation retained: https://doi.org/10.1016/j.resconrec.2021.105619 .</t>
+        </is>
       </c>
     </row>
     <row r="365" spans="1:7" ns3:dyDescent="0.2">
@@ -6925,8 +6927,8 @@
       <c r="A379" t="s">
         <v>252</v>
       </c>
-      <c r="B379" s="4">
-        <v>8.1000000000000003E-2</v>
+      <c r="B379" s="4" t="n">
+        <v>0.08121776898080177</v>
       </c>
       <c r="C379" t="s">
         <v>8</v>
@@ -6946,8 +6948,8 @@
       <c r="A380" t="s">
         <v>144</v>
       </c>
-      <c r="B380" s="4">
-        <v>1.458</v>
+      <c r="B380" s="4" t="n">
+        <v>1.4596580090875133</v>
       </c>
       <c r="C380" t="s">
         <v>8</v>
@@ -6967,8 +6969,8 @@
       <c r="A381" t="s">
         <v>146</v>
       </c>
-      <c r="B381" s="4">
-        <v>8.1000000000000003E-2</v>
+      <c r="B381" s="4" t="n">
+        <v>0.07912422193168524</v>
       </c>
       <c r="C381" t="s">
         <v>8</v>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X712"/>
+  <dimension ref="A1:X1097"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -11934,6 +11934,7805 @@
       </c>
     </row>
     <row r="712"/>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B716">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. To provide a consistent public LMO cell across all supported database versions, use DaiTable8 BEV ingredient list: detailed masses sum146.26999999999998kg versus printed146.29kg. Adopt detailed component sum; graphite and PVDF use inherited graphite/PVF cross-version proxies. Assume100percent assembly retention and20kWh electricity/kWh-cell (2.6kWh/kg at.13kWh/kg-cell), plus1MJ natural-gas heat/kg. These utilities/yields are engineering assumptions (sensitivity10-60kWh electricity/kWh-cell); source-specific cell formation, solvent recovery and material losses remain gaps. This fallback is not a measured modern LMO factory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+      <c r="B723">
+        <v>1</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>market for lithium manganese oxide</t>
+        </is>
+      </c>
+      <c r="B724">
+        <v>0.40794421275722986</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>lithium manganese oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B725">
+        <v>0.14056197443084706</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B726">
+        <v>0.02748342107062282</v>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>market for polyvinylfluoride</t>
+        </is>
+      </c>
+      <c r="B727">
+        <v>0.030286456552950026</v>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>polyvinylfluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B728">
+        <v>0.1503384152594517</v>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B729">
+        <v>0.07841662678608055</v>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>market for lithium hexafluorophosphate</t>
+        </is>
+      </c>
+      <c r="B730">
+        <v>0.02187735010596842</v>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>lithium hexafluorophosphate</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>market for ethylene carbonate</t>
+        </is>
+      </c>
+      <c r="B731">
+        <v>0.061119846858549265</v>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>ethylene carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>market for dimethyl carbonate</t>
+        </is>
+      </c>
+      <c r="B732">
+        <v>0.061119846858549265</v>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>dimethyl carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B733">
+        <v>0.014767211321528683</v>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B734">
+        <v>0.0034183359540575654</v>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B735">
+        <v>0.002666302044164901</v>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B736">
+        <v>2.6</v>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B737">
+        <v>1</v>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B742">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="B749">
+        <v>1</v>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="B750">
+        <v>0.7497078994157989</v>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B751">
+        <v>0.003149606299212598</v>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B752">
+        <v>0.18150876301752603</v>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B753">
+        <v>0.005080010160020319</v>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B754">
+        <v>0.0006604013208026415</v>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B755">
+        <v>0.00731521463042926</v>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B756">
+        <v>0.02628905257810515</v>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B757">
+        <v>0.02628905257810515</v>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B758">
+        <v>0.003149606299212598</v>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B759">
+        <v>0.18150876301752603</v>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B760">
+        <v>0.00731521463042926</v>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B761">
+        <v>0.005080010160020319</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B766">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+      <c r="B773">
+        <v>1</v>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B774">
+        <v>1</v>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B775">
+        <v>1.12</v>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B776">
+        <v>1.0300000000000002</v>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B777">
+        <v>-6.668</v>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B782">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
+      </c>
+      <c r="B789">
+        <v>1</v>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC111</t>
+        </is>
+      </c>
+      <c r="B790">
+        <v>0.7535548005536679</v>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC111</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B791">
+        <v>0.0032716748458537807</v>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B792">
+        <v>0.18591921479803694</v>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B793">
+        <v>0.005473763684409209</v>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B794">
+        <v>0.0006920850635459921</v>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B795">
+        <v>0.0064175160437901085</v>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B796">
+        <v>0.022335472505347925</v>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B797">
+        <v>0.022335472505347925</v>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B798">
+        <v>0.0032716748458537807</v>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B799">
+        <v>0.18591921479803694</v>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B800">
+        <v>0.0064175160437901085</v>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B801">
+        <v>0.005473763684409209</v>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B806">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+      <c r="B813">
+        <v>1</v>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B814">
+        <v>1</v>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B815">
+        <v>1.12</v>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B816">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B817">
+        <v>-6.548</v>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B822">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
+      </c>
+      <c r="B829">
+        <v>1</v>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+      <c r="B830">
+        <v>0.7412515438452038</v>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC532</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B831">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B832">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B833">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B834">
+        <v>0.0007547687662961438</v>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B835">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B836">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B837">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B838">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B839">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B840">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B841">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B846">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+      <c r="B853">
+        <v>1</v>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B854">
+        <v>1</v>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B855">
+        <v>1.12</v>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B856">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B857">
+        <v>-6.538</v>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B862">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
+      </c>
+      <c r="B869">
+        <v>1</v>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+      <c r="B870">
+        <v>0.7412515438452038</v>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B871">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B872">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B873">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B874">
+        <v>0.0007547687662961438</v>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B875">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B876">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B877">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B878">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B879">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B880">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B881">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B886">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+      <c r="B893">
+        <v>1</v>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B894">
+        <v>1</v>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B895">
+        <v>1.12</v>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B896">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B897">
+        <v>-6.538</v>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B902">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
+      </c>
+      <c r="B909">
+        <v>1</v>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC811</t>
+        </is>
+      </c>
+      <c r="B910">
+        <v>0.7410802611620391</v>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC811</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B911">
+        <v>0.0034953505243025783</v>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B912">
+        <v>0.19415682912352433</v>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B913">
+        <v>0.005737650860647627</v>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B914">
+        <v>0.0007254501088175162</v>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B915">
+        <v>0.0066609509991426485</v>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B916">
+        <v>0.02407175361076304</v>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B917">
+        <v>0.02407175361076304</v>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B918">
+        <v>0.0034953505243025783</v>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B919">
+        <v>0.19415682912352433</v>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B920">
+        <v>0.0066609509991426485</v>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B921">
+        <v>0.005737650860647627</v>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B926">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+      <c r="B933">
+        <v>1</v>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B934">
+        <v>1</v>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B935">
+        <v>1.12</v>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B936">
+        <v>0.9299999999999997</v>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B937">
+        <v>-6.568</v>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B942">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B949">
+        <v>1</v>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-ion, NMC955</t>
+        </is>
+      </c>
+      <c r="B950">
+        <v>0.7412515438452038</v>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC955</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B951">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B952">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B953">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B954">
+        <v>0.0007547687662961438</v>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B955">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B956">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B957">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B958">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B959">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B960">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B961">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B966">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+      <c r="B973">
+        <v>1</v>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B974">
+        <v>1</v>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B975">
+        <v>1.12</v>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B976">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B977">
+        <v>-6.538</v>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B982">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
+      </c>
+      <c r="B989">
+        <v>1</v>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NCA</t>
+        </is>
+      </c>
+      <c r="B990">
+        <v>0.7372339678303014</v>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NCA</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B991">
+        <v>0.0036524548711104874</v>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B992">
+        <v>0.1963194493221887</v>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B993">
+        <v>0.00590011940717848</v>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B994">
+        <v>0.0007726346842733724</v>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B995">
+        <v>0.006462035541195478</v>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B996">
+        <v>0.024829669171876102</v>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B997">
+        <v>0.024829669171876102</v>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B998">
+        <v>0.0036524548711104874</v>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B999">
+        <v>0.1963194493221887</v>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1000">
+        <v>0.006462035541195478</v>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1001">
+        <v>0.00590011940717848</v>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1006">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1013">
+        <v>1</v>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1014">
+        <v>1</v>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1015">
+        <v>1.12</v>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1016">
+        <v>0.9100000000000001</v>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1017">
+        <v>-6.548</v>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1022">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1029">
+        <v>1</v>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+      <c r="B1030">
+        <v>0.7412515438452038</v>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1031">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1032">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1033">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1034">
+        <v>0.0007547687662961438</v>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1035">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1036">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1037">
+        <v>0.02408398517908604</v>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1038">
+        <v>0.0035679978043090432</v>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1039">
+        <v>0.19397557293810894</v>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1040">
+        <v>0.006449842184712501</v>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1041">
+        <v>0.005832304103197475</v>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1046">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1053">
+        <v>1</v>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1054">
+        <v>1</v>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1055">
+        <v>1.12</v>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1056">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1057">
+        <v>-6.538</v>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1062">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1069">
+        <v>1</v>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+      <c r="B1070">
+        <v>0.7776182881446039</v>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1071">
+        <v>0.0024986709197235514</v>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1072">
+        <v>0.17288676236044656</v>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1073">
+        <v>0.0049441786283891545</v>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1074">
+        <v>0.000531632110579479</v>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1075">
+        <v>0.0063264221158958</v>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1076">
+        <v>0.017597022860180757</v>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1077">
+        <v>0.017597022860180757</v>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1078">
+        <v>0.0024986709197235514</v>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1079">
+        <v>0.17288676236044656</v>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1080">
+        <v>0.0063264221158958</v>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1081">
+        <v>0.0049441786283891545</v>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1086">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1093">
+        <v>1</v>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+      <c r="B1094">
+        <v>1</v>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1095">
+        <v>1.12</v>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+      <c r="B1096">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1097">
+        <v>-6.478</v>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -8778,8 +8778,12 @@
       <c r="A503" t="s">
         <v>1</v>
       </c>
-      <c r="B503" t="s">
-        <v>2</v>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+</t>
+        </is>
       </c>
     </row>
     <row r="504" spans="1:8" ns3:dyDescent="0.2">
@@ -8991,8 +8995,12 @@
       <c r="A519" t="s">
         <v>1</v>
       </c>
-      <c r="B519" t="s">
-        <v>257</v>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Source: Additional Emissions and Cost from Storing Electricity in Stationary Battery Systems. Schmidt et al. 2019. https://doi.org/10.1021/acs.est.8b05313. Specific energy at cell, updated LCI, excluding BMS and cooling: 60 Wh/kg cell</t>
+        </is>
       </c>
     </row>
     <row r="520" spans="1:9" ns3:dyDescent="0.2">
@@ -9097,7 +9105,7 @@
         <v>196</v>
       </c>
       <c r="B528" s="6">
-        <v>0.2518019267668084</v>
+        <v>0.25344590054486715</v>
       </c>
       <c r="C528" t="s">
         <v>8</v>
@@ -9120,7 +9128,7 @@
         <v>244</v>
       </c>
       <c r="B529" s="6">
-        <v>0.35001598795342187</v>
+        <v>0.3523011853444236</v>
       </c>
       <c r="C529" t="s">
         <v>8</v>
@@ -9140,7 +9148,7 @@
         <v>245</v>
       </c>
       <c r="B530" s="6">
-        <v>8.3314285714285674E-2</v>
+        <v>0.08385823111935328</v>
       </c>
       <c r="C530" t="s">
         <v>8</v>
@@ -9160,7 +9168,7 @@
         <v>246</v>
       </c>
       <c r="B531" s="6">
-        <v>9.6767999999999937E-2</v>
+        <v>0.09739978251492293</v>
       </c>
       <c r="C531" t="s">
         <v>8</v>
@@ -9180,7 +9188,7 @@
         <v>247</v>
       </c>
       <c r="B532" s="6">
-        <v>8.5714285714285743E-2</v>
+        <v>0.08627390032855284</v>
       </c>
       <c r="C532" t="s">
         <v>8</v>
@@ -9200,7 +9208,7 @@
         <v>119</v>
       </c>
       <c r="B533" s="6">
-        <v>9.4811249781359991E-2</v>
+        <v>0.09543025699273006</v>
       </c>
       <c r="C533" t="s">
         <v>8</v>
@@ -9223,7 +9231,7 @@
         <v>201</v>
       </c>
       <c r="B534" s="6">
-        <v>3.7574264069838326E-2</v>
+        <v>0.03129074315514994</v>
       </c>
       <c r="C534" t="s">
         <v>8</v>
@@ -9321,7 +9329,9 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>APPROVED LTO NON-CELL ASSEMBLY IDENTITY CORRECTION, 2026-10-18. This existing broad inventory contains housing, module packaging, coolant, management electronics, steel, plastic and copper. Its physical product inputs sum to 1.0000000000000002 kg per kg assembly when manufacturing services are excluded. It was named battery management system production, for Li-ion battery, with a market of the corresponding name. Those identities collide with native electronics-only BMS inventories, causing the broad recipes to be skipped at import. LTO then bought 0.25 kg of electronics-only BMS per kg battery instead of its intended 0.25 kg non-cell hardware proxy alongside 0.75 kg cells. Give the existing broad producer and market distinct LTO-proxy names and a consistent reference product; redirect only the LTO non-cell purchase and the renamed market provider. The NMC955 battery keeps its separate 0.02424 kg purchase from the native electronics-only BMS producer under the original identity. No material, energy, service, transport or output quantity changes. The retained non-cell recipe is inherited from the NMC111 reference inventory attributed here to Dai et al. (2019), Batteries 5(2), 48, and Crenna et al. (2021), DOI 10.1016/j.resconrec.2021.105619. It is an explicit proxy, not a measured LTO pack design or a reconstruction of the Schmidt et al. (2019) LTO hardware. The retained 75/25 cell/non-cell split, cell energy density, manufacturing yields, replacement lives and future design assumptions remain unvalidated. The direct nested management-system input is 0.08843810427231934 kg/kg assembly, or 0.022109526068079834 kg/kg LTO battery at the retained 0.25 assembly dose. This is only that direct management path, not the total electronics content: module regulators and other electronic components remain in the recipe. Their potential functional overlap remains unresolved. The correction restores the intended assembly boundary and avoids substituting a complete non-cell fraction with BMS electronics. It does not validate complete component coverage, pack composition, primary/secondary shares, recycling balance or a system metal correction. Preserve the existing supplier mixes and lifetime/per-MJ allocations; no extra scrap, disposal, recovery credit or runtime mapping is introduced. No complete scenario/indicator/dashboard rebuild is claimed. Source context: https://doi.org/10.3390/batteries5020048 ; https://doi.org/10.1016/j.resconrec.2021.105619 ; https://doi.org/10.1021/acs.est.8b05313 .
+          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED LTO NON-CELL ASSEMBLY IDENTITY CORRECTION, 2026-10-18. This existing broad inventory contains housing, module packaging, coolant, management electronics, steel, plastic and copper. Its physical product inputs sum to 1.0000000000000002 kg per kg assembly when manufacturing services are excluded. It was named battery management system production, for Li-ion battery, with a market of the corresponding name. Those identities collide with native electronics-only BMS inventories, causing the broad recipes to be skipped at import. LTO then bought 0.25 kg of electronics-only BMS per kg battery instead of its intended 0.25 kg non-cell hardware proxy alongside 0.75 kg cells. Give the existing broad producer and market distinct LTO-proxy names and a consistent reference product; redirect only the LTO non-cell purchase and the renamed market provider. The NMC955 battery keeps its separate 0.02424 kg purchase from the native electronics-only BMS producer under the original identity. No material, energy, service, transport or output quantity changes. The retained non-cell recipe is inherited from the NMC111 reference inventory attributed here to Dai et al. (2019), Batteries 5(2), 48, and Crenna et al. (2021), DOI 10.1016/j.resconrec.2021.105619. It is an explicit proxy, not a measured LTO pack design or a reconstruction of the Schmidt et al. (2019) LTO hardware. The retained 75/25 cell/non-cell split, cell energy density, manufacturing yields, replacement lives and future design assumptions remain unvalidated. The direct nested management-system input is 0.08843810427231934 kg/kg assembly, or 0.022109526068079834 kg/kg LTO battery at the retained 0.25 assembly dose. This is only that direct management path, not the total electronics content: module regulators and other electronic components remain in the recipe. Their potential functional overlap remains unresolved. The correction restores the intended assembly boundary and avoids substituting a complete non-cell fraction with BMS electronics. It does not validate complete component coverage, pack composition, primary/secondary shares, recycling balance or a system metal correction. Preserve the existing supplier mixes and lifetime/per-MJ allocations; no extra scrap, disposal, recovery credit or runtime mapping is introduced. No complete scenario/indicator/dashboard rebuild is claimed. Source context: https://doi.org/10.3390/batteries5020048 ; https://doi.org/10.1016/j.resconrec.2021.105619 ; https://doi.org/10.1021/acs.est.8b05313 .
 PREVIOUS SOURCE NOTES:
 Market structure adapted from ecoinvent's "market for battery, Li-ion, NMC811". Battery inventory source: Additional Emissions and Cost from Storing Electricity in Stationary Battery Systems. Schmidt et al. 2019. https://doi.org/10.1021/acs.est.8b05313. Specific energy at cell, updated LCI, excluding BMS and cooling: 60 Wh/kg cell</t>
         </is>
@@ -18207,7 +18217,9 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -18728,7 +18740,9 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1097"/>
+  <dimension ref="A1:X1175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -15811,7 +15811,9 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -15897,7 +15899,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC811</t>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
         </is>
       </c>
       <c r="B910">
@@ -15920,7 +15922,7 @@
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NMC811</t>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17417,9 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -17501,7 +17505,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NCA</t>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
         </is>
       </c>
       <c r="B990">
@@ -17524,7 +17528,7 @@
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NCA</t>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
         </is>
       </c>
     </row>
@@ -19744,6 +19748,1749 @@
       <c r="G1097" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1109">
+        <v>1</v>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>market for synthetic graphite, battery grade</t>
+        </is>
+      </c>
+      <c r="B1110">
+        <v>0.92</v>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>synthetic graphite, battery grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>market for carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+      <c r="B1111">
+        <v>0.03</v>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1112">
+        <v>0.01</v>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>market for latex</t>
+        </is>
+      </c>
+      <c r="B1113">
+        <v>0.02</v>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>latex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>market for silicon, metallurgical grade</t>
+        </is>
+      </c>
+      <c r="B1114">
+        <v>0.02</v>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>silicon, metallurgical grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1115">
+        <v>0.96</v>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1116">
+        <v>0.46810728671732227</v>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1117">
+        <v>8.48487394434316</v>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1118">
+        <v>-0.00096</v>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1119">
+        <v>4e-10</v>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="B1131">
+        <v>1</v>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1132">
+        <v>0.21810344190530598</v>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1133">
+        <v>0.16827868095293008</v>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="B1134">
+        <v>0.018198205552528147</v>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1135">
+        <v>0.12428814664305506</v>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1136">
+        <v>0.3772827805438338</v>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1137">
+        <v>0.028397628643084264</v>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B1138">
+        <v>0.0028046446825488345</v>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1139">
+        <v>0.0012340436603214871</v>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1140">
+        <v>0.02841251262985209</v>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>market for copper, anode</t>
+        </is>
+      </c>
+      <c r="B1141">
+        <v>0.03299991478654021</v>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B1142">
+        <v>0.004038688342870322</v>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B1143">
+        <v>0.02841251262985209</v>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="B1144">
+        <v>0.03299991478654021</v>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1145">
+        <v>1.2616436427660642</v>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1146">
+        <v>13.2908528113879</v>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1147">
+        <v>4e-10</v>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="B1159">
+        <v>1</v>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1160">
+        <v>0.23064330385898058</v>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1161">
+        <v>0.14835636017151047</v>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="B1162">
+        <v>0.01844306812767981</v>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1163">
+        <v>0.131661603239638</v>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>cathode, NCA, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1164">
+        <v>0.3738112625059551</v>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>cathode, NCA, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1165">
+        <v>0.02813633158646974</v>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B1166">
+        <v>0.002953787517865653</v>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1167">
+        <v>0.001280609814197233</v>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1168">
+        <v>0.029717008099094836</v>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>market for copper, anode</t>
+        </is>
+      </c>
+      <c r="B1169">
+        <v>0.034996665078608824</v>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B1170">
+        <v>0.004234397332062886</v>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B1171">
+        <v>0.029717008099094836</v>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="B1172">
+        <v>0.034996665078608824</v>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1173">
+        <v>1.3502879072040033</v>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1174">
+        <v>14.2246805827825</v>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1175">
+        <v>4e-10</v>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1175"/>
+  <dimension ref="A1:X1188"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -13124,7 +13124,9 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -13176,6 +13178,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -13206,6 +13213,11 @@
           <t>battery monitoring and central controls, LFP, engineering reference</t>
         </is>
       </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LFP, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -13236,6 +13248,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -13266,6 +13283,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -13296,6 +13318,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -13326,6 +13353,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -13926,7 +13958,9 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -13978,6 +14012,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -14008,6 +14047,11 @@
           <t>battery monitoring and central controls, NMC111, engineering reference</t>
         </is>
       </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -14038,6 +14082,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -14068,6 +14117,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -14098,6 +14152,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -14128,6 +14187,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -14728,7 +14792,9 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -14780,6 +14846,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -14810,6 +14881,11 @@
           <t>battery monitoring and central controls, NMC532, engineering reference</t>
         </is>
       </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -14840,6 +14916,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -14870,6 +14951,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -14900,6 +14986,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -14930,6 +15021,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -15530,7 +15626,9 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -15582,6 +15680,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -15612,6 +15715,11 @@
           <t>battery monitoring and central controls, NMC622, engineering reference</t>
         </is>
       </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -15642,6 +15750,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -15672,6 +15785,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -15702,6 +15820,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -15728,6 +15851,11 @@
         </is>
       </c>
       <c r="G897" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
@@ -16334,7 +16462,9 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -16386,6 +16516,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -16416,6 +16551,11 @@
           <t>battery monitoring and central controls, NMC811, engineering reference</t>
         </is>
       </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -16446,6 +16586,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -16476,6 +16621,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -16506,6 +16656,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -16536,6 +16691,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -17136,7 +17296,9 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -17188,6 +17350,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -17218,6 +17385,11 @@
           <t>battery monitoring and central controls, NMC955, engineering reference</t>
         </is>
       </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -17248,6 +17420,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -17278,6 +17455,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -17308,6 +17490,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -17334,6 +17521,11 @@
         </is>
       </c>
       <c r="G977" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
@@ -17940,7 +18132,9 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -17992,6 +18186,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="1013">
       <c r="A1013" t="inlineStr">
@@ -18022,6 +18221,11 @@
           <t>battery monitoring and central controls, NCA, engineering reference</t>
         </is>
       </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, NCA, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
@@ -18052,6 +18256,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
@@ -18082,6 +18291,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
@@ -18112,6 +18326,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1017">
       <c r="A1017" t="inlineStr">
@@ -18138,6 +18357,11 @@
         </is>
       </c>
       <c r="G1017" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
         <is>
           <t>used Li-ion battery</t>
         </is>
@@ -18744,7 +18968,9 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -18798,6 +19024,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="1053">
       <c r="A1053" t="inlineStr">
@@ -18828,6 +19059,11 @@
           <t>battery monitoring and central controls, LTO, engineering reference</t>
         </is>
       </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LTO, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
@@ -18858,6 +19094,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -18888,6 +19129,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
@@ -18918,6 +19164,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" t="inlineStr">
@@ -18948,6 +19199,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -19548,7 +19804,9 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -19600,6 +19858,11 @@
           <t>comment</t>
         </is>
       </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
     </row>
     <row r="1093">
       <c r="A1093" t="inlineStr">
@@ -19630,6 +19893,11 @@
           <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
         </is>
       </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
@@ -19660,6 +19928,11 @@
           <t>battery central controls and protection, engineering reference</t>
         </is>
       </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>battery central controls and protection, engineering reference</t>
+        </is>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -19690,6 +19963,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
@@ -19720,6 +19998,11 @@
           <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
         </is>
       </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+        </is>
+      </c>
     </row>
     <row r="1097">
       <c r="A1097" t="inlineStr">
@@ -19750,6 +20033,11 @@
           <t>used Li-ion battery</t>
         </is>
       </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
     </row>
     <row r="1100">
       <c r="A1100" t="inlineStr">
@@ -20290,7 +20578,9 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20786,7 @@
     <row r="1136">
       <c r="A1136" t="inlineStr">
         <is>
-          <t>cathode, NMC811, for Li-ion battery</t>
+          <t>market for cathode, NMC811, for Li-ion battery</t>
         </is>
       </c>
       <c r="B1136">
@@ -20504,7 +20794,7 @@
       </c>
       <c r="C1136" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="D1136" t="inlineStr">
@@ -21491,6 +21781,212 @@
       <c r="G1175" t="inlineStr">
         <is>
           <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Existing public Crenna2021 supplemental cathode, ecoinvent3.8 fallback only; superseded by native market identity when present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1187">
+        <v>1</v>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1188">
+        <v>1</v>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>cathode, NMC811, for Li-ion battery</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -13124,7 +13124,9 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -13257,7 +13259,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B775">
@@ -13280,12 +13282,12 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13960,9 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -14091,7 +14095,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B815">
@@ -14114,12 +14118,12 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14796,9 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -14925,7 +14931,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B855">
@@ -14948,12 +14954,12 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15632,9 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -15759,7 +15767,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B895">
@@ -15782,12 +15790,12 @@
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16470,9 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -16595,7 +16605,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B935">
@@ -16618,12 +16628,12 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -17296,7 +17306,9 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -17429,7 +17441,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B975">
@@ -17452,12 +17464,12 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18144,9 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -18265,7 +18279,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B1015">
@@ -18288,12 +18302,12 @@
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -18968,7 +18982,9 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -19103,7 +19119,7 @@
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B1055">
@@ -19126,12 +19142,12 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19820,9 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -19937,7 +19955,7 @@
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="B1095">
@@ -19960,12 +19978,12 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery module control board, engineering material reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1188"/>
+  <dimension ref="A1:X1250"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -13439,7 +13439,9 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -13525,7 +13527,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC111</t>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
         </is>
       </c>
       <c r="B790">
@@ -13548,7 +13550,7 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NMC111</t>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
         </is>
       </c>
     </row>
@@ -22008,6 +22010,1429 @@
         </is>
       </c>
     </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1200">
+        <v>1</v>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>market for synthetic graphite, battery grade</t>
+        </is>
+      </c>
+      <c r="B1201">
+        <v>0.94</v>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>synthetic graphite, battery grade</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>synthetic graphite, battery grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>market for carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+      <c r="B1202">
+        <v>0.03</v>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>carboxymethyl cellulose, powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>market for carbon black</t>
+        </is>
+      </c>
+      <c r="B1203">
+        <v>0.01</v>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>carbon black</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>market for latex</t>
+        </is>
+      </c>
+      <c r="B1204">
+        <v>0.02</v>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>latex</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>latex</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1205">
+        <v>1</v>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1206">
+        <v>0.44058783783783784</v>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1207">
+        <v>7.724380864066159</v>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1208">
+        <v>-0.001</v>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1209">
+        <v>4e-10</v>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1221">
+        <v>1</v>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1222">
+        <v>1</v>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1234">
+        <v>1</v>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1235">
+        <v>0.20368979046664995</v>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1236">
+        <v>0.14625594790884047</v>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="B1237">
+        <v>0.017530678687703482</v>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1238">
+        <v>0.12379998330411553</v>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1239">
+        <v>0.4118582519408965</v>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>cathode, NMC111, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1240">
+        <v>0.03100008347942232</v>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B1241">
+        <v>0.00282243926872026</v>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1242">
+        <v>0.0012680524250772184</v>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1243">
+        <v>0.028299524167292762</v>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>market for copper, anode</t>
+        </is>
+      </c>
+      <c r="B1244">
+        <v>0.033475248351281406</v>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B1245">
+        <v>0.004090491693797479</v>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B1246">
+        <v>0.028299524167292762</v>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="B1247">
+        <v>0.033475248351281406</v>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1248">
+        <v>1.1874731722</v>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1249">
+        <v>12.509500000000001</v>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1250">
+        <v>4e-10</v>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1250"/>
+  <dimension ref="A1:X1264"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -6407,8 +6407,12 @@
       <c r="A343" t="s">
         <v>1</v>
       </c>
-      <c r="B343" t="s">
-        <v>2</v>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+</t>
+        </is>
       </c>
     </row>
     <row r="344" spans="1:7" ns3:dyDescent="0.2">
@@ -6624,7 +6628,7 @@
         <v>282</v>
       </c>
       <c r="B358" s="4">
-        <v>0.94899999999999995</v>
+        <v>0.9494744386829469</v>
       </c>
       <c r="C358" t="s">
         <v>8</v>
@@ -6664,7 +6668,7 @@
         <v>134</v>
       </c>
       <c r="B360" s="4">
-        <v>0.20699999999999999</v>
+        <v>0.2257899500408401</v>
       </c>
       <c r="C360" t="s">
         <v>8</v>
@@ -6681,7 +6685,7 @@
         <v>137</v>
       </c>
       <c r="B361" s="4">
-        <v>1.2504399999999999E-4</v>
+        <v>0.00018485336862849572</v>
       </c>
       <c r="C361" t="s">
         <v>138</v>
@@ -6691,6 +6695,36 @@
       </c>
       <c r="F361" t="s">
         <v>136</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+      <c r="B362">
+        <v>1</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="363" spans="1:7" ht="16" ns3:dyDescent="0.2">
@@ -6707,7 +6741,9 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>APPROVED NMC955 PRECURSOR MOLAR-COMPOSITION CORRECTION, 2026-10-18. The existing source metadata targets NMC 90%-5%-5% chemistry. Former anhydrous sulfate inputs were NiSO4 1.458, CoSO4 0.081 and MnSO4 0.081 kg/kg precursor: a 90/5/5 compound-mass split, which gives Ni/Co/Mn cation mole percentages 89.8951655059211/4.986449042714119/5.118385451364775. Set the nominal cation fractions to Ni=0.90, Co=0.05, Mn=0.05 while retaining the existing combined 1.62 kg sulfate/kg precursor dose. For each salt i, q_i = 1.62*x_i*M_i/sum_j(x_j*M_j). Explicit conventional atomic weights, g/mol: Ni 58.6934, Co 58.933194, Mn 54.938044, S 32.06, O 15.999. Anhydrous molar masses are NiSO4 154.7494, CoSO4 154.989194, MnSO4 150.994044 g/mol. New inputs are NiSO4 1.4596580090875133, CoSO4 0.08121776898080177, MnSO4 0.07912422193168524 kg/kg precursor. Their sum is 1.62 within floating-point precision and their cation mole fractions are 0.90/0.05/0.05. Formula references confirm the anhydrous species and approximate molar masses; their last-digit conventions may differ from the explicit atomic weights used here: https://pubchem.ncbi.nlm.nih.gov/compound/7786-81-4 ; https://webbook.nist.gov/cgi/cbook.cgi?ID=10124-43-3 ; https://pubchem.ncbi.nlm.nih.gov/compound/Manganese-sulphate . Use of pure anhydrous salts is the explicit nominal modelling basis, not evidence of measured industrial purity or hydration. Keep all supplier identities/mixes, the cobalt supplier and its 0.38 kg Co/kg CoSO4 basis, all metal-indicator factors, other inputs/emissions, 1 kg reference output, downstream precursor purchases, cell/pack and lifetime/per-MJ allocations unchanged. The total precursor dose, economic allocation, purity/hydration, conversion yields, sodium/hydrogen/oxygen/sulfur balance, co-products and auxiliary process coefficients remain unvalidated. No new allocation multiplier, generic renormalization, calcination correction, recovery credit or primary/secondary split is introduced. This small nominal-composition repair does not explain the large transport-metal increase or validate a complete physical precursor/cell inventory. No complete scenario rebuild or quantified system-metal effect is claimed. Original source adaptation retained: https://doi.org/10.1016/j.resconrec.2021.105619 .</t>
+          <t>APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED NMC955 PRECURSOR MOLAR-COMPOSITION CORRECTION, 2026-10-18. The existing source metadata targets NMC 90%-5%-5% chemistry. Former anhydrous sulfate inputs were NiSO4 1.458, CoSO4 0.081 and MnSO4 0.081 kg/kg precursor: a 90/5/5 compound-mass split, which gives Ni/Co/Mn cation mole percentages 89.8951655059211/4.986449042714119/5.118385451364775. Set the nominal cation fractions to Ni=0.90, Co=0.05, Mn=0.05 while retaining the existing combined 1.62 kg sulfate/kg precursor dose. For each salt i, q_i = 1.62*x_i*M_i/sum_j(x_j*M_j). Explicit conventional atomic weights, g/mol: Ni 58.6934, Co 58.933194, Mn 54.938044, S 32.06, O 15.999. Anhydrous molar masses are NiSO4 154.7494, CoSO4 154.989194, MnSO4 150.994044 g/mol. New inputs are NiSO4 1.4596580090875133, CoSO4 0.08121776898080177, MnSO4 0.07912422193168524 kg/kg precursor. Their sum is 1.62 within floating-point precision and their cation mole fractions are 0.90/0.05/0.05. Formula references confirm the anhydrous species and approximate molar masses; their last-digit conventions may differ from the explicit atomic weights used here: https://pubchem.ncbi.nlm.nih.gov/compound/7786-81-4 ; https://webbook.nist.gov/cgi/cbook.cgi?ID=10124-43-3 ; https://pubchem.ncbi.nlm.nih.gov/compound/Manganese-sulphate . Use of pure anhydrous salts is the explicit nominal modelling basis, not evidence of measured industrial purity or hydration. Keep all supplier identities/mixes, the cobalt supplier and its 0.38 kg Co/kg CoSO4 basis, all metal-indicator factors, other inputs/emissions, 1 kg reference output, downstream precursor purchases, cell/pack and lifetime/per-MJ allocations unchanged. The total precursor dose, economic allocation, purity/hydration, conversion yields, sodium/hydrogen/oxygen/sulfur balance, co-products and auxiliary process coefficients remain unvalidated. No new allocation multiplier, generic renormalization, calcination correction, recovery credit or primary/secondary split is introduced. This small nominal-composition repair does not explain the large transport-metal increase or validate a complete physical precursor/cell inventory. No complete scenario rebuild or quantified system-metal effect is claimed. Original source adaptation retained: https://doi.org/10.1016/j.resconrec.2021.105619 .</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6943,7 @@
         <v>141</v>
       </c>
       <c r="B378" s="4">
-        <v>0.86360624003470599</v>
+        <v>0.8644994750708028</v>
       </c>
       <c r="C378" t="s">
         <v>8</v>
@@ -6928,7 +6964,7 @@
         <v>252</v>
       </c>
       <c r="B379" s="4" t="n">
-        <v>0.08121776898080177</v>
+        <v>0.08374931229860999</v>
       </c>
       <c r="C379" t="s">
         <v>8</v>
@@ -6949,7 +6985,7 @@
         <v>144</v>
       </c>
       <c r="B380" s="4" t="n">
-        <v>1.4596580090875133</v>
+        <v>1.5051552878919114</v>
       </c>
       <c r="C380" t="s">
         <v>8</v>
@@ -6970,7 +7006,7 @@
         <v>146</v>
       </c>
       <c r="B381" s="4" t="n">
-        <v>0.07912422193168524</v>
+        <v>0.08159050976280359</v>
       </c>
       <c r="C381" t="s">
         <v>8</v>
@@ -7032,7 +7068,7 @@
         <v>150</v>
       </c>
       <c r="B384" s="4">
-        <v>-6.1963397318955398E-4</v>
+        <v>-0.003019128033284485</v>
       </c>
       <c r="C384" t="s">
         <v>138</v>
@@ -23433,6 +23469,247 @@
         </is>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+      <c r="B1262">
+        <v>1</v>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B1263">
+        <v>0.08208351497883162</v>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1264">
+        <v>-0.0039146349924426005</v>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1264"/>
+  <dimension ref="A1:X1305"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -14313,7 +14313,9 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t>APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14401,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>market for battery cell, Li-ion, NMC532</t>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
         </is>
       </c>
       <c r="B830">
@@ -14422,7 +14424,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>battery cell, Li-ion, NMC532</t>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
         </is>
       </c>
     </row>
@@ -23710,6 +23712,943 @@
         </is>
       </c>
     </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1276">
+        <v>1</v>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1277">
+        <v>1</v>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+      <c r="B1289">
+        <v>1</v>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1290">
+        <v>0.20368979046664995</v>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1291">
+        <v>0.14625594790884047</v>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>electrolyte, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="B1292">
+        <v>0.017530678687703482</v>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>battery separator</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1293">
+        <v>0.12379998330411553</v>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>copper collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>market for cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1294">
+        <v>0.4118582519408965</v>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>cathode, NMC532, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1295">
+        <v>0.03100008347942232</v>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>aluminium collector foil, for Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B1296">
+        <v>0.00282243926872026</v>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>market for polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="B1297">
+        <v>0.0012680524250772184</v>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>polypropylene, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1298">
+        <v>0.028299524167292762</v>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>market for copper, anode</t>
+        </is>
+      </c>
+      <c r="B1299">
+        <v>0.033475248351281406</v>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>copper, anode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>market for extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="B1300">
+        <v>0.004090491693797479</v>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>extrusion, plastic film</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="B1301">
+        <v>0.028299524167292762</v>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>sheet rolling, aluminium</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>market for sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="B1302">
+        <v>0.033475248351281406</v>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>sheet rolling, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1303">
+        <v>1.1874731722</v>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1304">
+        <v>12.509500000000001</v>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1305">
+        <v>4e-10</v>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -5678,7 +5678,9 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Anode boundary correction: 0.2 kg dry silicon-graphite paste plus 0.12 kg separate copper collector foil per nominal kg cell. Dry paste contains 85.54% synthetic graphite, 8.46% silicon and 6% additives/binders. The prior complete-anode supplier embedded collector foil in the paste input. Remaining cell exchanges are preserved. Retained material inputs sum to 0.9919 kg/kg nominal cell; the 0.0081 kg source rounding/coverage gap is not filled with an assumed material. This boundary/composition correction does not validate practical energy density, first-cycle losses or lifetime.</t>
+          <t>APPROVED NMC955 SOURCE-PRECISION CELL PARTS, issue 46, 2026-10-18. Crenna et al. 2021 DOI 10.1016/j.resconrec.2021.105619, public SI NMC111 J79:J99. Existing NMC955 is an engineering chemistry adaptation of this cell geometry. The existing corrected dry anode already implements the approved 9% substitution of the 94% graphite/silicon pool: 85.54% graphite and 8.46% silicon of dry paste. Preserve that recipe and the earlier NMC955 precursor/calcination correction. Resolve the 0.9919 kg retained-material sum by consistently transferring the original component table at source precision, not adding 0.0081 kg of an arbitrary balancing material. All historical adapted cell fractions were rounded or copied from incompatible anode aggregates. Use source dry-paste, cathode-paste, electrolyte, separator, Cu/Al collectors, case and terminals together; source column J explicitly adjusts cathode paste and Al foil. This changes the adapted NMC955 active-material amounts slightly as part of the documented geometry reference; it is not an independently measured Ni90 cell recipe. Extrusion, terminal rolling, assembly electricity and heat use corresponding source quantities and are not counted as extra retained material. Final cell retained sum is one kg at an explicit 100% assembly-retention reference; upstream manufacturing yields remain in suppliers. Source plant coefficient retained. Existing pack cell share, 0.34 kWh/kg baseline and future density learning remain unchanged and unvalidated against this geometry. Practical voltage/capacity, first-cycle silicon lithium loss, swelling, N/P and ageing remain gaps; one-kg closure is not proof of usable energy. No new lithium compensation is guessed, no recovery credits and no second cell disposal on top of complete-pack end-of-life.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Anode boundary correction: 0.2 kg dry silicon-graphite paste plus 0.12 kg separate copper collector foil per nominal kg cell. Dry paste contains 85.54% synthetic graphite, 8.46% silicon and 6% additives/binders. The prior complete-anode supplier embedded collector foil in the paste input. Remaining cell exchanges are preserved. Retained material inputs sum to 0.9919 kg/kg nominal cell; the 0.0081 kg source rounding/coverage gap is not filled with an assumed material. This boundary/composition correction does not validate practical energy density, first-cycle losses or lifetime.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5776,7 @@
         <v>112</v>
       </c>
       <c r="B304" s="4">
-        <v>12.51</v>
+        <v>12.509500000000001</v>
       </c>
       <c r="C304" t="s">
         <v>113</v>
@@ -5794,7 +5796,7 @@
         <v>45</v>
       </c>
       <c r="B305" s="4">
-        <v>1.1875</v>
+        <v>1.1874731722</v>
       </c>
       <c r="C305" t="s">
         <v>46</v>
@@ -5814,7 +5816,7 @@
         <v>279</v>
       </c>
       <c r="B306" s="4">
-        <v>0.41</v>
+        <v>0.4118582519408965</v>
       </c>
       <c r="C306" t="s">
         <v>8</v>
@@ -5836,7 +5838,7 @@
         </is>
       </c>
       <c r="B307" s="4">
-        <v>0.2</v>
+        <v>0.20368979046664995</v>
       </c>
       <c r="C307" t="s">
         <v>8</v>
@@ -5858,7 +5860,7 @@
         <v>116</v>
       </c>
       <c r="B308" s="4">
-        <v>0.14599999999999999</v>
+        <v>0.14625594790884047</v>
       </c>
       <c r="C308" t="s">
         <v>8</v>
@@ -5878,7 +5880,7 @@
         <v>117</v>
       </c>
       <c r="B309" s="4">
-        <v>0.12</v>
+        <v>0.12379998330411553</v>
       </c>
       <c r="C309" t="s">
         <v>8</v>
@@ -5898,7 +5900,7 @@
         <v>43</v>
       </c>
       <c r="B310" s="4">
-        <v>3.3500000000000002E-2</v>
+        <v>0.033475248351281406</v>
       </c>
       <c r="C310" t="s">
         <v>8</v>
@@ -5918,7 +5920,7 @@
         <v>41</v>
       </c>
       <c r="B311" s="4">
-        <v>3.3500000000000002E-2</v>
+        <v>0.033475248351281406</v>
       </c>
       <c r="C311" t="s">
         <v>8</v>
@@ -5938,7 +5940,7 @@
         <v>118</v>
       </c>
       <c r="B312" s="4">
-        <v>0.03</v>
+        <v>0.03100008347942232</v>
       </c>
       <c r="C312" t="s">
         <v>8</v>
@@ -5958,7 +5960,7 @@
         <v>15</v>
       </c>
       <c r="B313" s="4">
-        <v>2.8299999999999999E-2</v>
+        <v>0.028299524167292762</v>
       </c>
       <c r="C313" t="s">
         <v>8</v>
@@ -5978,7 +5980,7 @@
         <v>39</v>
       </c>
       <c r="B314" s="4">
-        <v>2.8299999999999999E-2</v>
+        <v>0.028299524167292762</v>
       </c>
       <c r="C314" t="s">
         <v>8</v>
@@ -5998,7 +6000,7 @@
         <v>119</v>
       </c>
       <c r="B315" s="4">
-        <v>0.02</v>
+        <v>0.017530678687703482</v>
       </c>
       <c r="C315" t="s">
         <v>8</v>
@@ -6018,7 +6020,7 @@
         <v>63</v>
       </c>
       <c r="B316" s="4">
-        <v>4.1000000000000003E-3</v>
+        <v>0.004090491693797479</v>
       </c>
       <c r="C316" t="s">
         <v>8</v>
@@ -6038,7 +6040,7 @@
         <v>85</v>
       </c>
       <c r="B317" s="4">
-        <v>2.8E-3</v>
+        <v>0.00282243926872026</v>
       </c>
       <c r="C317" t="s">
         <v>8</v>
@@ -6058,7 +6060,7 @@
         <v>120</v>
       </c>
       <c r="B318" s="4">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0012680524250772184</v>
       </c>
       <c r="C318" t="s">
         <v>8</v>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1305"/>
+  <dimension ref="A1:X1319"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -10805,7 +10805,9 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Hydrate-basis correction v1. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity). Preserve the original rounded anhydrous LiOH dose, precursor, output and energy boundary. Correct battery-grade monohydrate mass and add its water of crystallisation to the existing air emission. Existing reaction-water baseline is not validated by this change. NCA source includes 0.04 kg oxygen and 0.00024 m3 water; this workbook omits that oxygen and repeats the NMC811 water value. Those inherited reaction discrepancies need a separate correction. No complete reaction or whole-cell validation is claimed.</t>
+          <t>APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Hydrate-basis correction v1. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity). Preserve the original rounded anhydrous LiOH dose, precursor, output and energy boundary. Correct battery-grade monohydrate mass and add its water of crystallisation to the existing air emission. Existing reaction-water baseline is not validated by this change. NCA source includes 0.04 kg oxygen and 0.00024 m3 water; this workbook omits that oxygen and repeats the NMC811 water value. Those inherited reaction discrepancies need a separate correction. No complete reaction or whole-cell validation is claimed.</t>
         </is>
       </c>
     </row>
@@ -11032,7 +11034,7 @@
         <v>261</v>
       </c>
       <c r="B663" s="4">
-        <v>0.95</v>
+        <v>0.9576022616511578</v>
       </c>
       <c r="C663" t="s">
         <v>8</v>
@@ -11072,7 +11074,7 @@
         <v>137</v>
       </c>
       <c r="B665" s="4">
-        <v>0.0003836915747275233</v>
+        <v>0.00047400378931160514</v>
       </c>
       <c r="C665" t="s">
         <v>138</v>
@@ -11090,7 +11092,34 @@
       </c>
     </row>
     <row r="666" spans="1:7" ns3:dyDescent="0.2">
-      <c r="G666" s="5"/>
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+      <c r="B666">
+        <v>1</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G666" s="5" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
     </row>
     <row r="667" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A667" s="2" t="s">
@@ -11104,8 +11133,12 @@
       <c r="A668" t="s">
         <v>1</v>
       </c>
-      <c r="B668" t="s">
-        <v>2</v>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+</t>
+        </is>
       </c>
     </row>
     <row r="669" spans="1:7" ns3:dyDescent="0.2">
@@ -11301,7 +11334,7 @@
         <v>141</v>
       </c>
       <c r="B682" s="4">
-        <v>0.85814000000000001</v>
+        <v>0.8911536465998793</v>
       </c>
       <c r="C682" t="s">
         <v>8</v>
@@ -11321,7 +11354,7 @@
         <v>252</v>
       </c>
       <c r="B683" s="4">
-        <v>0.25081999999999999</v>
+        <v>0.2526774547465847</v>
       </c>
       <c r="C683" t="s">
         <v>8</v>
@@ -11341,7 +11374,7 @@
         <v>144</v>
       </c>
       <c r="B684" s="4">
-        <v>1.3120000000000001</v>
+        <v>1.345528110923179</v>
       </c>
       <c r="C684" t="s">
         <v>8</v>
@@ -11361,7 +11394,7 @@
         <v>262</v>
       </c>
       <c r="B685" s="4">
-        <v>8.6822999999999997E-2</v>
+        <v>0.09296219034692595</v>
       </c>
       <c r="C685" t="s">
         <v>8</v>
@@ -11421,7 +11454,7 @@
         <v>150</v>
       </c>
       <c r="B688" s="4">
-        <v>-6.1963397318955398E-4</v>
+        <v>-0.0030931483224060025</v>
       </c>
       <c r="C688" t="s">
         <v>138</v>
@@ -24651,6 +24684,247 @@
         </is>
       </c>
     </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+      <c r="B1317">
+        <v>1</v>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B1318">
+        <v>0.07909434353110459</v>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1319">
+        <v>-0.0007643905981805525</v>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -10323,11 +10323,15 @@
       </c>
     </row>
     <row r="615" spans="1:8" ns3:dyDescent="0.2">
-      <c r="A615" t="s">
-        <v>13</v>
-      </c>
-      <c r="B615" t="s">
-        <v>227</v>
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>APPROVED LTO ACTIVE-MATERIAL FEED AND RESIDUE ACCOUNTING, issue 53, 2026-10-18. Existing Crenna2021 LTO route; physical reaction 2Li2CO3+5TiO2 -&gt; Li4Ti5O12+2CO2. Original experimental support for retaining a lithium-excess allowance: Scientific Reports 2019 DOI 10.1038/s41598-019-41206-0, https://pmc.ncbi.nlm.nih.gov/articles/PMC6423044/ , experimental section reports 5% excess Li2CO3; its carbon-reduced product is NOT substituted for stoichiometric LTO here. Preserve current 0.338kg battery-grade lithium carbonate and 0.87kg TiO2 per kg nominal Li4Ti5O12. Their approximately 5% Li excess is compatible with a published processing allowance, so it is not deleted as a proven overcount. Adopt explicit reference 100% reaction of the stoichiometric portion and collection of excess Li2CO3/TiO2 as mixed solid residue; this is a mass-conserving engineering fate assumption, NOT evidence that the source plant collects all excess rather than volatilizing Li or retaining impurity phases. Real lithium volatilization species, capture, TiO2 assay and residual phases require validation. Pure anhydrous carbonate and stoichiometric TiO2/LTO are nominal formulas, not manufacturer assays. Update carbonate-derived CO2 to exact reaction mass and treat both excess portions once through the existing hazardous-waste-incineration proxy; inorganic-lithium treatment is unresolved and no recovery or secondary credit is added. Keep 2.88kWh manufacture, downstream electrode/cell amounts, 60Wh/kg cell reference, pack density learning and vehicle lifetime energy unchanged. Balance atoms and mass at the declared foreground boundary, not all economically allocated upstream supplies. Sensitivity: source Li allowance 0-5%, purity/yield and collected-versus-volatilized loss; these are not automatic numerical reductions. Reference coefficients: {"formula_mass_g_per_mol":459.08299999999997,"Li2CO3_feed_kg":0.338,"TiO2_feed_kg":0.87,"stoichiometric_Li2CO3_kg":0.3218938623299055,"stoichiometric_TiO2_kg":0.8698318169045685,"Li2CO3_excess_kg":0.0161061376700945,"TiO2_excess_kg":0.00016818309543153998,"CO2_kg":0.19172567923447395,"relative_Li_feed_excess":0.05003555381117362}</t>
+        </is>
       </c>
     </row>
     <row r="616" spans="1:8" ns3:dyDescent="0.2">
@@ -10405,7 +10409,7 @@
         <v>134</v>
       </c>
       <c r="B621">
-        <v>0.192</v>
+        <v>0.19172567923447395</v>
       </c>
       <c r="C621" t="s">
         <v>8</v>
@@ -10487,6 +10491,36 @@
       </c>
       <c r="H624" t="s">
         <v>250</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B625">
+        <v>-0.01627432076552604</v>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
       </c>
     </row>
     <row r="626" spans="1:6" ht="16" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1319"/>
+  <dimension ref="A1:X1345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -3668,8 +3668,12 @@
       <c r="A160" t="s">
         <v>1</v>
       </c>
-      <c r="B160" t="s">
-        <v>2</v>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED VINYLENE-CARBONATE REACTION REFERENCE, issue47, 2026-10-18. Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive. The intended cyclic unsaturated battery additive is VINYLENE carbonate, not a sulfite or an unspecified vinyl carbonate ester. Correct active electrolyte link to a uniquely named VC supplier, retaining0.024kg/kg electrolyte. Existing vinyl carbonate name becomes a compatibility alias purchasing the same new VC once; its old chemically unbalanced inputs are disabled. Patent Example1 uses0.420mol chloroethylene carbonate,84mlEC solvent and0.630molTEA near60C; Example3 yields73.3%purified VC. Adopt that isolated yield, but explicitly assume100%selective initial UV chlorination and complete chemical dehydrochlorination, with unrecovered VC collected as same-composition organic/polymer residue. Those reaction-versus-isolation splits are engineering assumptions, not measured process selectivities. Reactions: EC+Cl2 -&gt; chloroEC+HCl; chloroEC+TEA -&gt; VC+TEA.HCl. One HCl is captured from chlorination; the other is bound in amine salt. Assume95%recovery of unreacted0.5molTEA/molCEC, and95%ECsolvent recovery, with solvent density1320kg/m3 assumed at process temperature. Buy net make-up only; internally recycled material receives no avoided-production credit. Remaining amine and solvent go once to hazardous organic waste; do not send TEA.HCl to inert landfill. Acid/amine salt collected in wastewater, not vented as unbalanced chlorine:30wt%HCl capture plus wash water equal salt mass, wastewater density1000kg/m3 assumed. Generic wastewater cannot certify chloride or amine-specific fate. Nitrogen0.019kg/kg remains original inert-gas utility, venting/direct species unresolved. Retain original aggregate0.416kWh+2.35MJ, factory and freight as unvalidated utility/delivery proxies; UV lamp, cooling, solvent distillation and high-purity drying energy are not independently measured. Plant corrosion alloys and auxiliary equipment remain unquantified critical-metal coverage gaps. This is a mass/atom-consistent declared engineering reference, not a recovered manufacturer LCI or proof of industrial electrolyte purity. No new catalyst metals or commercial-grade purity claims. Sensitivity:59-85%isolation,90-99%amine/solvent recovery, nonselective chlorination and process utilities. Source assumptions and numeric mass budget: {"CAS":"872-36-6","formula":"C3H2O3","isolated_yield_from_CEC":0.733,"ethylene_carbonate_reactant_kg":1.3962200934498092,"chlorine_kg":1.124117151842923,"triethylamine_gross_kg":2.406617495340781,"triethylamine_recovered_internal_kg":0.7620955401912473,"triethylamine_net_kg":1.6445219551495338,"EC_solvent_circulation_kg":4.185711256509614,"EC_solvent_makeup_kg":0.20928556282548072,"TEA_HCl_in_effluent_kg":2.182452046097746,"HCl_in_effluent_kg":0.5780403825372256,"water_for_capture_and_washing_kg":3.5312129386846056,"effluent_kg":6.291705367319578,"organic_waste_kg":0.6136523346327748}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+</t>
+        </is>
       </c>
     </row>
     <row r="161" spans="1:7" ns3:dyDescent="0.2">
@@ -3801,8 +3805,10 @@
       </c>
     </row>
     <row r="171" spans="1:7" ns3:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>161</v>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
       </c>
       <c r="B171">
         <v>2.4E-2</v>
@@ -3816,8 +3822,10 @@
       <c r="F171" t="s">
         <v>16</v>
       </c>
-      <c r="G171" t="s">
-        <v>161</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="172" spans="1:7" ns3:dyDescent="0.2">
@@ -7133,7 +7141,9 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>APPROVED ADDITIVE PRODUCT-METADATA CONSISTENCY CORRECTION, 2026-10-18. The existing activity is named vinyl carbonate; its production exchange and the electrolyte buyer both already specify vinyl carbonate. The activity-level reference product instead said disodium disulphite. Align only that declared reference product with the existing provider/output/consumer label, vinyl carbonate. Retain 1 kg output and the 0.024 kg/kg electrolyte purchase, all process inputs, emissions, waste, supplier geographies, allocations and existing source text. This is metadata consistency, not independent validation of the intended chemical identity, synthesis stoichiometry, reaction/process yields or emissions. The existing source field includes a sulfites reference and a generic chemical LCI methodology citation; it remains unverified provenance for this additive recipe and is retained for traceability, not endorsed as evidence of the intended synthesis. Recover the original chemical-specific source before treating the recipe as validated. The existing inventory label vinyl carbonate is preserved; no substitution or rename to vinylene carbonate or another chemical is implied. No quantities, other product labels, runtime/migrations, native inventories or metal factors change. No full scenario rebuild or quantified system-metal effect is claimed.</t>
+          <t>APPROVED VINYLENE-CARBONATE REACTION REFERENCE, issue47, 2026-10-18. Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive. The intended cyclic unsaturated battery additive is VINYLENE carbonate, not a sulfite or an unspecified vinyl carbonate ester. Correct active electrolyte link to a uniquely named VC supplier, retaining0.024kg/kg electrolyte. Existing vinyl carbonate name becomes a compatibility alias purchasing the same new VC once; its old chemically unbalanced inputs are disabled. Patent Example1 uses0.420mol chloroethylene carbonate,84mlEC solvent and0.630molTEA near60C; Example3 yields73.3%purified VC. Adopt that isolated yield, but explicitly assume100%selective initial UV chlorination and complete chemical dehydrochlorination, with unrecovered VC collected as same-composition organic/polymer residue. Those reaction-versus-isolation splits are engineering assumptions, not measured process selectivities. Reactions: EC+Cl2 -&gt; chloroEC+HCl; chloroEC+TEA -&gt; VC+TEA.HCl. One HCl is captured from chlorination; the other is bound in amine salt. Assume95%recovery of unreacted0.5molTEA/molCEC, and95%ECsolvent recovery, with solvent density1320kg/m3 assumed at process temperature. Buy net make-up only; internally recycled material receives no avoided-production credit. Remaining amine and solvent go once to hazardous organic waste; do not send TEA.HCl to inert landfill. Acid/amine salt collected in wastewater, not vented as unbalanced chlorine:30wt%HCl capture plus wash water equal salt mass, wastewater density1000kg/m3 assumed. Generic wastewater cannot certify chloride or amine-specific fate. Nitrogen0.019kg/kg remains original inert-gas utility, venting/direct species unresolved. Retain original aggregate0.416kWh+2.35MJ, factory and freight as unvalidated utility/delivery proxies; UV lamp, cooling, solvent distillation and high-purity drying energy are not independently measured. Plant corrosion alloys and auxiliary equipment remain unquantified critical-metal coverage gaps. This is a mass/atom-consistent declared engineering reference, not a recovered manufacturer LCI or proof of industrial electrolyte purity. No new catalyst metals or commercial-grade purity claims. Sensitivity:59-85%isolation,90-99%amine/solvent recovery, nonselective chlorination and process utilities. Source assumptions and numeric mass budget: {"CAS":"872-36-6","formula":"C3H2O3","isolated_yield_from_CEC":0.733,"ethylene_carbonate_reactant_kg":1.3962200934498092,"chlorine_kg":1.124117151842923,"triethylamine_gross_kg":2.406617495340781,"triethylamine_recovered_internal_kg":0.7620955401912473,"triethylamine_net_kg":1.6445219551495338,"EC_solvent_circulation_kg":4.185711256509614,"EC_solvent_makeup_kg":0.20928556282548072,"TEA_HCl_in_effluent_kg":2.182452046097746,"HCl_in_effluent_kg":0.5780403825372256,"water_for_capture_and_washing_kg":3.5312129386846056,"effluent_kg":6.291705367319578,"organic_waste_kg":0.6136523346327748}
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED ADDITIVE PRODUCT-METADATA CONSISTENCY CORRECTION, 2026-10-18. The existing activity is named vinyl carbonate; its production exchange and the electrolyte buyer both already specify vinyl carbonate. The activity-level reference product instead said disodium disulphite. Align only that declared reference product with the existing provider/output/consumer label, vinyl carbonate. Retain 1 kg output and the 0.024 kg/kg electrolyte purchase, all process inputs, emissions, waste, supplier geographies, allocations and existing source text. This is metadata consistency, not independent validation of the intended chemical identity, synthesis stoichiometry, reaction/process yields or emissions. The existing source field includes a sulfites reference and a generic chemical LCI methodology citation; it remains unverified provenance for this additive recipe and is retained for traceability, not endorsed as evidence of the intended synthesis. Recover the original chemical-specific source before treating the recipe as validated. The existing inventory label vinyl carbonate is preserved; no substitution or rename to vinylene carbonate or another chemical is implied. No quantities, other product labels, runtime/migrations, native inventories or metal factors change. No full scenario rebuild or quantified system-metal effect is claimed.</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7242,7 @@
         <v>61</v>
       </c>
       <c r="B398">
-        <v>0.59899999999999998</v>
+        <v>0</v>
       </c>
       <c r="C398" t="s">
         <v>53</v>
@@ -7252,7 +7262,7 @@
         <v>55</v>
       </c>
       <c r="B399">
-        <v>0.20880000000000001</v>
+        <v>0</v>
       </c>
       <c r="C399" t="s">
         <v>53</v>
@@ -7272,7 +7282,7 @@
         <v>59</v>
       </c>
       <c r="B400">
-        <v>0.30909999999999999</v>
+        <v>0</v>
       </c>
       <c r="C400" t="s">
         <v>53</v>
@@ -7292,7 +7302,7 @@
         <v>185</v>
       </c>
       <c r="B401">
-        <v>2.46E-2</v>
+        <v>0</v>
       </c>
       <c r="C401" t="s">
         <v>53</v>
@@ -7312,7 +7322,7 @@
         <v>186</v>
       </c>
       <c r="B402">
-        <v>2.5999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="C402" t="s">
         <v>8</v>
@@ -7332,7 +7342,7 @@
         <v>45</v>
       </c>
       <c r="B403">
-        <v>0.41599999999999998</v>
+        <v>0</v>
       </c>
       <c r="C403" t="s">
         <v>46</v>
@@ -7352,7 +7362,7 @@
         <v>122</v>
       </c>
       <c r="B404" s="5">
-        <v>4.0000000000000001E-10</v>
+        <v>0</v>
       </c>
       <c r="C404" t="s">
         <v>7</v>
@@ -7372,7 +7382,7 @@
         <v>187</v>
       </c>
       <c r="B405">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="C405" t="s">
         <v>113</v>
@@ -7392,7 +7402,7 @@
         <v>190</v>
       </c>
       <c r="B406">
-        <v>1.23826772231672</v>
+        <v>0</v>
       </c>
       <c r="C406" t="s">
         <v>8</v>
@@ -7412,7 +7422,7 @@
         <v>162</v>
       </c>
       <c r="B407">
-        <v>1.0773504325799399</v>
+        <v>0</v>
       </c>
       <c r="C407" t="s">
         <v>8</v>
@@ -7433,7 +7443,7 @@
         <v>188</v>
       </c>
       <c r="B408">
-        <v>4.09211487463271E-3</v>
+        <v>0</v>
       </c>
       <c r="C408" t="s">
         <v>8</v>
@@ -7453,7 +7463,7 @@
         <v>188</v>
       </c>
       <c r="B409">
-        <v>1.4907885125367301E-2</v>
+        <v>0</v>
       </c>
       <c r="C409" t="s">
         <v>8</v>
@@ -7473,7 +7483,7 @@
         <v>150</v>
       </c>
       <c r="B410" s="5">
-        <v>-8.4364552406030698E-7</v>
+        <v>0</v>
       </c>
       <c r="C410" t="s">
         <v>138</v>
@@ -7493,7 +7503,7 @@
         <v>150</v>
       </c>
       <c r="B411" s="5">
-        <v>-9.1266630702019795E-8</v>
+        <v>0</v>
       </c>
       <c r="C411" t="s">
         <v>138</v>
@@ -7513,7 +7523,7 @@
         <v>150</v>
       </c>
       <c r="B412" s="5">
-        <v>-1.7650878452376699E-6</v>
+        <v>0</v>
       </c>
       <c r="C412" t="s">
         <v>138</v>
@@ -7533,7 +7543,7 @@
         <v>192</v>
       </c>
       <c r="B413">
-        <v>-3.2378916563019001E-3</v>
+        <v>0</v>
       </c>
       <c r="C413" t="s">
         <v>8</v>
@@ -7554,7 +7564,7 @@
         <v>192</v>
       </c>
       <c r="B414">
-        <v>-0.49735210834369797</v>
+        <v>0</v>
       </c>
       <c r="C414" t="s">
         <v>8</v>
@@ -7575,7 +7585,7 @@
         <v>194</v>
       </c>
       <c r="B415">
-        <v>0.144590178265634</v>
+        <v>0</v>
       </c>
       <c r="C415" t="s">
         <v>8</v>
@@ -7596,7 +7606,7 @@
         <v>194</v>
       </c>
       <c r="B416">
-        <v>0.72281543479071697</v>
+        <v>0</v>
       </c>
       <c r="C416" t="s">
         <v>8</v>
@@ -7609,6 +7619,36 @@
       </c>
       <c r="G416" t="s">
         <v>195</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="B417">
+        <v>1</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
       </c>
     </row>
     <row r="418" spans="1:6" ht="16" ns3:dyDescent="0.2">
@@ -24959,6 +24999,667 @@
         </is>
       </c>
     </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>APPROVED VINYLENE-CARBONATE REACTION REFERENCE, issue47, 2026-10-18. Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive. The intended cyclic unsaturated battery additive is VINYLENE carbonate, not a sulfite or an unspecified vinyl carbonate ester. Correct active electrolyte link to a uniquely named VC supplier, retaining0.024kg/kg electrolyte. Existing vinyl carbonate name becomes a compatibility alias purchasing the same new VC once; its old chemically unbalanced inputs are disabled. Patent Example1 uses0.420mol chloroethylene carbonate,84mlEC solvent and0.630molTEA near60C; Example3 yields73.3%purified VC. Adopt that isolated yield, but explicitly assume100%selective initial UV chlorination and complete chemical dehydrochlorination, with unrecovered VC collected as same-composition organic/polymer residue. Those reaction-versus-isolation splits are engineering assumptions, not measured process selectivities. Reactions: EC+Cl2 -&gt; chloroEC+HCl; chloroEC+TEA -&gt; VC+TEA.HCl. One HCl is captured from chlorination; the other is bound in amine salt. Assume95%recovery of unreacted0.5molTEA/molCEC, and95%ECsolvent recovery, with solvent density1320kg/m3 assumed at process temperature. Buy net make-up only; internally recycled material receives no avoided-production credit. Remaining amine and solvent go once to hazardous organic waste; do not send TEA.HCl to inert landfill. Acid/amine salt collected in wastewater, not vented as unbalanced chlorine:30wt%HCl capture plus wash water equal salt mass, wastewater density1000kg/m3 assumed. Generic wastewater cannot certify chloride or amine-specific fate. Nitrogen0.019kg/kg remains original inert-gas utility, venting/direct species unresolved. Retain original aggregate0.416kWh+2.35MJ, factory and freight as unvalidated utility/delivery proxies; UV lamp, cooling, solvent distillation and high-purity drying energy are not independently measured. Plant corrosion alloys and auxiliary equipment remain unquantified critical-metal coverage gaps. This is a mass/atom-consistent declared engineering reference, not a recovered manufacturer LCI or proof of industrial electrolyte purity. No new catalyst metals or commercial-grade purity claims. Sensitivity:59-85%isolation,90-99%amine/solvent recovery, nonselective chlorination and process utilities. Source assumptions and numeric mass budget: {"CAS":"872-36-6","formula":"C3H2O3","isolated_yield_from_CEC":0.733,"ethylene_carbonate_reactant_kg":1.3962200934498092,"chlorine_kg":1.124117151842923,"triethylamine_gross_kg":2.406617495340781,"triethylamine_recovered_internal_kg":0.7620955401912473,"triethylamine_net_kg":1.6445219551495338,"EC_solvent_circulation_kg":4.185711256509614,"EC_solvent_makeup_kg":0.20928556282548072,"TEA_HCl_in_effluent_kg":2.182452046097746,"HCl_in_effluent_kg":0.5780403825372256,"water_for_capture_and_washing_kg":3.5312129386846056,"effluent_kg":6.291705367319578,"organic_waste_kg":0.6136523346327748}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="B1331">
+        <v>1</v>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>vinylene carbonate, EC chlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>market for ethylene carbonate</t>
+        </is>
+      </c>
+      <c r="B1332">
+        <v>1.60550565627529</v>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>ethylene carbonate</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>ethylene carbonate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>market for triethyl amine</t>
+        </is>
+      </c>
+      <c r="B1333">
+        <v>1.6445219551495338</v>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>triethyl amine</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>triethyl amine</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B1334">
+        <v>1.124117151842923</v>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>market group for tap water</t>
+        </is>
+      </c>
+      <c r="B1335">
+        <v>3.5312129386846056</v>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B1336">
+        <v>-0.006291705367319577</v>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B1337">
+        <v>-0.6136523346327748</v>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B1338">
+        <v>0.019</v>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B1339">
+        <v>0.416</v>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>market group for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B1340">
+        <v>2.35</v>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>market for chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="B1341">
+        <v>4e-10</v>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>chemical factory, organics</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>market for transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="B1342">
+        <v>0.599</v>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>transport, freight, sea, container ship</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>market for transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="B1343">
+        <v>0.2088</v>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>transport, freight, lorry, unspecified</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>market group for transport, freight train</t>
+        </is>
+      </c>
+      <c r="B1344">
+        <v>0.3091</v>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>transport, freight train</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>market group for transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="B1345">
+        <v>0.0246</v>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>ton kilometer</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>transport, freight, inland waterways, barge</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -13269,7 +13269,9 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -13439,7 +13441,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B776">
@@ -13462,12 +13464,12 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14109,9 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -14277,7 +14281,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B816">
@@ -14300,12 +14304,12 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14949,9 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -15115,7 +15121,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B856">
@@ -15138,12 +15144,12 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15787,9 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -15951,7 +15959,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B896">
@@ -15974,12 +15982,12 @@
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16627,9 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -16789,7 +16799,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B936">
@@ -16812,12 +16822,12 @@
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17465,9 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17625,7 +17637,7 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B976">
@@ -17648,12 +17660,12 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -18293,7 +18305,9 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18463,7 +18477,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B1016">
@@ -18486,12 +18500,12 @@
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -19131,7 +19145,9 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -19303,7 +19319,7 @@
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B1056">
@@ -19326,12 +19342,12 @@
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>
@@ -19969,7 +19985,9 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
+          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -20139,7 +20157,7 @@
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>market for printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="B1096">
@@ -20162,12 +20180,12 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>printed wiring board, through-hole mounted, unspecified, Pb free</t>
+          <t>battery auxiliary interface and power conditioning, engineering reference</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -1318,7 +1318,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X1345"/>
+  <dimension ref="A1:X1687"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="74.1640625" customWidth="1"/>
@@ -25678,6 +25678,7494 @@
         </is>
       </c>
     </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1357">
+        <v>1</v>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="B1358">
+        <v>1</v>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LFP</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1359">
+        <v>-1</v>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1371">
+        <v>1</v>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1372">
+        <v>0.02625694538555359</v>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1373">
+        <v>1.5131623526223064</v>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1374">
+        <v>0.04234991191218321</v>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1375">
+        <v>0.0055054885485838175</v>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1376">
+        <v>0.060983873153543824</v>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1377">
+        <v>0.2191607941455481</v>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1378">
+        <v>0.2191607941455481</v>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1379">
+        <v>0.02625694538555359</v>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1380">
+        <v>1.5131623526223064</v>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1381">
+        <v>0.060983873153543824</v>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1382">
+        <v>0.04234991191218321</v>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1383">
+        <v>-2.0865801599132667</v>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1388">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1395">
+        <v>1</v>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="B1396">
+        <v>1</v>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>battery cell, NMC111, Crenna engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1397">
+        <v>-1</v>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1402">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1409">
+        <v>1</v>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1410">
+        <v>0.024120304658001912</v>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1411">
+        <v>1.370682697392224</v>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1412">
+        <v>0.04035512510088781</v>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1413">
+        <v>0.005102372139192712</v>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1414">
+        <v>0.04731290529069606</v>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1415">
+        <v>0.16466746449212843</v>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1416">
+        <v>0.16466746449212843</v>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1417">
+        <v>0.024120304658001912</v>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1418">
+        <v>1.370682697392224</v>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1419">
+        <v>0.04731290529069606</v>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1420">
+        <v>0.04035512510088781</v>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1421">
+        <v>-1.8169083335652612</v>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1426">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1433">
+        <v>1</v>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+      <c r="B1434">
+        <v>1</v>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>battery cell, NMC532, source-precision engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1435">
+        <v>-1</v>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1440">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1446" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1447">
+        <v>1</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1447" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1448">
+        <v>0.024067388688327314</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1448" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1449">
+        <v>1.3084328427288714</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1449" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1450">
+        <v>0.03934092381745811</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1450" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1451">
+        <v>0.005091178376376932</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1451" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1452">
+        <v>0.043506433398130144</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1452" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1453">
+        <v>0.16245487364620936</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1453" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1454">
+        <v>0.16245487364620936</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1454" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1455">
+        <v>0.024067388688327314</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1455" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1456">
+        <v>1.3084328427288714</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1456" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1457">
+        <v>0.043506433398130144</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1457" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1458">
+        <v>0.03934092381745811</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1458" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1459">
+        <v>-1.745348514301583</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1459" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1470" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1471">
+        <v>1</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1471" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+      <c r="B1472">
+        <v>1</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1472" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC622</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1473">
+        <v>-1</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1484" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1485">
+        <v>1</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1485" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1486">
+        <v>0.020056157240272765</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1486" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1487">
+        <v>1.0903607022740596</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1487" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1488">
+        <v>0.0327841031812151</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1488" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1489">
+        <v>0.004242648646980777</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1489" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1490">
+        <v>0.03625536116510846</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1490" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1491">
+        <v>0.13537906137184114</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1491" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1492">
+        <v>0.13537906137184114</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1492" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1493">
+        <v>0.020056157240272765</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1493" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1494">
+        <v>1.0903607022740596</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1494" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1495">
+        <v>0.03625536116510846</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1495" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1496">
+        <v>0.0327841031812151</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1496" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1497">
+        <v>-1.4544570952513194</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1497" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1508" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1509">
+        <v>1</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1509" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="B1510">
+        <v>1</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1510" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1511">
+        <v>-1</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1511" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1516">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1522" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1523">
+        <v>1</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1523" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1524">
+        <v>0.016844861999262637</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1524" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1525">
+        <v>0.9356844099213057</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1525" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1526">
+        <v>0.02765099988558206</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1526" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1527">
+        <v>0.0034961034338092264</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1527" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1528">
+        <v>0.03210058607406653</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1528" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1529">
+        <v>0.11600706848548797</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1529" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1530">
+        <v>0.11600706848548797</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1530" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1531">
+        <v>0.016844861999262637</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1531" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1532">
+        <v>0.9356844099213057</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1532" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1533">
+        <v>0.03210058607406653</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1533" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1534">
+        <v>0.02765099988558206</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1534" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1535">
+        <v>-1.247791098285003</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1540">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1546" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1546" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1547">
+        <v>1</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1547" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1547" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>battery cell production, Li-ion, NMC955</t>
+        </is>
+      </c>
+      <c r="B1548">
+        <v>1</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1548" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC955</t>
+        </is>
+      </c>
+      <c r="I1548" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, NMC955</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1549">
+        <v>-1</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1549" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1549" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1554">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1560" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1561">
+        <v>1</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1561" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1562">
+        <v>0.014157287463721949</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1562" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1563">
+        <v>0.7696663780758067</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1563" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1564">
+        <v>0.02314171989262242</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1564" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1564" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1565">
+        <v>0.0029948108096334893</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1565" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1566">
+        <v>0.02559201964595891</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1566" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1567">
+        <v>0.09556169038012315</v>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1567" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1567" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1568">
+        <v>0.09556169038012315</v>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1568" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1568" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1569">
+        <v>0.014157287463721949</v>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1569" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1569" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1570">
+        <v>0.7696663780758067</v>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1570" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1570" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1571">
+        <v>0.02559201964595891</v>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1571" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1571" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1572">
+        <v>0.02314171989262242</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1572" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1572" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1573">
+        <v>-1.0266755966479901</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1573" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1573" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1578">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1584" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1585">
+        <v>1</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1585" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1585" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="B1586">
+        <v>1</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1586" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+      <c r="I1586" t="inlineStr">
+        <is>
+          <t>battery cell, NCA, Crenna anode engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1587">
+        <v>-1</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1587" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1587" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1592">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1598" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1598" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1599">
+        <v>1</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1599" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1599" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1600">
+        <v>0.017693815331010453</v>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1600" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1600" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1601">
+        <v>0.9510425740418119</v>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1601" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1602">
+        <v>0.028582317073170733</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1602" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1603">
+        <v>0.003742922473867596</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1603" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1604">
+        <v>0.031304442508710804</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1604" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1604" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1605">
+        <v>0.12028391768292683</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1605" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1605" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1606">
+        <v>0.12028391768292683</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1606" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1607">
+        <v>0.017693815331010453</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1607" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1607" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1608">
+        <v>0.9510425740418119</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1608" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1608" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1609">
+        <v>0.031304442508710804</v>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1609" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1609" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1610">
+        <v>0.028582317073170733</v>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1610" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1610" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1611">
+        <v>-1.2729339067944248</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1611" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1611" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1616">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1622" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1623">
+        <v>1</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1623" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>market for battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+      <c r="B1624">
+        <v>1</v>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1624" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>battery cell, Li-ion, LTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1625">
+        <v>-1</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1625" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1630">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1636" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1636" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1637">
+        <v>1</v>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1637" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1637" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1638">
+        <v>0.07970425287261226</v>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1638" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1638" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1639">
+        <v>4.33315236290144</v>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1639" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1639" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1640">
+        <v>0.130285797964847</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1640" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1640" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1641">
+        <v>0.016860515030744903</v>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1641" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1641" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1642">
+        <v>0.14408076480818371</v>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1642" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1642" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1643">
+        <v>0.5380037068901328</v>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1643" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1644">
+        <v>0.5380037068901328</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1644" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1644" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1645">
+        <v>0.07970425287261226</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1645" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1645" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1646">
+        <v>4.33315236290144</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1646" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1647">
+        <v>0.14408076480818371</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1647" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1647" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1648">
+        <v>0.130285797964847</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1648" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1649">
+        <v>-5.7800911073580945</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1649" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1649" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1654">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1660" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1660" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="B1661">
+        <v>1</v>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1661" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+        </is>
+      </c>
+      <c r="I1661" t="inlineStr">
+        <is>
+          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+      <c r="B1662">
+        <v>1</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1662" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+      <c r="I1662" t="inlineStr">
+        <is>
+          <t>battery cell, LiMn2O4, public engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1663">
+        <v>-1</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1663" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B1668">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F1674" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I1674" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="B1675">
+        <v>1</v>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F1675" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
+      </c>
+      <c r="I1675" t="inlineStr">
+        <is>
+          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B1676">
+        <v>0.024717198437031632</v>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1676" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>market for aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="B1677">
+        <v>1.7102197727069544</v>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1677" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>aluminium, wrought alloy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>market for polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="B1678">
+        <v>0.04890849903497748</v>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1678" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>polyethylene, high density, granulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="B1679">
+        <v>0.005258978390857794</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1679" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyester resin, hand lay-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>market for steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="B1680">
+        <v>0.06258184285120774</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1680" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>steel, low-alloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>ethylene glycol production</t>
+        </is>
+      </c>
+      <c r="B1681">
+        <v>0.174072184737393</v>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1681" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+      <c r="I1681" t="inlineStr">
+        <is>
+          <t>ethylene glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>market for water, deionised</t>
+        </is>
+      </c>
+      <c r="B1682">
+        <v>0.174072184737393</v>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1682" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>water, deionised</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1683">
+        <v>0.024717198437031632</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1683" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>metal working, average for copper product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1684">
+        <v>1.7102197727069544</v>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1684" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1684" t="inlineStr">
+        <is>
+          <t>metal working, average for aluminium product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="B1685">
+        <v>0.06258184285120774</v>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1685" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+      <c r="I1685" t="inlineStr">
+        <is>
+          <t>metal working, average for steel product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="B1686">
+        <v>0.04890849903497748</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1686" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>injection moulding</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>market for used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="B1687">
+        <v>-2.199830660895816</v>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F1687" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>used Li-ion battery</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:X737" ns2:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -8553,6 +8553,11 @@
       <c r="H487" t="s">
         <v>6</v>
       </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="488" spans="1:8" ns3:dyDescent="0.2">
       <c r="A488" t="s">
@@ -8573,6 +8578,11 @@
       <c r="G488" t="s">
         <v>136</v>
       </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</t>
+        </is>
+      </c>
     </row>
     <row r="489" spans="1:8" ns3:dyDescent="0.2">
       <c r="A489" t="s">
@@ -8826,7 +8836,7 @@
         <v>241</v>
       </c>
       <c r="B500">
-        <v>-1.8</v>
+        <v>-0.0018</v>
       </c>
       <c r="C500" t="s">
         <v>207</v>
@@ -8842,6 +8852,11 @@
       </c>
       <c r="H500" t="s">
         <v>242</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</t>
+        </is>
       </c>
     </row>
     <row r="502" spans="1:8" ht="16" ns3:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -3807,7 +3807,7 @@
     <row r="171" spans="1:7" ns3:dyDescent="0.2">
       <c r="A171" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate production, ethylene carbonate chlorination</t>
         </is>
       </c>
       <c r="B171">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate, ethylene carbonate chlorination</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
         </is>
       </c>
       <c r="B362">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7624,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate production, ethylene carbonate chlorination</t>
         </is>
       </c>
       <c r="B417">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate, ethylene carbonate chlorination</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
     <row r="666" spans="1:7" ns3:dyDescent="0.2">
       <c r="A666" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
         </is>
       </c>
       <c r="B666">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="G666" s="5" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
         </is>
       </c>
     </row>
@@ -12112,7 +12112,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,8 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. To provide a consistent public LMO cell across all supported database versions, use DaiTable8 BEV ingredient list: detailed masses sum146.26999999999998kg versus printed146.29kg. Adopt detailed component sum; graphite and PVDF use inherited graphite/PVF cross-version proxies. Assume100percent assembly retention and20kWh electricity/kWh-cell (2.6kWh/kg at.13kWh/kg-cell), plus1MJ natural-gas heat/kg. These utilities/yields are engineering assumptions (sensitivity10-60kWh electricity/kWh-cell); source-specific cell formation, solvent recovery and material losses remain gaps. This fallback is not a measured modern LMO factory.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cell, LiMn2O4, public engineering reference. Former reference product: battery cell, LiMn2O4, public engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. To provide a consistent public LMO cell across all supported database versions, use DaiTable8 BEV ingredient list: detailed masses sum146.26999999999998kg versus printed146.29kg. Adopt detailed component sum; graphite and PVDF use inherited graphite/PVF cross-version proxies. Assume100percent assembly retention and20kWh electricity/kWh-cell (2.6kWh/kg at.13kWh/kg-cell), plus1MJ natural-gas heat/kg. These utilities/yields are engineering assumptions (sensitivity10-60kWh electricity/kWh-cell); source-specific cell formation, solvent recovery and material losses remain gaps. This fallback is not a measured modern LMO factory.</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12239,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="B723">
@@ -12261,7 +12262,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12694,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LFP, without electronics</t>
         </is>
       </c>
     </row>
@@ -12727,7 +12728,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LFP, without electronics</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12764,8 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, LFP, engineering reference. Former reference product: battery hardware, Li-ion, LFP, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LFP; geometry proxy=LFP; cellmass=147.58kg, scalablehardware=196.85000000000002kg, assumed cellbaseline=0.16kWh/kg, grossreference=23.612800000000004kWh, fixedcontrolmass=6.668kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12821,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LFP, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LFP, without electronics</t>
         </is>
       </c>
       <c r="B749">
@@ -12842,7 +12844,7 @@
       </c>
       <c r="G749" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LFP, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LFP, without electronics</t>
         </is>
       </c>
     </row>
@@ -13214,7 +13216,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13250,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13286,8 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, LFP, engineering reference. Former reference product: battery monitoring and central controls, LFP, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -13351,7 +13354,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LFP</t>
         </is>
       </c>
       <c r="B773">
@@ -13374,19 +13377,19 @@
       </c>
       <c r="G773" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LFP, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LFP</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B774">
@@ -13409,19 +13412,19 @@
       </c>
       <c r="G774" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B775">
@@ -13444,19 +13447,19 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B776">
@@ -13479,12 +13482,12 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13534,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC111, without electronics</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13568,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC111, without electronics</t>
         </is>
       </c>
     </row>
@@ -13601,7 +13604,8 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NMC111, engineering reference. Former reference product: battery hardware, Li-ion, NMC111, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC111; geometry proxy=NMC111; cellmass=119.77kg, scalablehardware=158.94000000000003kg, assumed cellbaseline=0.18kWh/kg, grossreference=21.5586kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -13659,7 +13663,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC111, without electronics</t>
         </is>
       </c>
       <c r="B789">
@@ -13682,14 +13686,14 @@
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC111, without electronics</t>
         </is>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
       <c r="B790">
@@ -13712,7 +13716,7 @@
       </c>
       <c r="G790" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
     </row>
@@ -14054,7 +14058,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
         </is>
       </c>
     </row>
@@ -14088,7 +14092,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC111</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14128,8 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NMC111, engineering reference. Former reference product: battery monitoring and central controls, NMC111, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -14191,7 +14196,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC111</t>
         </is>
       </c>
       <c r="B813">
@@ -14214,19 +14219,19 @@
       </c>
       <c r="G813" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC111</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC111, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC111</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B814">
@@ -14249,19 +14254,19 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B815">
@@ -14284,19 +14289,19 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B816">
@@ -14319,12 +14324,12 @@
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14376,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC532, without electronics</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14410,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC532, without electronics</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14446,8 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NMC532, engineering reference. Former reference product: battery hardware, Li-ion, NMC532, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC532; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.2kWh/kg, grossreference=21.606kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -14499,7 +14505,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC532, without electronics</t>
         </is>
       </c>
       <c r="B829">
@@ -14522,14 +14528,14 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC532, without electronics</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
       <c r="B830">
@@ -14552,7 +14558,7 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
     </row>
@@ -14894,7 +14900,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14934,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC532</t>
         </is>
       </c>
     </row>
@@ -14964,7 +14970,8 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NMC532, engineering reference. Former reference product: battery monitoring and central controls, NMC532, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -15031,7 +15038,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC532</t>
         </is>
       </c>
       <c r="B853">
@@ -15054,19 +15061,19 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC532</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC532, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC532</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B854">
@@ -15089,19 +15096,19 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B855">
@@ -15124,19 +15131,19 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B856">
@@ -15159,12 +15166,12 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15218,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC622, without electronics</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15252,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC622, without electronics</t>
         </is>
       </c>
     </row>
@@ -15281,7 +15288,8 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NMC622, engineering reference. Former reference product: battery hardware, Li-ion, NMC622, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC622; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.24kWh/kg, grossreference=25.9272kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -15337,7 +15345,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC622, without electronics</t>
         </is>
       </c>
       <c r="B869">
@@ -15360,7 +15368,7 @@
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC622, without electronics</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15740,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
@@ -15766,7 +15774,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15810,8 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NMC622, engineering reference. Former reference product: battery monitoring and central controls, NMC622, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -15869,7 +15878,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="B893">
@@ -15892,19 +15901,19 @@
       </c>
       <c r="G893" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC622</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC622, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC622</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B894">
@@ -15927,19 +15936,19 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B895">
@@ -15962,19 +15971,19 @@
       </c>
       <c r="G895" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B896">
@@ -15997,12 +16006,12 @@
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16058,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC811, without electronics</t>
         </is>
       </c>
     </row>
@@ -16083,7 +16092,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC811, without electronics</t>
         </is>
       </c>
     </row>
@@ -16119,7 +16128,8 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NMC811, engineering reference. Former reference product: battery hardware, Li-ion, NMC811, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC811; geometry proxy=NMC811; cellmass=112.37kg, scalablehardware=151.63000000000002kg, assumed cellbaseline=0.28kWh/kg, grossreference=31.463600000000003kWh, fixedcontrolmass=6.568kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -16177,7 +16187,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC811, without electronics</t>
         </is>
       </c>
       <c r="B909">
@@ -16200,14 +16210,14 @@
       </c>
       <c r="G909" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC811, without electronics</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B910">
@@ -16230,7 +16240,7 @@
       </c>
       <c r="G910" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -16572,7 +16582,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
         </is>
       </c>
     </row>
@@ -16606,7 +16616,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC811</t>
         </is>
       </c>
     </row>
@@ -16642,7 +16652,8 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NMC811, engineering reference. Former reference product: battery monitoring and central controls, NMC811, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -16709,7 +16720,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC811</t>
         </is>
       </c>
       <c r="B933">
@@ -16732,19 +16743,19 @@
       </c>
       <c r="G933" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC811</t>
         </is>
       </c>
       <c r="I933" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC811, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC811</t>
         </is>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B934">
@@ -16767,19 +16778,19 @@
       </c>
       <c r="G934" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I934" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B935">
@@ -16802,19 +16813,19 @@
       </c>
       <c r="G935" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I935" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B936">
@@ -16837,12 +16848,12 @@
       </c>
       <c r="G936" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I936" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16900,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC955, without electronics</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16934,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC955, without electronics</t>
         </is>
       </c>
     </row>
@@ -16959,7 +16970,8 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NMC955, engineering reference. Former reference product: battery hardware, Li-ion, NMC955, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NMC955; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.34kWh/kg, grossreference=36.7302kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17027,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NMC955, without electronics</t>
         </is>
       </c>
       <c r="B949">
@@ -17038,7 +17050,7 @@
       </c>
       <c r="G949" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NMC955, without electronics</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17422,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -17444,7 +17456,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17492,8 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NMC955, engineering reference. Former reference product: battery monitoring and central controls, NMC955, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -17547,7 +17560,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="B973">
@@ -17570,19 +17583,19 @@
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
       <c r="I973" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NMC955, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NMC955</t>
         </is>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B974">
@@ -17605,19 +17618,19 @@
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I974" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B975">
@@ -17640,19 +17653,19 @@
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I975" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B976">
@@ -17675,12 +17688,12 @@
       </c>
       <c r="G976" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I976" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -17727,7 +17740,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NCA, without electronics</t>
         </is>
       </c>
     </row>
@@ -17761,7 +17774,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NCA, without electronics</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17810,8 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, NCA, engineering reference. Former reference product: battery hardware, Li-ion, NCA, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=NCA; geometry proxy=NCA; cellmass=104.96kg, scalablehardware=142.36999999999998kg, assumed cellbaseline=0.28kWh/kg, grossreference=29.3888kWh, fixedcontrolmass=6.548kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -17855,7 +17869,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, NCA, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, NCA, without electronics</t>
         </is>
       </c>
       <c r="B989">
@@ -17878,14 +17892,14 @@
       </c>
       <c r="G989" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, NCA, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, NCA, without electronics</t>
         </is>
       </c>
     </row>
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B990">
@@ -17908,7 +17922,7 @@
       </c>
       <c r="G990" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18264,7 @@
       </c>
       <c r="B1004" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NCA</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18298,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NCA</t>
         </is>
       </c>
     </row>
@@ -18320,7 +18334,8 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, NCA, engineering reference. Former reference product: battery monitoring and central controls, NCA, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -18387,7 +18402,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, NCA</t>
         </is>
       </c>
       <c r="B1013">
@@ -18410,19 +18425,19 @@
       </c>
       <c r="G1013" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NCA</t>
         </is>
       </c>
       <c r="I1013" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, NCA, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, NCA</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B1014">
@@ -18445,19 +18460,19 @@
       </c>
       <c r="G1014" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I1014" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B1015">
@@ -18480,19 +18495,19 @@
       </c>
       <c r="G1015" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I1015" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1016">
@@ -18515,12 +18530,12 @@
       </c>
       <c r="G1016" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1016" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -18567,7 +18582,7 @@
       </c>
       <c r="B1020" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LTO, without electronics</t>
         </is>
       </c>
     </row>
@@ -18601,7 +18616,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, without electronics</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18652,8 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, LTO, engineering reference. Former reference product: battery hardware, Li-ion, LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOURCE-CONSISTENT NCA/LTO CELL AND CAPACITY REFERENCE,item22,2026-10-18. Schmidt etal2019 DOI10.1021/acs.est.8b05313, Supporting Data es8b05313_si_002.zip, NCA LTO battery import.xlsx summary!H54=16.040428932169362kg/kWh dry cell components excluding pouch, H56=.5181296021158341kg/kWh pouch; H60=1000/(H54+H56)=60.39173022998696Wh/kg-cell. This is the source harmonized historical NCA/LTO engineering design, not modern fleet validation. The current capacity reference85Wh/kg is inconsistent with that recipe. Restore seven component fractions to source per-kWh masses divided by16.558558534285197kg/kWh; the old six non-pouch fractions were multiplied by rounded.060kWh/kg and the pouch filled the remainder, rather than using the source pouch mass. This restores source component ratios and a1kg component-sum cell. Preserve all previously corrected upstream electrode/graphite/collector recipes and supplier identities, cell water/electricity/heat proxies, reference pack cellmass108.03kg and non-cell geometry37.71kg (NMC622 geometry proxy), controls/protection6.538kg per reference and all vehicle energy/cycle/replacement assumptions. Factory utilities and upstream manufacturing yields remain inherited proxies rather than a claim of complete original-source reproduction. Use exact source cell energy.060391730229986965kWh/kg in the capacity market. Scalable hardware145.74kg now represents6.524118616745492grosskWh, hence22.338649641643293kg/kWh instead of15.871408268944903. Pair identical negative waste mass and signed uncertainty endpoints; retain prior engineering75-125percent mass range, without claiming source statistical confidence. Fixed-unit controls remain unchanged per reference pack, but dose becomes1/6.524118616745492unit/kWh to share the same capacity basis. No future LTO improvement is assumed; existing2020/2050 density-factor ratio is1 even though its YAML absolute values are historical50Wh/kg. No runtime/YAML changes. Original standalone75/25 LTO battery market remains a separate legacy assembly reference, while capacity markets buy the explicit hardware/central-control reference. Source pack48.6049Wh/kg excludes BMS/cooling and is distinct from the adopted cell-specific60.3917Wh/kg. Remaining material-grade, utility, thermal rating, life and future-design limitations remain explicit.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LTO; geometry proxy=NMC622; cellmass=108.03kg, scalablehardware=145.74kg, assumed cellbaseline=0.085kWh/kg, grossreference=9.18255kWh, fixedcontrolmass=6.538kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
@@ -18695,7 +18711,7 @@
     <row r="1029">
       <c r="A1029" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LTO, without electronics</t>
         </is>
       </c>
       <c r="B1029">
@@ -18718,7 +18734,7 @@
       </c>
       <c r="G1029" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LTO, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LTO, without electronics</t>
         </is>
       </c>
     </row>
@@ -19090,7 +19106,7 @@
       </c>
       <c r="B1044" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LTO</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19140,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LTO</t>
         </is>
       </c>
     </row>
@@ -19160,7 +19176,8 @@
       </c>
       <c r="B1050" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, LTO, engineering reference. Former reference product: battery monitoring and central controls, LTO, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -19229,7 +19246,7 @@
     <row r="1053">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LTO</t>
         </is>
       </c>
       <c r="B1053">
@@ -19252,19 +19269,19 @@
       </c>
       <c r="G1053" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LTO</t>
         </is>
       </c>
       <c r="I1053" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LTO, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LTO</t>
         </is>
       </c>
     </row>
     <row r="1054">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B1054">
@@ -19287,19 +19304,19 @@
       </c>
       <c r="G1054" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I1054" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B1055">
@@ -19322,19 +19339,19 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I1055" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1056">
@@ -19357,12 +19374,12 @@
       </c>
       <c r="G1056" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1056" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19426,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LiMn2O4, without electronics</t>
         </is>
       </c>
     </row>
@@ -19443,7 +19460,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LiMn2O4, without electronics</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19496,8 @@
       </c>
       <c r="B1066" t="inlineStr">
         <is>
-          <t>APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery hardware, Li-ion, LiMn2O4, engineering reference. Former reference product: battery hardware, Li-ion, LiMn2O4, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ENGINEERING PACK CONTROL BOUNDARY, item14, 2026-10-18. Dai etal2018, Argonne ANL/ESD-18/4, https://publications.anl.gov/anlpubs/2018/10/146906.pdf, Table8 BEV material inventory; Wickerts corrected SI S26 and Ellingsen2014 BMS component function split. Replace opaque whole-pack supply in capacity markets by explicit public-source cell+non-electronic module/pack hardware, plus one separately named monitoring/central-protection package. This avoids combining module monitors with an undifferentiated whole BMS. Dai per-pack module electronics1.12kg are represented ONCE by populated-PCB proxy; assume4kg of the reported pack electronics correspond to the former undifferentiated BMS, remove that proxy and substitute one central4.518kg engineering package (0.49board+2.8HV+1.2LV+.028fasteners) with no module monitoring. Remaining pack electronics=(Dai pack electronics-4kg), represented once by the same generic PCB proxy with unspecified function; the4kg split is an engineering function assumption, not a source component breakdown. The inherited LTO cell source states60Wh/kg while the configured85Wh/kg remains an explicit unresolved performance assumption. Thermal mass uses Dai coolant, assumed50/50 ethylene glycol/water; module aluminium includes source thermal interface, while hoses/pump/control thermal ratings remain gaps. Hardware materials are retained mass with100percent assembly retention reference and generic working/injection services; source rounding is resolved by adding listed components, not silently forcing source totals. No native proprietary pack inventory is copied or numerically subtracted. Generic PCB, insulation proxies (module glass fibre reinforced plastic; pack HDPE), material grades and manufacturing energy remain engineering limitations. NMC532/NMC955/LTO use NMC622 non-cell geometry as an explicit proxy, retaining their own existing cell supplier. No claim of chemistry-specific validated outer-pack geometry. Use each declared cell-baseline specific energy (.16LFP,.18NMC111,.20NMC532,.24NMC622,.28NMC811/NCA,.34NMC955,.085LTO,.13LMO kWh/kg), correcting small mismatches between historical rounded share metadata/formulas: gross reference kWh=source cellmass*that baseline. Thus the historical23.5kWh Dai label is not forced onto a different configured cell density. Fixed controls use unit input1/referencekWh; scalable hardware and equal negative waste usekg. Future density learning changes kg hardware/waste while fixed controls and their own waste stay fixed. Controls are conservatively co-replaced with delivered packs; independent life remains unknown. No common glider/roadway or new recovery credits. Sensitivities: central split3-5kg, module monitoring0.5-2x, fixed versus scalable non-cell materials. These engineering packs resolve accounting duplication but are not verified vehicle designs. Chemistry=LiMn2O4; geometry proxy=LiMn2O4; cellmass=146.26999999999998kg, scalablehardware=188.1kg, assumed cellbaseline=0.13kWh/kg, grossreference=19.015099999999997kWh, fixedcontrolmass=6.478kg. Retained listed hardware material coefficients sum1kg/kg; upstream cell/processing yields are not overwritten. Raw source rounding and cell-specific gaps remain in those providers.</t>
         </is>
       </c>
     </row>
@@ -19535,7 +19553,7 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>market for battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery pack production, Li-ion, LiMn2O4, without electronics</t>
         </is>
       </c>
       <c r="B1069">
@@ -19558,14 +19576,14 @@
       </c>
       <c r="G1069" t="inlineStr">
         <is>
-          <t>battery hardware, Li-ion, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery pack, Li-ion, LiMn2O4, without electronics</t>
         </is>
       </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="B1070">
@@ -19588,7 +19606,7 @@
       </c>
       <c r="G1070" t="inlineStr">
         <is>
-          <t>battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -19930,7 +19948,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -19964,7 +19982,7 @@
       </c>
       <c r="B1087" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20018,8 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery monitoring and central controls, LiMn2O4, engineering reference. Former reference product: battery monitoring and central controls, LiMn2O4, engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED AUXILIARY BATTERY BOARD BOUNDARY, issue58, 2026-10-18. TI TIDA020076 SLURB87 component classes; TI package declarations and KEMET/Bourns references documented in issues55-57; Wickerts2024 DOI10.1021/acssuschemeng.4c01782.s001 and Ellingsen2014 DOI10.1111/jiec.12072 regulator/board allowances. Additional interface BOM below is explicitly engineered,not manufacturermeasured. Replace the remaining0.84-1.03kg/reference generic mountedTHT regulator allowance by a scoped auxiliarypower/interface assembly, distinct from16x70g modulemonitorboards and the490g centralboard. No second fullBMS,centralprocessor,monitorASIC,tractionconverter or duplicated board area is added. Onekg finishedreference has glass0.24,epoxy0.16,copper0.18,ferrite0.15,Alheatspreaders0.10,nylonconnectors/insulation0.09,solder0.03,Class2capacitors0.025,nonzeroresistors0.005,logicpackages0.01 and regulatorpackages0.01kg. These are explicit function-level mass allowances with unknown actual counts/ratings; materialcomposition is an engineering sensitivity reference, not measured exact auxiliaryboards. 40%barelaminate and combined18%Cu include boardtracks and inductorwindings, so no additional wholeinductors or mountedboard proxy. Use package unit counts derived from actual selected package masses, and documented ceramic/resistor families; retain real preciousmetals without genericZn-as-Sb. Maintain total original regulator allowance and paired complete-control disposal, not invent a source-measured mass reduction. Replace the small unresolved generic mountedcomponent remainders inside existing central/moduleboards by this explicitly identified auxiliary-component analogue at unchanged residual mass; it includes laminate by engineering transfer, and is not evidence that the residual is an actual second fitted board. Their detailed fittedpart inputs remain, no recount. Retain uncertainty as actual-component coveragegaps: transformer/diode/isolationpart ratings,trace metals,laminate layout,thermaldesign,assemblyyield and exact topology. Test zero-to-double additional interface allowance as an explicit coverage sensitivity. Component supplymanufacture is separate from boardassembly2kWh/kg;100%final assemblyretention assumed. No chassis, native inventory mutation or extra EOL on top of currentcompletecontrol treatment.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED FUNCTION-SPECIFIC BATTERY CONTROL ELECTRONICS, issue35, 2026-10-18. TI TIDA020076 public BOM https://www.ti.com/lit/pdf/SLURB87; TI BQ79616PAPRQ1 material declaration https://www.ti.com/quality-reliability-packaging-download/report?opn=BQ79616PAPRQ1; TI CC2662 BCU guide https://www.ti.com/lit/pdf/SWRU641. Preserve existing central0.49kg, module1.12kg or1.1kg/16 and residual-pack electronics mass/count budgets. Replace central and identified module-monitor boards, not unidentified residual pack electronics. Engineering monitor70g (1.1kg reference uses68.75g/board through mass scaling),16channelBQ79616one/70g instead of TI18channelBQ79718; this is a declared alternative, not an exact TI board replica or validated channel architecture. Source TIDA fitted passives134ceramiccapacitors(62x0402,27x0603,39x0805,6x1206),128resistors(63x0402,21x0603,4x0805,38x1206,2x2010). Assumed individual masses0402=1mg,0603=3mg,0805=10mg,1206=30mg,2010=60mg,ceramiccapacitor0805=15mg; component-specific manufacturer masses remain unknown. Monitoring bareboard100x100mm,6copperlayers35um,50percent retainedcopper,1.6mm1850kg/m3FR4; centralbareboard0.1m2,4layers samegeometry. Central490g size is legacy mass-constrained engineering reference, not manufacturer dimensions:validate area0.03-0.1m2,layer4-8 andparts independently. FR4 proxy60percentglass/40epoxy plus2g/m2soldermask;ENIGfinish1percentarea,5umNi,0.05umAu.95percentCu/glass/epoxyretention reference with matching waste; etching/process chemistry remains a gap,assume10kWh/m2 bareboard and1kWh/board finalassembly. Monitor20gconnectors,1.5gotherlogic,1gmagnetics,1gdiodes,0.4gRF/crystals,1gsolder;central100gconnectors,5glogic,2gcapacitors,3gresistors,5gsolder. Use existing constituent manufacturing proxies, so logic/resistor/ceramiccap/connector upstreamPd/Ta/Sb/Au remain and are not assumed absent. Remaining component mass explicitly retains a generic populated-board proxy; trace-metal completeness is NOT proven by bulk closure. TI declared366.484301mg BQpackage explicitly purchases Cu/Fe/Ni/Ag/Au/Pd/Pb/Zn/Mn/S/SiO2/epoxy/phenolic/carbonblack and fabricatedsilicondie once. Gold0.034234mg,Pd0.179949mg,Ag4.372259mg perpackage; no generic1percentgoldbondwire. Phosphorus0.048897mg unmodeled due to absent exact feed; mass/trace gap documented. Fabricatedwafer proxy300um2330kg/m3 includes die manufacture, no duplicate elementalSi purchase. No new EOL:existing complete control mass treatment remains once. Component fabrication yields beyond bareboard, automobile qualification, functional reliability andfutureelectronics evolution remain gaps; sensitivity0.5-2xcomponentcounts andunknowncomponentmetalrecipes. This is a transparent engineering reference, not recovered manufacturer complete BOM.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
@@ -20067,7 +20086,7 @@
     <row r="1093">
       <c r="A1093" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system production, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="B1093">
@@ -20090,19 +20109,19 @@
       </c>
       <c r="G1093" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="I1093" t="inlineStr">
         <is>
-          <t>battery monitoring and central controls, LiMn2O4, engineering reference</t>
+          <t xml:space="preserve">battery monitoring and central control system, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
     <row r="1094">
       <c r="A1094" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit production</t>
         </is>
       </c>
       <c r="B1094">
@@ -20125,19 +20144,19 @@
       </c>
       <c r="G1094" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
       <c r="I1094" t="inlineStr">
         <is>
-          <t>battery central controls and protection, engineering reference</t>
+          <t xml:space="preserve">battery central control and protection unit</t>
         </is>
       </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board production, battery module control, mounted</t>
         </is>
       </c>
       <c r="B1095">
@@ -20160,19 +20179,19 @@
       </c>
       <c r="G1095" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
       <c r="I1095" t="inlineStr">
         <is>
-          <t>battery module control board, engineering material reference</t>
+          <t xml:space="preserve">printed circuit board, battery module control, mounted</t>
         </is>
       </c>
     </row>
     <row r="1096">
       <c r="A1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit production</t>
         </is>
       </c>
       <c r="B1096">
@@ -20195,12 +20214,12 @@
       </c>
       <c r="G1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
       <c r="I1096" t="inlineStr">
         <is>
-          <t>battery auxiliary interface and power conditioning, engineering reference</t>
+          <t xml:space="preserve">battery auxiliary interface and power conditioning unit</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20266,7 @@
       </c>
       <c r="B1100" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
     </row>
@@ -20281,7 +20300,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
     </row>
@@ -20317,7 +20336,8 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: anode paste, silicon-graphite, Crenna engineering reference. Former reference product: anode paste, silicon-graphite, Crenna engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20393,7 @@
     <row r="1109">
       <c r="A1109" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
       <c r="B1109">
@@ -20396,7 +20416,7 @@
       </c>
       <c r="G1109" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20728,7 @@
       </c>
       <c r="B1122" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20762,7 @@
       </c>
       <c r="B1125" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -20778,7 +20798,8 @@
       </c>
       <c r="B1128" t="inlineStr">
         <is>
-          <t>BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery cell, NMC811, Crenna anode engineering reference. Former reference product: battery cell, NMC811, Crenna anode engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+BATTERY WORKBOOK LINK COMPLETION AFTER COMBINED IMPORT, approved batch23-32, 2026-10-18. Full default import checks product identities in workbook order. The central controls assembly is supplied by later lci-batteries-LiS.xlsx, so explicit product metadata is needed to declare this valid forward link. Add a product column equal to the existing reference product on affected control-package header/exchange rows; this declares an exact intended product, not a numeric substitute or unresolved wildcard. Validate again against the complete imported database. NMC811 Crenna cell uses the existing native Chinese cathode market when available (ecoinvent3.9+). In3.8 add a public fallback market with the identical native identity, supplying one kg of the existing public supplemental GLO cathode. Normal duplicate removal suppresses this fallback when the native market exists; use explicit product metadata so its legacy input is not prematurely looked up before the fallback is removed. Foreground manufacturing and source quantities otherwise unchanged. The selected anode remains chemistry-specific; native cathode composition is the declared background proxy for newer versions. This is a linking correction, not a new technology-performance or metal-content assumption. Full combined import and all-version link checks are required; do not treat isolated existence checks as proof of import-order compatibility.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
         </is>
@@ -20836,7 +20857,7 @@
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B1131">
@@ -20859,14 +20880,14 @@
       </c>
       <c r="G1131" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
       <c r="B1132">
@@ -20889,7 +20910,7 @@
       </c>
       <c r="G1132" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
     </row>
@@ -21351,7 +21372,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -21385,7 +21406,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -21421,7 +21442,8 @@
       </c>
       <c r="B1156" t="inlineStr">
         <is>
-          <t>APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery cell, NCA, Crenna anode engineering reference. Former reference product: battery cell, NCA, Crenna anode engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CHEMISTRY-SPECIFIC ANODE REFERENCE, item23, 2026-10-18. Crenna et al2021 DOI10.1016/j.resconrec.2021.105619, supplementary workbook https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC811/NCA sheets rows79-99,145-154. Public source dry anode nominal percentages:92 graphite,3 CMC,1 carbon black,2 SBR,2 silicon. Use these nominal percentages summing100 rather than tiny spreadsheet binder roundoff. Graphite is represented as synthetic graphite; exact source graphite blend/coating remains a proxy uncertainty. Source metallurgical silicon is a coating/additive proxy, not a validated nanosilicon manufacturing route. Retain source paste water0.96kg/kg, drying heat8.48487394434316MJ/kg, mixing electricity0.46810728671732227kWh/kg and wastewater0.00096m3/kg. Recover exact public cell component fractions and separate anode paste from copper foil: foil/(paste+foil)=0.363 forNMC811,0.3634 forNCA. Each new cell has1kg retained materials; working services are additional processes, not retained material. No chemistry-independent native anode assembly is used. Original cathode/electrolyte/separator/foil processes remain background proxies; their yields and upstream chemistry are not revalidated. Existing pack cell shares, nominal capacity and future relative density learning remain unchanged. The future fixed-recipe density curve and practical silicon utilization/N:P/aging remain explicit design gaps; this correction restores the historical source design rather than certifying a future cell. New names prevent native datasets silently replacing these selected cell designs.</t>
         </is>
       </c>
     </row>
@@ -21477,7 +21499,7 @@
     <row r="1159">
       <c r="A1159" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B1159">
@@ -21500,14 +21522,14 @@
       </c>
       <c r="G1159" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
     </row>
     <row r="1160">
       <c r="A1160" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
       <c r="B1160">
@@ -21530,7 +21552,7 @@
       </c>
       <c r="G1160" t="inlineStr">
         <is>
-          <t>anode paste, silicon-graphite, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, silicon-graphite, for Li-ion batteries</t>
         </is>
       </c>
     </row>
@@ -22198,7 +22220,7 @@
       </c>
       <c r="B1191" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22254,7 @@
       </c>
       <c r="B1194" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
     </row>
@@ -22268,7 +22290,8 @@
       </c>
       <c r="B1197" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: anode paste, graphite NMC111, Crenna engineering reference. Former reference product: anode paste, graphite NMC111, Crenna engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
         </is>
       </c>
     </row>
@@ -22329,7 +22352,7 @@
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="B1200">
@@ -22352,12 +22375,12 @@
       </c>
       <c r="G1200" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="I1200" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
     </row>
@@ -22890,7 +22913,7 @@
       </c>
       <c r="B1225" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
     </row>
@@ -22924,7 +22947,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22983,8 @@
       </c>
       <c r="B1231" t="inlineStr">
         <is>
-          <t>APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery cell, NMC111, Crenna engineering reference. Former reference product: battery cell, NMC111, Crenna engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED SOURCE-PRECISION NMC111 CELL, issue41, 2026-10-18. Crenna etal2021 DOI10.1016/j.resconrec.2021.105619 public SI https://ars.els-cdn.com/content/image/1-s2.0-S0921344921002287-mmc2.xlsx NMC111 rows79-99,144-153, columnJ. Use exactpublic119.79kgcellretainedmaterials,sourcecolumnJ expertadjustedcathodepaste/Alfoil,explicitgraphiteanodepasteandCufoil. Drygraphitepaste94percentgraphite,3CMC,1carbonblack,2SBR;noSi coating inNMC111source. Source water1kg/kgdrypaste is processwater,not retainedcellmass;heat7.724380864066159MJ,mix/cut/calender.44058783783783784kWh,wastewater.001m3perkgdrypaste. Syntheticgraphite/latexmanufacturing remainbackgroundproxies. CellCufoil.12379998330411553kg/kg separatefromanodepaste.20368979046664995,sourceCufoil/(paste+foil)=37.803percent;notnative rounded32percentanodeassembly. Preservefullpublicelectrolyte,separator,cathodepaste,Alfoil,PET/PPcase,Alcase/positive/Cunegativeterminals. Exactretainedsum1kg/kg;extrusion/rolling are fabricationservicesandnotaddedas retainedmaterial. Reference100percentcellassemblyretention,not measuredprocessyield;upstreammanufacturingyieldsleftinsuppliers. Sourcecellfactory.902917389kWh+formation.2845557832kWh,12.5095MJheat retainedonce. Existing1kgcapacityhardwarecellfractionandbaseline.18kWh/kgcellunchanged;do NOT apply1/.9919toeveryoriginalinput. Source119.79kgmassdoesnotvalidateconfigured180Wh/kgfuturecellperformance;futuredensitylearningunchangedinexistingcapacitymarkets and chemistry-specificaging/loading remainsgap. For3.9+useexistingnativeCNcathodeNMC111marketasbackgroundproxy.3.8publicGLOsupplementprovidesexplicitfallbackCNmarketremovedwhen nativeexists;newanode/cellidentitypreventsnativecellfromsilentlysubstitutingthisreference. Cathodeupstreamrecipe/electrolytepurity/N:P/formationlossarenotrevalidated. PackandcellEOLremain existingcompletepack treatmentboundary,not extra1kgwastepercellhere. This corrects source transfer/materialboundary,not provenwhole-systemaccuracyorprimary/secondaryshare.</t>
         </is>
       </c>
     </row>
@@ -23021,7 +23045,7 @@
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
       <c r="B1234">
@@ -23044,19 +23068,19 @@
       </c>
       <c r="G1234" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
       <c r="I1234" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="B1235">
@@ -23079,12 +23103,12 @@
       </c>
       <c r="G1235" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="I1235" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
     </row>
@@ -23621,7 +23645,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
         </is>
       </c>
     </row>
@@ -23655,7 +23679,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23715,8 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: calcination oxygen and residue handling, NMC955 engineering reference. Former reference product: calcination oxygen and residue handling, NMC955 engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}</t>
         </is>
       </c>
     </row>
@@ -23752,7 +23777,7 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
         </is>
       </c>
       <c r="B1262">
@@ -23775,12 +23800,12 @@
       </c>
       <c r="G1262" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
         </is>
       </c>
       <c r="I1262" t="inlineStr">
         <is>
-          <t>calcination oxygen and residue handling, NMC955 engineering reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24093,7 @@
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
     </row>
@@ -24102,7 +24127,7 @@
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24163,8 @@
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery cell, NMC532, source-precision engineering reference. Former reference product: battery cell, NMC532, source-precision engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED NMC532 DRY-PASTE / COLLECTOR REFERENCE, issue 45, 2026-10-18. Crenna et al. 2021, DOI 10.1016/j.resconrec.2021.105619, public SI mmc2.xlsx, NMC111 J79:J99 and J144:J153; NMC532 is a declared chemistry adaptation, not a measured NMC532 cell. Use the same public 119.79 kg component geometry underlying the historical adapted NMC532 recipe, at source precision. Adopt the expert-adjusted column J cathode-paste and aluminium-collector quantities. Dry paste is 94% synthetic graphite, 3% CMC, 1% carbon black and 2% SBR, with no assumed silicon; use the existing explicit graphite-paste reference from issue 41. This is an engineering transfer of NMC111 geometry to NMC532, not chemistry-specific measured electrode dimensions. Separate 0.20368979046665 kg dry paste and 0.123799983304116 kg copper foil per kg cell; never buy a complete foil-containing anode as paste. Source PP is 0.1519/119.79 = 0.00126805242507722 kg/kg cell for this reference, not the erroneous native 107/48 denominator or an unsupported mixture of two cell reference masses. PET, separator, electrolyte, case, terminal and process quantities are transferred consistently with that geometry. Retained material sum is one kg; forming and rolling are additional services, not retained mass. No blanket normalization, invented filler or source-measured yield: 100% final assembly retention remains the explicit reference; upstream supplier yields remain. Preserve current pack cell share, nominal kWh, density learning and vehicle service budgets. Density, voltage, utilization, N/P, actual NMC532 electrode loading and cycle life remain unvalidated performance assumptions. Existing NMC532 cathode is a background proxy: use native Chinese cathode market when present, with a public GLO supplemental fallback for older source versions. The fallback is removed as a duplicate where native supply exists. Dedicated cell identity is linked from the current hardware provider in a workbook loaded for every supported version, so a skipped legacy supplement cannot undo this correction. No primary/secondary or extra battery end-of-life treatment; existing complete-pack treatment remains once.</t>
         </is>
       </c>
     </row>
@@ -24199,7 +24225,7 @@
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
       <c r="B1289">
@@ -24222,19 +24248,19 @@
       </c>
       <c r="G1289" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
       <c r="I1289" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste production, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="B1290">
@@ -24257,12 +24283,12 @@
       </c>
       <c r="G1290" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
       <c r="I1290" t="inlineStr">
         <is>
-          <t>anode paste, graphite NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">anode paste, graphite, for Li-ion battery, NMC111</t>
         </is>
       </c>
     </row>
@@ -24799,7 +24825,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
         </is>
       </c>
     </row>
@@ -24833,7 +24859,7 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
         </is>
       </c>
     </row>
@@ -24869,7 +24895,8 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t>APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: oxygen and LiOH residue handling, NCA calcination reference. Former reference product: oxygen and LiOH residue handling, NCA calcination reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}</t>
         </is>
       </c>
     </row>
@@ -24930,7 +24957,7 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
         </is>
       </c>
       <c r="B1317">
@@ -24953,12 +24980,12 @@
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
         </is>
       </c>
       <c r="I1317" t="inlineStr">
         <is>
-          <t>oxygen and LiOH residue handling, NCA calcination reference</t>
+          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25067,7 @@
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate production, ethylene carbonate chlorination</t>
         </is>
       </c>
     </row>
@@ -25074,7 +25101,7 @@
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate, ethylene carbonate chlorination</t>
         </is>
       </c>
     </row>
@@ -25110,7 +25137,8 @@
       </c>
       <c r="B1328" t="inlineStr">
         <is>
-          <t>APPROVED VINYLENE-CARBONATE REACTION REFERENCE, issue47, 2026-10-18. Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive. The intended cyclic unsaturated battery additive is VINYLENE carbonate, not a sulfite or an unspecified vinyl carbonate ester. Correct active electrolyte link to a uniquely named VC supplier, retaining0.024kg/kg electrolyte. Existing vinyl carbonate name becomes a compatibility alias purchasing the same new VC once; its old chemically unbalanced inputs are disabled. Patent Example1 uses0.420mol chloroethylene carbonate,84mlEC solvent and0.630molTEA near60C; Example3 yields73.3%purified VC. Adopt that isolated yield, but explicitly assume100%selective initial UV chlorination and complete chemical dehydrochlorination, with unrecovered VC collected as same-composition organic/polymer residue. Those reaction-versus-isolation splits are engineering assumptions, not measured process selectivities. Reactions: EC+Cl2 -&gt; chloroEC+HCl; chloroEC+TEA -&gt; VC+TEA.HCl. One HCl is captured from chlorination; the other is bound in amine salt. Assume95%recovery of unreacted0.5molTEA/molCEC, and95%ECsolvent recovery, with solvent density1320kg/m3 assumed at process temperature. Buy net make-up only; internally recycled material receives no avoided-production credit. Remaining amine and solvent go once to hazardous organic waste; do not send TEA.HCl to inert landfill. Acid/amine salt collected in wastewater, not vented as unbalanced chlorine:30wt%HCl capture plus wash water equal salt mass, wastewater density1000kg/m3 assumed. Generic wastewater cannot certify chloride or amine-specific fate. Nitrogen0.019kg/kg remains original inert-gas utility, venting/direct species unresolved. Retain original aggregate0.416kWh+2.35MJ, factory and freight as unvalidated utility/delivery proxies; UV lamp, cooling, solvent distillation and high-purity drying energy are not independently measured. Plant corrosion alloys and auxiliary equipment remain unquantified critical-metal coverage gaps. This is a mass/atom-consistent declared engineering reference, not a recovered manufacturer LCI or proof of industrial electrolyte purity. No new catalyst metals or commercial-grade purity claims. Sensitivity:59-85%isolation,90-99%amine/solvent recovery, nonselective chlorination and process utilities. Source assumptions and numeric mass budget: {"CAS":"872-36-6","formula":"C3H2O3","isolated_yield_from_CEC":0.733,"ethylene_carbonate_reactant_kg":1.3962200934498092,"chlorine_kg":1.124117151842923,"triethylamine_gross_kg":2.406617495340781,"triethylamine_recovered_internal_kg":0.7620955401912473,"triethylamine_net_kg":1.6445219551495338,"EC_solvent_circulation_kg":4.185711256509614,"EC_solvent_makeup_kg":0.20928556282548072,"TEA_HCl_in_effluent_kg":2.182452046097746,"HCl_in_effluent_kg":0.5780403825372256,"water_for_capture_and_washing_kg":3.5312129386846056,"effluent_kg":6.291705367319578,"organic_waste_kg":0.6136523346327748}</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: vinylene carbonate, EC chlorination engineering reference. Former reference product: vinylene carbonate, EC chlorination engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED VINYLENE-CARBONATE REACTION REFERENCE, issue47, 2026-10-18. Vinylene carbonate identity CAS872-36-6, C3H2O3; Merck primary patent US6395908B1 Examples1/3 https://patents.google.com/patent/US6395908B1/en ; chlorination/amine route also described in US20090176997A1 https://patents.google.com/patent/US20090176997A1/en . Public Crenna2021 SI NMC111 electrolyte recipe retains2.4wt% additive. The intended cyclic unsaturated battery additive is VINYLENE carbonate, not a sulfite or an unspecified vinyl carbonate ester. Correct active electrolyte link to a uniquely named VC supplier, retaining0.024kg/kg electrolyte. Existing vinyl carbonate name becomes a compatibility alias purchasing the same new VC once; its old chemically unbalanced inputs are disabled. Patent Example1 uses0.420mol chloroethylene carbonate,84mlEC solvent and0.630molTEA near60C; Example3 yields73.3%purified VC. Adopt that isolated yield, but explicitly assume100%selective initial UV chlorination and complete chemical dehydrochlorination, with unrecovered VC collected as same-composition organic/polymer residue. Those reaction-versus-isolation splits are engineering assumptions, not measured process selectivities. Reactions: EC+Cl2 -&gt; chloroEC+HCl; chloroEC+TEA -&gt; VC+TEA.HCl. One HCl is captured from chlorination; the other is bound in amine salt. Assume95%recovery of unreacted0.5molTEA/molCEC, and95%ECsolvent recovery, with solvent density1320kg/m3 assumed at process temperature. Buy net make-up only; internally recycled material receives no avoided-production credit. Remaining amine and solvent go once to hazardous organic waste; do not send TEA.HCl to inert landfill. Acid/amine salt collected in wastewater, not vented as unbalanced chlorine:30wt%HCl capture plus wash water equal salt mass, wastewater density1000kg/m3 assumed. Generic wastewater cannot certify chloride or amine-specific fate. Nitrogen0.019kg/kg remains original inert-gas utility, venting/direct species unresolved. Retain original aggregate0.416kWh+2.35MJ, factory and freight as unvalidated utility/delivery proxies; UV lamp, cooling, solvent distillation and high-purity drying energy are not independently measured. Plant corrosion alloys and auxiliary equipment remain unquantified critical-metal coverage gaps. This is a mass/atom-consistent declared engineering reference, not a recovered manufacturer LCI or proof of industrial electrolyte purity. No new catalyst metals or commercial-grade purity claims. Sensitivity:59-85%isolation,90-99%amine/solvent recovery, nonselective chlorination and process utilities. Source assumptions and numeric mass budget: {"CAS":"872-36-6","formula":"C3H2O3","isolated_yield_from_CEC":0.733,"ethylene_carbonate_reactant_kg":1.3962200934498092,"chlorine_kg":1.124117151842923,"triethylamine_gross_kg":2.406617495340781,"triethylamine_recovered_internal_kg":0.7620955401912473,"triethylamine_net_kg":1.6445219551495338,"EC_solvent_circulation_kg":4.185711256509614,"EC_solvent_makeup_kg":0.20928556282548072,"TEA_HCl_in_effluent_kg":2.182452046097746,"HCl_in_effluent_kg":0.5780403825372256,"water_for_capture_and_washing_kg":3.5312129386846056,"effluent_kg":6.291705367319578,"organic_waste_kg":0.6136523346327748}</t>
         </is>
       </c>
     </row>
@@ -25171,7 +25199,7 @@
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate production, ethylene carbonate chlorination</t>
         </is>
       </c>
       <c r="B1331">
@@ -25194,12 +25222,12 @@
       </c>
       <c r="G1331" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate, ethylene carbonate chlorination</t>
         </is>
       </c>
       <c r="I1331" t="inlineStr">
         <is>
-          <t>vinylene carbonate, EC chlorination engineering reference</t>
+          <t xml:space="preserve">vinylene carbonate, ethylene carbonate chlorination</t>
         </is>
       </c>
     </row>
@@ -25701,7 +25729,7 @@
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -25735,7 +25763,7 @@
       </c>
       <c r="B1351" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -25771,7 +25799,8 @@
       </c>
       <c r="B1354" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, LFP, density-scaled reference. Former reference product: market for battery cells, Li-ion, LFP, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -25832,7 +25861,7 @@
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1357">
@@ -25855,12 +25884,12 @@
       </c>
       <c r="G1357" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1357" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LFP, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LFP, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -25942,7 +25971,7 @@
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -25976,7 +26005,7 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26012,7 +26041,9 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -26073,7 +26104,7 @@
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="B1371">
@@ -26096,12 +26127,12 @@
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="I1371" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26533,7 +26564,7 @@
       </c>
       <c r="B1386" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -26567,7 +26598,7 @@
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -26603,7 +26634,8 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NMC111, density-scaled reference. Former reference product: market for battery cells, Li-ion, NMC111, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -26664,7 +26696,7 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1395">
@@ -26687,19 +26719,19 @@
       </c>
       <c r="G1395" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1395" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC111, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
       <c r="B1396">
@@ -26722,12 +26754,12 @@
       </c>
       <c r="G1396" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
       <c r="I1396" t="inlineStr">
         <is>
-          <t>battery cell, NMC111, Crenna engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC111, prismatic</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26806,7 @@
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26808,7 +26840,7 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26844,7 +26876,9 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -26905,7 +26939,7 @@
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="B1409">
@@ -26928,12 +26962,12 @@
       </c>
       <c r="G1409" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="I1409" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27365,7 +27399,7 @@
       </c>
       <c r="B1424" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -27399,7 +27433,7 @@
       </c>
       <c r="B1427" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -27435,7 +27469,8 @@
       </c>
       <c r="B1430" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NMC532, density-scaled reference. Former reference product: market for battery cells, Li-ion, NMC532, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -27496,7 +27531,7 @@
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1433">
@@ -27519,19 +27554,19 @@
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1433" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC532, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
       <c r="B1434">
@@ -27554,12 +27589,12 @@
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
       <c r="I1434" t="inlineStr">
         <is>
-          <t>battery cell, NMC532, source-precision engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC532, prismatic</t>
         </is>
       </c>
     </row>
@@ -27606,7 +27641,7 @@
       </c>
       <c r="B1438" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27640,7 +27675,7 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27676,7 +27711,9 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -27737,7 +27774,7 @@
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="B1447">
@@ -27760,12 +27797,12 @@
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="I1447" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28197,7 +28234,7 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -28231,7 +28268,7 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -28267,7 +28304,8 @@
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NMC622, density-scaled reference. Former reference product: market for battery cells, Li-ion, NMC622, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -28328,7 +28366,7 @@
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1471">
@@ -28351,12 +28389,12 @@
       </c>
       <c r="G1471" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1471" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC622, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC622, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28476,7 @@
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28472,7 +28510,7 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28508,7 +28546,9 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -28569,7 +28609,7 @@
     <row r="1485">
       <c r="A1485" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="B1485">
@@ -28592,12 +28632,12 @@
       </c>
       <c r="G1485" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="I1485" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29029,7 +29069,7 @@
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -29063,7 +29103,7 @@
       </c>
       <c r="B1503" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -29099,7 +29139,8 @@
       </c>
       <c r="B1506" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NMC811, density-scaled reference. Former reference product: market for battery cells, Li-ion, NMC811, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -29160,7 +29201,7 @@
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1509">
@@ -29183,19 +29224,19 @@
       </c>
       <c r="G1509" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1509" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC811, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B1510">
@@ -29218,12 +29259,12 @@
       </c>
       <c r="G1510" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
       <c r="I1510" t="inlineStr">
         <is>
-          <t>battery cell, NMC811, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC811, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -29270,7 +29311,7 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29304,7 +29345,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29340,7 +29381,9 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -29401,7 +29444,7 @@
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="B1523">
@@ -29424,12 +29467,12 @@
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="I1523" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29861,7 +29904,7 @@
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -29895,7 +29938,7 @@
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -29931,7 +29974,8 @@
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NMC955, density-scaled reference. Former reference product: market for battery cells, Li-ion, NMC955, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -29992,7 +30036,7 @@
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1547">
@@ -30015,12 +30059,12 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1547" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NMC955, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NMC955, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -30102,7 +30146,7 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30136,7 +30180,7 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30172,7 +30216,9 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -30233,7 +30279,7 @@
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="B1561">
@@ -30256,12 +30302,12 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="I1561" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30693,7 +30739,7 @@
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -30727,7 +30773,7 @@
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -30763,7 +30809,8 @@
       </c>
       <c r="B1582" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, NCA, density-scaled reference. Former reference product: market for battery cells, Li-ion, NCA, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -30824,7 +30871,7 @@
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1585">
@@ -30847,19 +30894,19 @@
       </c>
       <c r="G1585" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1585" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, NCA, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell production, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
       <c r="B1586">
@@ -30882,12 +30929,12 @@
       </c>
       <c r="G1586" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
       <c r="I1586" t="inlineStr">
         <is>
-          <t>battery cell, NCA, Crenna anode engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, NCA, silicon-graphite anode</t>
         </is>
       </c>
     </row>
@@ -30934,7 +30981,7 @@
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30968,7 +31015,7 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31004,7 +31051,9 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -31065,7 +31114,7 @@
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="B1599">
@@ -31088,12 +31137,12 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="I1599" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31525,7 +31574,7 @@
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -31559,7 +31608,7 @@
       </c>
       <c r="B1617" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -31595,7 +31644,8 @@
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, LTO, density-scaled reference. Former reference product: market for battery cells, Li-ion, LTO, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -31656,7 +31706,7 @@
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1623">
@@ -31679,12 +31729,12 @@
       </c>
       <c r="G1623" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1623" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LTO, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LTO, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -31766,7 +31816,7 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31800,7 +31850,7 @@
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31836,7 +31886,9 @@
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -31897,7 +31949,7 @@
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="B1637">
@@ -31920,12 +31972,12 @@
       </c>
       <c r="G1637" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="I1637" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -32357,7 +32409,7 @@
       </c>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -32391,7 +32443,7 @@
       </c>
       <c r="B1655" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
     </row>
@@ -32427,7 +32479,8 @@
       </c>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: market for battery cells, Li-ion, LiMn2O4, density-scaled reference. Former reference product: market for battery cells, Li-ion, LiMn2O4, density-scaled reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -32488,7 +32541,7 @@
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
       <c r="B1661">
@@ -32511,19 +32564,19 @@
       </c>
       <c r="G1661" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
       <c r="I1661" t="inlineStr">
         <is>
-          <t>market for battery cells, Li-ion, LiMn2O4, density-scaled reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4, including end-of-life treatment</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>market for battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="B1662">
@@ -32546,12 +32599,12 @@
       </c>
       <c r="G1662" t="inlineStr">
         <is>
-          <t>battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
       <c r="I1662" t="inlineStr">
         <is>
-          <t>battery cell, LiMn2O4, public engineering reference</t>
+          <t xml:space="preserve">battery cell, Li-ion, LiMn2O4</t>
         </is>
       </c>
     </row>
@@ -32598,7 +32651,7 @@
       </c>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -32632,7 +32685,7 @@
       </c>
       <c r="B1669" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -32668,7 +32721,9 @@
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t>APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
+APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
       </c>
     </row>
@@ -32729,7 +32784,7 @@
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack component production and end-of-life treatment, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="B1675">
@@ -32752,12 +32807,12 @@
       </c>
       <c r="G1675" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="I1675" t="inlineStr">
         <is>
-          <t>battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference</t>
+          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -6710,7 +6710,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NMC955 oxide calcination</t>
         </is>
       </c>
       <c r="B362">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
+          <t xml:space="preserve">calcination support, NMC955 oxide</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
     <row r="666" spans="1:7" ns3:dyDescent="0.2">
       <c r="A666" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NCA oxide calcination</t>
         </is>
       </c>
       <c r="B666">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -11206,7 +11206,13 @@
       </c>
       <c r="G666" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
+          <t xml:space="preserve">calcination support, NCA oxide</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Oxygen supply and residue handling per kilogram of NCA oxide processed. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+</t>
         </is>
       </c>
     </row>
@@ -23645,7 +23651,7 @@
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NMC955 oxide calcination</t>
         </is>
       </c>
     </row>
@@ -23679,7 +23685,7 @@
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
+          <t xml:space="preserve">calcination support, NMC955 oxide</t>
         </is>
       </c>
     </row>
@@ -23691,7 +23697,7 @@
       </c>
       <c r="B1257" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23721,8 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: calcination oxygen and residue handling, NMC955 engineering reference. Former reference product: calcination oxygen and residue handling, NMC955 engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Oxygen supply and residue handling per kilogram of NMC955 oxide processed. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: calcination oxygen and residue handling, NMC955 engineering reference. Former reference product: calcination oxygen and residue handling, NMC955 engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED NMC955 CALCINATION/PRECURSOR ELEMENTAL REFERENCE, issue42, 2026-10-18. Crenna2021 public cathode-process adaptation DOI10.1016/j.resconrec.2021.105619; explicit balanced reactions derived from nominal formulas; co-precipitation/oxygen-calcination route documented by Merck https://www.merckmillipore.com/SG/en/technical-documents/technical-article/materials-science-and-engineering/batteries-supercapacitors-and-fuel-cells/lib-couette-taylor-flow-reactor; US20200031682A1 https://patents.google.com/patent/US20200031682A1/en describes sulfate-bearing effluent. Nominal dryLiNi0.90Co0.05Mn0.05O2 andM(OH)2,100percentpureanhydroussulfates/dryprecursor,100percentcationrecovery as an ENGINEERING REFERENCE,not measuredindustrialpurity/hydration/conversionyield. Calcinationreaction0.5Li2CO3+M(OH)2+0.25O2-&gt;LiMO2+0.5CO2+H2O. PrecipitationMSO4+2NaOH-&gt;M(OH)2+Na2SO4. BalancesLi/Ni/Co/Mn/C/H/O/S/Na,not onlyCO2/water. Retain existing0.383kgLi2CO3feed/kgoxide; amount above required stoichiometry explicitly leaves asunreactedcarbonate residue,not assumed extraLi in1kgoxide orrecoveredcredit. Liquidoxygen is a stoichiometricmanufactured-atmosphere supplyproxy;actualgasflow/purge/utilizationliquefaction needvalidation,no claim realprocessusesliquidO2delivery. Newnamed helperbuysO2andtreatsresidueonceperkgoxide;existingCO2/waterexchangesmatch reaction. Upstream dryhydroxide metalfeeds corrected frompreviousfixed1.62kgsulfates toformula-derivedspecies masses per1kgprecursor;retaining1.62wouldleavea cationdeficit evenwithcorrect90/5/5ratios. Sodiumhydroxide input unitis dryNaOHin50wtpercentsolution,not total solutionkg;associate equalmasscarriedwater. Existing0.619633973189554kgwaterresource retainedas once-throughcooling/processdilutionreference;assumecollectionwithsulfatesolution. Effluentvolume=(Na2SO4+solutionwater+retainedwaterdraw)/1000m3perkgprecursor atassumed1000kg/m3;actualsolutiondensity/concentration/washingneedvalidation. GenericwastewaterproxydoesNOTexplicitlymodel sodium/sulfate fate,not product-sodiumsulfatemarket,not credit; masscompositiondeclaredinmetadata,chemicaltreatmentremainsgap. Ammoniainputequalsairoutput,existingenergy/factory/transportunchangednot revalidatedagainstnewmassflows. Existingcobalt supplier is economically allocated;no physicalore/scalingfactororprimary-secondarysplitisintroduced. Its rounded0.38kgCo/kgCoSO4 versuspureformula fractionremains backgroundproxygap;do notreadbalancedforegroundasvalidatedwholeupstreammetalbalance. Li-richNi90 industrialrouteusuallyusesLiOH;retainoriginalcarbonate-routeas declaredengineering stoichiometricbenchmark,not validatedcommercialNMC955recipe or futureelectrodeperformance. Sensitivities95-100percentcationretention,0-2percentLi excess,oxygenutilization50-100percent,anhydrousversushydratedfeedwithcorrectdry-equivalent conversions. These variations are documented,not silentlyassignedas probabilities. Existingcell/pack/density/serviceallocationunchanged; numericalsystemmetalchange requiresnewscenarioresults. Computed reference coefficients: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Mn":54.938044,"H":1.008,"O":15.999,"C":12.011,"S":32.06,"Na":22.98976928},"cation_moles":{"Ni":0.9,"Co":0.05,"Mn":0.05},"M_hydroxide_g_per_mol":92.5316219,"M_oxide_g_per_mol":97.4556219,"oxide_per_kg":{"dry_hydroxide_kg":0.9494744386829469,"Li2CO3_feed_kg":0.383,"stoichiometric_Li2CO3_kg":0.3790853650075574,"O2_kg":0.08208351497883162,"CO2_kg":0.2257899500408401,"water_kg":0.18485336862849572,"unreacted_Li2CO3_kg":0.0039146349924426005},"hydroxide_per_kg":{"anhydrous_sulfates_kg":{"Ni":1.5051552878919114,"Co":0.08374931229860999,"Mn":0.08159050976280359},"dry_NaOH_kg":0.8644994750708028,"NaOH_solution_associated_water_kg":0.8644994750708028,"Na2SO4_kg_in_effluent":1.534994585024128,"retained_water_draw_kg":0.619633973189554,"effluent_kg_at1000kg_per_m3":3.0191280332844848}}</t>
         </is>
       </c>
@@ -23777,7 +23784,7 @@
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NMC955</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NMC955 oxide calcination</t>
         </is>
       </c>
       <c r="B1262">
@@ -23790,7 +23797,7 @@
       </c>
       <c r="D1262" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F1262" t="inlineStr">
@@ -23800,12 +23807,12 @@
       </c>
       <c r="G1262" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
+          <t xml:space="preserve">calcination support, NMC955 oxide</t>
         </is>
       </c>
       <c r="I1262" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NMC955</t>
+          <t xml:space="preserve">calcination support, NMC955 oxide</t>
         </is>
       </c>
     </row>
@@ -24825,7 +24832,7 @@
       </c>
       <c r="B1308" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NCA oxide calcination</t>
         </is>
       </c>
     </row>
@@ -24859,7 +24866,7 @@
       </c>
       <c r="B1311" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
+          <t xml:space="preserve">calcination support, NCA oxide</t>
         </is>
       </c>
     </row>
@@ -24871,7 +24878,7 @@
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -24895,7 +24902,8 @@
       </c>
       <c r="B1314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: oxygen and LiOH residue handling, NCA calcination reference. Former reference product: oxygen and LiOH residue handling, NCA calcination reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Oxygen supply and residue handling per kilogram of NCA oxide processed. Unit field: kilogram. Former reference: 1 unit = 1 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: oxygen and LiOH residue handling, NCA calcination reference. Former reference product: oxygen and LiOH residue handling, NCA calcination reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED NCA PRECURSOR AND LITHIATION BALANCE, issue 52, 2026-10-18. NCA co-precipitation reference: Journal of Electrochemistry DOI 10.13208/j.electrochem.180328, https://electrochem.xmu.edu.cn/CN/10.13208/j.electrochem.180328 ; Ni0.8Co0.15Al0.05(OH)2.05 is also specified in ACS AMI DOI 10.1021/acsami.7b12306. Existing Crenna2021 engineering process adaptation retained for utilities. Adopt pure dry mixed hydroxide containing Ni(II), Co(II), Al(III), hence 2.05 hydroxyl groups per total cation; the Al sulfate route is a documented preparation option, not proof that commercial NCA uses this exact plant. Precipitation: 0.8NiSO4+0.15CoSO4+0.025Al2(SO4)3+2.05NaOH -&gt; mixed(OH)2.05+1.025Na2SO4. Lithiation per mol oxide: mixed(OH)2.05+LiOH.H2O+0.2375O2 -&gt; LiNi0.8Co0.15Al0.05O2+2.525H2O. Explicit engineering reference: 100% nominal reagent purity and cation recovery, dry anhydrous sulfates, hydrated LiOH as already correctly supplied; not measured industrial assays/yields. Preserve the existing LiOH-monohydrate feed and its 0.25 kg anhydrous-equivalent basis. Necessary stoichiometric Li reacts; remaining dry LiOH is collected as residue, while all hydrate water evaporates. No repeated hydration multiplier or assumed additional lithium dose. Manufactured liquid oxygen is a supply-route proxy for furnace oxygen; purge/utilization/delivery form remain uncertain. Retain original process energy, freight, factory and ammonia input/air emissions. The small NH3 input-minus-air difference is declared dissolved in effluent, not erased. NaOH product is dry equivalent in 50% solution; equal associated solution-water mass plus existing cooling/process draw and dissolved sulfate are collected at assumed 1000kg/m3 density. Generic wastewater and hazardous-residue treatment do not resolve sulfate or lithium-specific fate and receive no recovery credits. Cobalt remains its existing economically allocated background supplier, with purity/allocated-versus-physical feed differences unvalidated. This balances the explicit foreground chemistry without certifying the complete upstream supply chain. NCA cathode quantity in LTO cells and battery life/density remain unchanged. Sensitivity: 95-100% cation recovery, 0-2% Li excess, actual hydrate/assay, oxygen utilization and washing water. Numeric reference: {"atomic_g_per_mol":{"Li":6.94,"Ni":58.6934,"Co":58.933194,"Al":26.9815385,"H":1.008,"O":15.999,"S":32.06,"Na":22.98976928},"hydroxide_formula":"Ni0.8Co0.15Al0.05(OH)2.05","oxide_formula":"LiNi0.8Co0.15Al0.05O2","per_kg_oxide":{"dry_hydroxide_kg":0.9576022616511578,"LiOH_H2O_feed_kg":0.4380715747275233,"stoichiometric_LiOH_H2O_kg":0.4367321435553158,"oxygen_kg":0.07909434353110459,"water_vapor_kg":0.47400378931160514,"unreacted_anhydrous_LiOH_kg":0.0007643905981805525},"per_kg_hydroxide":{"anhydrous_sulfates_kg":{"Ni":1.345528110923179,"Co":0.2526774547465847,"Al":0.09296219034692595},"dry_NaOH_kg":0.8911536465998793,"dissolved_Na2SO4_kg":1.5823214026165688,"effluent_kg_at1000kg_per_m3":3.0931483224060026,"dissolved_NH3_kg":3.930000000000079e-05}}</t>
         </is>
       </c>
@@ -24957,7 +24965,7 @@
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t xml:space="preserve">treatment of calcination residues and oxygen handling, NCA</t>
+          <t xml:space="preserve">oxygen supply and residue handling, NCA oxide calcination</t>
         </is>
       </c>
       <c r="B1317">
@@ -24970,7 +24978,7 @@
       </c>
       <c r="D1317" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F1317" t="inlineStr">
@@ -24980,12 +24988,12 @@
       </c>
       <c r="G1317" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
+          <t xml:space="preserve">calcination support, NCA oxide</t>
         </is>
       </c>
       <c r="I1317" t="inlineStr">
         <is>
-          <t xml:space="preserve">calcination residue treatment and oxygen handling, NCA</t>
+          <t xml:space="preserve">calcination support, NCA oxide</t>
         </is>
       </c>
     </row>
@@ -26005,7 +26013,7 @@
       </c>
       <c r="B1365" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26017,7 +26025,7 @@
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -26041,7 +26049,8 @@
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LFP, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -26117,7 +26126,7 @@
       </c>
       <c r="D1371" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1371" t="inlineStr">
@@ -26127,12 +26136,12 @@
       </c>
       <c r="G1371" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
       <c r="I1371" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LFP, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LFP, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26840,7 +26849,7 @@
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -26852,7 +26861,7 @@
       </c>
       <c r="B1404" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -26876,7 +26885,8 @@
       </c>
       <c r="B1406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC111, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -26952,7 +26962,7 @@
       </c>
       <c r="D1409" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1409" t="inlineStr">
@@ -26962,12 +26972,12 @@
       </c>
       <c r="G1409" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
       <c r="I1409" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC111, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC111, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27675,7 +27685,7 @@
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -27687,7 +27697,7 @@
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -27711,7 +27721,8 @@
       </c>
       <c r="B1444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC532, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -27787,7 +27798,7 @@
       </c>
       <c r="D1447" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1447" t="inlineStr">
@@ -27797,12 +27808,12 @@
       </c>
       <c r="G1447" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
       <c r="I1447" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC532, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC532, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28510,7 +28521,7 @@
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -28522,7 +28533,7 @@
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -28546,7 +28557,8 @@
       </c>
       <c r="B1482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC622, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -28622,7 +28634,7 @@
       </c>
       <c r="D1485" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1485" t="inlineStr">
@@ -28632,12 +28644,12 @@
       </c>
       <c r="G1485" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
       <c r="I1485" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC622, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC622, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29345,7 +29357,7 @@
       </c>
       <c r="B1517" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -29357,7 +29369,7 @@
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -29381,7 +29393,8 @@
       </c>
       <c r="B1520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC811, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -29457,7 +29470,7 @@
       </c>
       <c r="D1523" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1523" t="inlineStr">
@@ -29467,12 +29480,12 @@
       </c>
       <c r="G1523" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
       <c r="I1523" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC811, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC811, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30180,7 +30193,7 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -30192,7 +30205,7 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -30216,7 +30229,8 @@
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NMC955, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -30292,7 +30306,7 @@
       </c>
       <c r="D1561" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -30302,12 +30316,12 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
       <c r="I1561" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NMC955, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NMC955, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31015,7 +31029,7 @@
       </c>
       <c r="B1593" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31027,7 +31041,7 @@
       </c>
       <c r="B1594" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -31051,7 +31065,8 @@
       </c>
       <c r="B1596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, NCA, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -31127,7 +31142,7 @@
       </c>
       <c r="D1599" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1599" t="inlineStr">
@@ -31137,12 +31152,12 @@
       </c>
       <c r="G1599" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
       <c r="I1599" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, NCA, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, NCA, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31850,7 +31865,7 @@
       </c>
       <c r="B1631" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -31862,7 +31877,7 @@
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -31886,7 +31901,8 @@
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LTO, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -31962,7 +31978,7 @@
       </c>
       <c r="D1637" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1637" t="inlineStr">
@@ -31972,12 +31988,12 @@
       </c>
       <c r="G1637" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
       <c r="I1637" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LTO, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LTO, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -32685,7 +32701,7 @@
       </c>
       <c r="B1669" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
     </row>
@@ -32697,7 +32713,7 @@
       </c>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
     </row>
@@ -32721,7 +32737,8 @@
       </c>
       <c r="B1672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: Provision of the fixed noncell components attributed to one baseline nominal kWh of installed battery storage capacity. Unit field: kilowatt hour. Former reference: 1 unit = 1 kilowatt hour on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. This is noncell component provision per nominal kWh of installed storage capacity served, not electricity supplied and not a second complete battery. Cell capacity remains supplied separately. The noncell recipe and dose are unchanged; its non-kg reference keeps the approved fixed hardware outside cell-only density learning in future years. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Former reference product: battery fixed noncell hardware, Li-ion, LiMn2O4, baseline-kWh reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 The reference remains the non-cell component package attributed to one baseline nominal kWh, not one complete physical battery pack.
 APPROVED CELL-ONLY DENSITY LEARNING AND FIXED PACK HARDWARE, issue63, 2026-10-18. Existing public/source-corrected pack and cell designs documented in these supplemental workbooks; existing premise cell_energy_density trajectories retained verbatim. Fixed noncell design is an explicit counterfactual in absence of pack/current/thermal redesign evidence,not a measuredfuturedesign. For nine conventionalmobile chemistries,LiS,SIB,LiO2 andthreeASSB references,split active capacitypath into kgcellmanufacture and one fixednoncellreference unit perbaseline nominalkWh. Preserve exactbaselinecell mass,allnoncellmaterials,processservices,controls,transport and totaldisposal. Unitbasis is the original explicitly sizedpack architecture attributed to1nominalkWh,not onephysicalpackper1kWh or a newcapacity. Existingruntime scaling appliesonly kgexchanges of namedcapacitydatasets; thus cellmanufacturekg and matchingusedcellkg followunchangeddensityfactor,while casing,busbars,coolant,packaging and theirdisposal are fixedinsideunitprovider. Existing separatelyunitizedcentral/modulecontrols,oxygenlifecycle,cooling are unchanged. No runtime/YAML/learningcurve edit. Noncellhelper buys originalnoncellprocesses once,plusits originalfraction ofusedbattery treatment;Negative cellwaste moves inside the scalablecellprovider at-1kg/kgcell, so it follows exactly the samecellmass; reuse originalcapacitywasterow forfixedunit without movingworkbookrows. The fixedunit is deterministic; prior signed mass uncertainty is removed from thatrow,while original scaledcell distribution is retained. No negativecredit tocancel a completepack orsecondwholepack disposal. LiS/SIB unfold onlyone-to-one packmarket/module boundary; sourcefinishedpackfreight divided bybaselinecell/noncellmass,cellfreight followscellmass andnoncellfreight fixed,baselinefreight identical. Existing cellrecipe andits internalcollectors/separator/case are retained andscale with cellmass: this is a reference ofsamecellformat atgreatercapacity,not proofphysicalcollectorareaorcellhousing canfallthatway. Propercellredesign/areal loading and lifetimepower/cycle behavior remainuncertainties. Fixedpackcurrent,busbarthermal/cooling design is conservativecomparison,not automatically optimalfuturelightweightdesign. No newachieveddensity or unsupportedstructurallearning. Controlsremainexistingfixedarchitecture,not resolvedvehicle-specificchannelcount. HighpowerFCEVcar/truck/bus andhydrogenrail fixedreferences remainoutsidegenericmobilecellcurve. Legacywholepackprovidersremainforotherconsumers; unrelatedstationary/homebattery andflow/leadacid designs needseparatelyscopednoncellaudit,not silentlyredefinedhere. Comparefixednoncellreference toformerproportionalhardware trajectory at2030/2050; baseline mustbeidentical andstaticnoncellwaste mustnotdecay.</t>
         </is>
@@ -32797,7 +32814,7 @@
       </c>
       <c r="D1675" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilowatt hour</t>
         </is>
       </c>
       <c r="F1675" t="inlineStr">
@@ -32807,12 +32824,12 @@
       </c>
       <c r="G1675" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
       <c r="I1675" t="inlineStr">
         <is>
-          <t xml:space="preserve">battery pack components, Li-ion, LiMn2O4, without cells and controls</t>
+          <t xml:space="preserve">battery pack component provision, Li-ion, LiMn2O4, without cells and controls</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC955-LTO.xlsx
@@ -12130,7 +12130,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
+          <t xml:space="preserve">market for battery cell, li-ion, limn2o4</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
+          <t xml:space="preserve">market for battery cell, li-ion, limn2o4</t>
         </is>
       </c>
       <c r="B725">
@@ -19817,7 +19817,7 @@
     <row r="1089">
       <c r="A1089" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
+          <t xml:space="preserve">market for battery cell, li-ion, limn2o4</t>
         </is>
       </c>
       <c r="B1089">
@@ -33208,7 +33208,7 @@
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t xml:space="preserve">market for battery cell, Li-ion, LiMn2O4</t>
+          <t xml:space="preserve">market for battery cell, li-ion, limn2o4</t>
         </is>
       </c>
       <c r="B1711">
